--- a/GearSage-client/rate/excel/rod.xlsx
+++ b/GearSage-client/rate/excel/rod.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K256"/>
+  <dimension ref="A1:K260"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -9558,9 +9558,149 @@
         <v>ダイワ調子極まる。軽量・高感度のバーチカルコンタクトロッド。</v>
       </c>
     </row>
+    <row r="257">
+      <c r="A257" t="str">
+        <v>KR001</v>
+      </c>
+      <c r="B257">
+        <v>35</v>
+      </c>
+      <c r="C257" t="str">
+        <v>NF Series 66 Casting Model</v>
+      </c>
+      <c r="D257" t="str">
+        <v>NF Series 66 Casting Model</v>
+      </c>
+      <c r="E257" t="str">
+        <v/>
+      </c>
+      <c r="F257" t="str">
+        <v/>
+      </c>
+      <c r="G257" t="str">
+        <v>casting</v>
+      </c>
+      <c r="H257" t="str">
+        <v>pkgGear/images/rod/KEITECH/202602261642543817.jpg</v>
+      </c>
+      <c r="I257" t="str">
+        <v>2026-04-10T05:56:19.503Z</v>
+      </c>
+      <c r="J257" t="str">
+        <v>2026-04-10T05:56:19.503Z</v>
+      </c>
+      <c r="K257" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="str">
+        <v>KR002</v>
+      </c>
+      <c r="B258">
+        <v>35</v>
+      </c>
+      <c r="C258" t="str">
+        <v>NF Series 76 Flippin' Stick®</v>
+      </c>
+      <c r="D258" t="str">
+        <v>NF Series 76 Flippin' Stick®</v>
+      </c>
+      <c r="E258" t="str">
+        <v/>
+      </c>
+      <c r="F258" t="str">
+        <v/>
+      </c>
+      <c r="G258" t="str">
+        <v>casting</v>
+      </c>
+      <c r="H258" t="str">
+        <v>pkgGear/images/rod/KEITECH/202407311709371706.jpg</v>
+      </c>
+      <c r="I258" t="str">
+        <v>2026-04-10T05:56:22.101Z</v>
+      </c>
+      <c r="J258" t="str">
+        <v>2026-04-10T05:56:22.101Z</v>
+      </c>
+      <c r="K258" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="str">
+        <v>KR003</v>
+      </c>
+      <c r="B259">
+        <v>35</v>
+      </c>
+      <c r="C259" t="str">
+        <v>F-SPEC Series</v>
+      </c>
+      <c r="D259" t="str">
+        <v>F-SPEC Series</v>
+      </c>
+      <c r="E259" t="str">
+        <v/>
+      </c>
+      <c r="F259" t="str">
+        <v/>
+      </c>
+      <c r="G259" t="str">
+        <v>casting</v>
+      </c>
+      <c r="H259" t="str">
+        <v>pkgGear/images/rod/KEITECH/202506201737523566.jpg</v>
+      </c>
+      <c r="I259" t="str">
+        <v>2026-04-10T05:56:24.964Z</v>
+      </c>
+      <c r="J259" t="str">
+        <v>2026-04-10T05:56:24.964Z</v>
+      </c>
+      <c r="K259" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="str">
+        <v>KR004</v>
+      </c>
+      <c r="B260">
+        <v>35</v>
+      </c>
+      <c r="C260" t="str">
+        <v>76 Series</v>
+      </c>
+      <c r="D260" t="str">
+        <v>76 Series</v>
+      </c>
+      <c r="E260" t="str">
+        <v/>
+      </c>
+      <c r="F260" t="str">
+        <v/>
+      </c>
+      <c r="G260" t="str">
+        <v>casting</v>
+      </c>
+      <c r="H260" t="str">
+        <v>pkgGear/images/rod/KEITECH/202208011647014321.jpg</v>
+      </c>
+      <c r="I260" t="str">
+        <v>2026-04-10T05:56:26.942Z</v>
+      </c>
+      <c r="J260" t="str">
+        <v>2026-04-10T05:56:26.942Z</v>
+      </c>
+      <c r="K260" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K256"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K260"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/GearSage-client/rate/excel/rod.xlsx
+++ b/GearSage-client/rate/excel/rod.xlsx
@@ -457,7 +457,7 @@
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>images/shimano_rods/WORLD SHAULA TECHNICAL EDITION_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/WORLD%20SHAULA%20TECHNICAL%20EDITION_main.jpg</v>
       </c>
       <c r="I2" t="str">
         <v/>
@@ -493,7 +493,7 @@
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>images/shimano_rods/POISON ADRENA_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/POISON%20ADRENA_main.jpg</v>
       </c>
       <c r="I3" t="str">
         <v/>
@@ -529,7 +529,7 @@
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>images/shimano_rods/POISON GLORIOUS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/POISON%20GLORIOUS%20XC_main.jpg</v>
       </c>
       <c r="I4" t="str">
         <v/>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>images/shimano_rods/Majestic+_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/Majestic%20XT_main.jpg</v>
       </c>
       <c r="I5" t="str">
         <v/>
@@ -601,7 +601,7 @@
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>images/shimano_rods/ZODIAS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/ZODIAS_main.jpg</v>
       </c>
       <c r="I6" t="str">
         <v/>
@@ -637,7 +637,7 @@
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>images/shimano_rods/LESATH_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/LESATH_main.jpg</v>
       </c>
       <c r="I7" t="str">
         <v/>
@@ -674,7 +674,7 @@
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>images/shimano_rods/CAPTURE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/CAPTURE_main.jpg</v>
       </c>
       <c r="I8" t="str">
         <v/>
@@ -710,7 +710,7 @@
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>images/shimano_rods/PEGAS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/PEGAS_main.jpg</v>
       </c>
       <c r="I9" t="str">
         <v/>
@@ -747,7 +747,7 @@
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>images/shimano_rods/CARDIFF STREAM PREMIUM_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/CARDIFF%20STREAM%20PREMIUM_main.jpg</v>
       </c>
       <c r="I10" t="str">
         <v/>
@@ -783,7 +783,7 @@
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>images/shimano_rods/UNFIX_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/UNFIX_main.jpg</v>
       </c>
       <c r="I11" t="str">
         <v/>
@@ -819,7 +819,7 @@
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>images/shimano_rods/POISON ULTIMA_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/POISON%20ULTIMA%20PACK_main.jpg</v>
       </c>
       <c r="I12" t="str">
         <v/>
@@ -854,7 +854,7 @@
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>images/shimano_rods/ARGUS HUNTER_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/ARGUS%20HUNTER%20SPECIAL_main.jpg</v>
       </c>
       <c r="I13" t="str">
         <v/>
@@ -891,7 +891,7 @@
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>images/shimano_rods/LEONIS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/LEONIS_main.jpg</v>
       </c>
       <c r="I14" t="str">
         <v/>
@@ -927,7 +927,7 @@
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>images/shimano_rods/TROUT ONE NS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/TROUT%20ONE%20NS_main.jpg</v>
       </c>
       <c r="I15" t="str">
         <v/>
@@ -963,7 +963,7 @@
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>images/shimano_rods/TROUT ONE AS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/TROUT%20ONE%20AS_main.jpg</v>
       </c>
       <c r="I16" t="str">
         <v/>
@@ -999,7 +999,7 @@
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>images/shimano_rods/WORLD SHAULA LIMITED_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/WORLD%20SHAULA%20LIMITED_main.jpg</v>
       </c>
       <c r="I17" t="str">
         <v/>
@@ -1039,7 +1039,7 @@
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>images/shimano_rods/BASS ONE XT+_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/BASS%20ONE%20XT%2B_main.jpg</v>
       </c>
       <c r="I18" t="str">
         <v/>
@@ -1075,7 +1075,7 @@
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>images/shimano_rods/LUREMATIC（BASS）_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/LUREMATIC%EF%BC%88BASS%EF%BC%89_main.jpg</v>
       </c>
       <c r="I19" t="str">
         <v/>
@@ -1113,7 +1113,7 @@
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>images/shimano_rods/LUREMATIC（TROUT）_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/LUREMATIC%EF%BC%88TROUT%EF%BC%89_main.jpg</v>
       </c>
       <c r="I20" t="str">
         <v/>
@@ -1151,7 +1151,7 @@
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>images/shimano_rods/Bantam_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/Bantam_main.jpg</v>
       </c>
       <c r="I21" t="str">
         <v/>
@@ -1187,7 +1187,7 @@
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>images/shimano_rods/WORLD SHAULA 衍生握把BG_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/WORLD%20SHAULA%20%E8%A1%8D%E7%94%9F%E6%8F%A1%E6%8A%8ABG_main.jpg</v>
       </c>
       <c r="I22" t="str">
         <v/>
@@ -1223,7 +1223,7 @@
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>images/shimano_rods/EXPRIDE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/EXPRIDE_main.jpg</v>
       </c>
       <c r="I23" t="str">
         <v/>
@@ -1259,7 +1259,7 @@
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>images/shimano_rods/CARDIFF AX_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/CARDIFF%20AX_main.jpg</v>
       </c>
       <c r="I24" t="str">
         <v/>
@@ -1295,7 +1295,7 @@
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>images/shimano_rods/ZODIAS PACK_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/ZODIAS%20PACK_main.jpg</v>
       </c>
       <c r="I25" t="str">
         <v/>
@@ -1331,7 +1331,7 @@
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>images/shimano_rods/Scorpion XV_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/Scorpion%20XV_main.jpg</v>
       </c>
       <c r="I26" t="str">
         <v/>
@@ -1367,7 +1367,7 @@
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>images/shimano_rods/POISON GLORIOUS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/POISON%20GLORIOUS%20XC_main.jpg</v>
       </c>
       <c r="I27" t="str">
         <v/>
@@ -1403,7 +1403,7 @@
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>images/shimano_rods/CARDIFF NX_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/CARDIFF%20NX_main.jpg</v>
       </c>
       <c r="I28" t="str">
         <v/>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>images/shimano_rods/WORLD SHAULA Dream Tour Edition_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/WORLD%20SHAULA%20Dream%20Tour%20Edition_main.jpg</v>
       </c>
       <c r="I29" t="str">
         <v/>
@@ -1474,7 +1474,7 @@
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>images/shimano_rods/ZODIAS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/ZODIAS_main.jpg</v>
       </c>
       <c r="I30" t="str">
         <v/>
@@ -1510,7 +1510,7 @@
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>images/shimano_rods/CARDIFF MONSTER LIMITED_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/CARDIFF%20MONSTER%20LIMITED_main.jpg</v>
       </c>
       <c r="I31" t="str">
         <v/>
@@ -1546,7 +1546,7 @@
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>images/shimano_rods/梦屋 X SEAT EXTREAM握把_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/%E6%A2%A6%E5%B1%8B%20X%20SEAT%20EXTREAM%E6%8F%A1%E6%8A%8A_main.jpg</v>
       </c>
       <c r="I32" t="str">
         <v/>
@@ -1582,7 +1582,7 @@
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>images/shimano_rods/CARDIFF NATIVE SPECIAL_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/CARDIFF%20NATIVE%20SPECIAL_main.jpg</v>
       </c>
       <c r="I33" t="str">
         <v/>
@@ -1618,7 +1618,7 @@
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>images/shimano_rods/TROUT RISE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/TROUT%20RISE_main.jpg</v>
       </c>
       <c r="I34" t="str">
         <v/>
@@ -1654,7 +1654,7 @@
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>images/shimano_rods/POISON GLORIOUS XC_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/POISON%20GLORIOUS%20XC_main.jpg</v>
       </c>
       <c r="I35" t="str">
         <v/>
@@ -1690,7 +1690,7 @@
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>images/shimano_rods/Scorpion_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/Scorpion_main.jpg</v>
       </c>
       <c r="I36" t="str">
         <v/>
@@ -1726,7 +1726,7 @@
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>images/shimano_rods/CONQUEST_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/CONQUEST_main.jpg</v>
       </c>
       <c r="I37" t="str">
         <v/>
@@ -1762,7 +1762,7 @@
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>images/shimano_rods/WORLD SHAULA_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/WORLD%20SHAULA%20BG_main.jpg</v>
       </c>
       <c r="I38" t="str">
         <v/>
@@ -1799,7 +1799,7 @@
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>images/shimano_rods/WORLD SHAULA 衍生握把_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/WORLD%20SHAULA%20%E8%A1%8D%E7%94%9F%E6%8F%A1%E6%8A%8ABG_main.jpg</v>
       </c>
       <c r="I39" t="str">
         <v/>
@@ -1834,7 +1834,7 @@
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>images/shimano_rods/梦屋 X SEAT 握把_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/%E6%A2%A6%E5%B1%8B%20X%20SEAT%20%E6%8F%A1%E6%8A%8A_main.jpg</v>
       </c>
       <c r="I40" t="str">
         <v/>
@@ -1869,7 +1869,7 @@
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>images/shimano_rods/Asquith_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/Asquith_main.jpg</v>
       </c>
       <c r="I41" t="str">
         <v/>
@@ -1905,7 +1905,7 @@
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>images/shimano_rods/BROOKSTONE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/BROOKSTONE_main.jpg</v>
       </c>
       <c r="I42" t="str">
         <v/>
@@ -1941,7 +1941,7 @@
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>images/shimano_rods/POISON ULTIMA PACK_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/POISON%20ULTIMA%20PACK_main.jpg</v>
       </c>
       <c r="I43" t="str">
         <v/>
@@ -1977,7 +1977,7 @@
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>images/shimano_rods/CARDIFF AREA LIMITED_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/CARDIFF%20AREA%20LIMITED_main.jpg</v>
       </c>
       <c r="I44" t="str">
         <v/>
@@ -2013,7 +2013,7 @@
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>images/shimano_rods/CARDIFF STREAM LIMITED_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/CARDIFF%20STREAM%20LIMITED_main.jpg</v>
       </c>
       <c r="I45" t="str">
         <v/>
@@ -2048,7 +2048,7 @@
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>images/shimano_rods/ARGUS HUNTER SPECIAL_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/ARGUS%20HUNTER%20SPECIAL_main.jpg</v>
       </c>
       <c r="I46" t="str">
         <v/>
@@ -2084,7 +2084,7 @@
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>images/shimano_rods/Majestic XT_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/Majestic%20XT_main.jpg</v>
       </c>
       <c r="I47" t="str">
         <v/>
@@ -2120,7 +2120,7 @@
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>images/shimano_rods/Majestic_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/Majestic_main.jpg</v>
       </c>
       <c r="I48" t="str">
         <v/>
@@ -2156,7 +2156,7 @@
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>images/shimano_rods/Soare SS BOAT_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/Soare%20SS%20BOAT_main.jpg</v>
       </c>
       <c r="I49" t="str">
         <v/>
@@ -2192,7 +2192,7 @@
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>images/shimano_rods/Soare BB_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/Soare%20BB%20AJING_main.jpg</v>
       </c>
       <c r="I50" t="str">
         <v/>
@@ -2228,7 +2228,7 @@
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>images/shimano_rods/Soare BB AJING_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/Soare%20BB%20AJING_main.jpg</v>
       </c>
       <c r="I51" t="str">
         <v/>
@@ -2264,7 +2264,7 @@
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>images/shimano_rods/Soare SS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/Soare%20SS%20AJING_main.jpg</v>
       </c>
       <c r="I52" t="str">
         <v/>
@@ -2300,7 +2300,7 @@
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>images/shimano_rods/Soare SS AJING_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/Soare%20SS%20AJING_main.jpg</v>
       </c>
       <c r="I53" t="str">
         <v/>
@@ -2336,7 +2336,7 @@
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>images/shimano_rods/Soare XTUNE MB_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/Soare%20XTUNE%20MB_main.jpg</v>
       </c>
       <c r="I54" t="str">
         <v/>
@@ -2372,7 +2372,7 @@
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>images/shimano_rods/Soare XR_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/Soare%20XR_main.jpg</v>
       </c>
       <c r="I55" t="str">
         <v/>
@@ -2408,7 +2408,7 @@
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>images/shimano_rods/Soare TT_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/Soare%20TT%20AJING_main.jpg</v>
       </c>
       <c r="I56" t="str">
         <v/>
@@ -2444,7 +2444,7 @@
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>images/shimano_rods/Soare TT AJING_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/Soare%20TT%20AJING_main.jpg</v>
       </c>
       <c r="I57" t="str">
         <v/>
@@ -2480,7 +2480,7 @@
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>images/shimano_rods/Soare LIMITED_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/Soare%20LIMITED_main.jpg</v>
       </c>
       <c r="I58" t="str">
         <v/>
@@ -2516,7 +2516,7 @@
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>images/shimano_rods/Soare XTUNE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/Soare%20XTUNE%20MB_main.jpg</v>
       </c>
       <c r="I59" t="str">
         <v/>
@@ -2552,7 +2552,7 @@
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>images/shimano_rods/COLTSNIPER XTUNE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/COLTSNIPER%20XTUNE_main.jpg</v>
       </c>
       <c r="I60" t="str">
         <v/>
@@ -2588,7 +2588,7 @@
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>images/shimano_rods/EXSENCE GENOS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/EXSENCE%20GENOS%20(%E6%9E%AA%E6%9F%84)_main.jpg</v>
       </c>
       <c r="I61" t="str">
         <v/>
@@ -2624,7 +2624,7 @@
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>images/shimano_rods/SALTY ADVANCE 船钓规格_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/SALTY%20ADVANCE%20%E8%88%B9%E9%92%93%E8%A7%84%E6%A0%BC_main.jpg</v>
       </c>
       <c r="I62" t="str">
         <v/>
@@ -2660,7 +2660,7 @@
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>images/shimano_rods/SALTY ADVANCE 岸钓规格_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/SALTY%20ADVANCE%20%E5%B2%B8%E9%92%93%E8%A7%84%E6%A0%BC_main.jpg</v>
       </c>
       <c r="I63" t="str">
         <v/>
@@ -2696,7 +2696,7 @@
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>images/shimano_rods/SEPHIA LIMITED METAL SUTTE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/SEPHIA%20LIMITED%20METAL%20SUTTE_main.jpg</v>
       </c>
       <c r="I64" t="str">
         <v/>
@@ -2732,7 +2732,7 @@
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>images/shimano_rods/SEPHIA LIMITED_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/SEPHIA%20LIMITED%20METAL%20SUTTE_main.jpg</v>
       </c>
       <c r="I65" t="str">
         <v/>
@@ -2768,7 +2768,7 @@
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>images/shimano_rods/GRAPPLER TYPE C_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/GRAPPLER%20TYPE%20C%203%E8%8A%82_main.jpg</v>
       </c>
       <c r="I66" t="str">
         <v/>
@@ -2804,7 +2804,7 @@
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>images/shimano_rods/GRAPPLER TYPE J_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/GRAPPLER%20TYPE%20J%203%E8%8A%82_main.jpg</v>
       </c>
       <c r="I67" t="str">
         <v/>
@@ -2840,7 +2840,7 @@
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>images/shimano_rods/OCEA PLUGGER BG_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/OCEA%20PLUGGER%20BG_main.jpg</v>
       </c>
       <c r="I68" t="str">
         <v/>
@@ -2876,7 +2876,7 @@
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>images/shimano_rods/LUNAMIS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/LUNAMIS_main.jpg</v>
       </c>
       <c r="I69" t="str">
         <v/>
@@ -2912,7 +2912,7 @@
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>images/shimano_rods/GRAPPLER TYPE J FULLBEND_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/GRAPPLER%20TYPE%20J%20FULLBEND_main.jpg</v>
       </c>
       <c r="I70" t="str">
         <v/>
@@ -2948,7 +2948,7 @@
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>images/shimano_rods/CROSSMISSION SS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/CROSSMISSION%20SS_main.jpg</v>
       </c>
       <c r="I71" t="str">
         <v/>
@@ -2984,7 +2984,7 @@
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>images/shimano_rods/BRENIOUS BB_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/BRENIOUS%20BB_main.jpg</v>
       </c>
       <c r="I72" t="str">
         <v/>
@@ -3020,7 +3020,7 @@
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>images/shimano_rods/SEPHIA LIMITED TIP EGING_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/SEPHIA%20LIMITED%20TIP%20EGING_main.jpg</v>
       </c>
       <c r="I73" t="str">
         <v/>
@@ -3056,7 +3056,7 @@
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>images/shimano_rods/HARD ROCKER XTUNE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/HARD%20ROCKER%20XTUNE_main.jpg</v>
       </c>
       <c r="I74" t="str">
         <v/>
@@ -3092,7 +3092,7 @@
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>images/shimano_rods/NESSA XTUNE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/NESSA%20XTUNE_main.jpg</v>
       </c>
       <c r="I75" t="str">
         <v/>
@@ -3128,7 +3128,7 @@
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>images/shimano_rods/OCEA JIGGER CONCEPT S_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/OCEA%20JIGGER%20CONCEPT%20S_main.jpg</v>
       </c>
       <c r="I76" t="str">
         <v/>
@@ -3164,7 +3164,7 @@
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>images/shimano_rods/COLTSNIPER SS LONG_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/COLTSNIPER%20SS%20LONG_main.jpg</v>
       </c>
       <c r="I77" t="str">
         <v/>
@@ -3200,7 +3200,7 @@
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>images/shimano_rods/DIALUNA ZOOM_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/DIALUNA%20ZOOM_main.jpg</v>
       </c>
       <c r="I78" t="str">
         <v/>
@@ -3236,7 +3236,7 @@
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>images/shimano_rods/GRAPPLER BB TYPE BLADE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/GRAPPLER%20BB%20TYPE%20BLADE_main.jpg</v>
       </c>
       <c r="I79" t="str">
         <v/>
@@ -3272,7 +3272,7 @@
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>images/shimano_rods/OCEA PLUGGER LIMITED_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/OCEA%20PLUGGER%20LIMITED_main.jpg</v>
       </c>
       <c r="I80" t="str">
         <v/>
@@ -3308,7 +3308,7 @@
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>images/shimano_rods/BRENIOUS XR_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/BRENIOUS%20XR_main.jpg</v>
       </c>
       <c r="I81" t="str">
         <v/>
@@ -3344,7 +3344,7 @@
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>images/shimano_rods/GRAPPLER TYPE SLOW J_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/GRAPPLER%20TYPE%20SLOW%20J_main.jpg</v>
       </c>
       <c r="I82" t="str">
         <v/>
@@ -3380,7 +3380,7 @@
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>images/shimano_rods/GRAPPLER TYPE LJ_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/GRAPPLER%20TYPE%20LJ_main.jpg</v>
       </c>
       <c r="I83" t="str">
         <v/>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>images/shimano_rods/GRAPPLER TYPE SLJ_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/GRAPPLER%20TYPE%20SLJ_main.jpg</v>
       </c>
       <c r="I84" t="str">
         <v/>
@@ -3451,7 +3451,7 @@
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>images/shimano_rods/OCEA EJ_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/OCEA%20EJ_main.jpg</v>
       </c>
       <c r="I85" t="str">
         <v/>
@@ -3487,7 +3487,7 @@
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>images/shimano_rods/INSTAGE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/INSTAGE_main.jpg</v>
       </c>
       <c r="I86" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>images/shimano_rods/OCEA JIGGER SLJ_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/OCEA%20JIGGER%20SLJ_main.jpg</v>
       </c>
       <c r="I87" t="str">
         <v/>
@@ -3563,7 +3563,7 @@
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>images/shimano_rods/OCEA PLUGGER LIGHT CONCEPT_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/OCEA%20PLUGGER%20LIGHT%20CONCEPT_main.jpg</v>
       </c>
       <c r="I88" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>images/shimano_rods/Sephia SS METAL SUTTE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/Sephia%20SS%20METAL%20SUTTE_main.jpg</v>
       </c>
       <c r="I89" t="str">
         <v/>
@@ -3635,7 +3635,7 @@
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>images/shimano_rods/HARD ROCKER BB_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/HARD%20ROCKER%20BB_main.jpg</v>
       </c>
       <c r="I90" t="str">
         <v/>
@@ -3671,7 +3671,7 @@
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>images/shimano_rods/OCEA JIGGER LJ_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/OCEA%20JIGGER%20LJ_main.jpg</v>
       </c>
       <c r="I91" t="str">
         <v/>
@@ -3711,7 +3711,7 @@
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>images/shimano_rods/COLTSNIPER SS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/COLTSNIPER%20SS%20LONG_main.jpg</v>
       </c>
       <c r="I92" t="str">
         <v/>
@@ -3747,7 +3747,7 @@
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>images/shimano_rods/ENCOUNTER_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/ENCOUNTER_main.jpg</v>
       </c>
       <c r="I93" t="str">
         <v/>
@@ -3783,7 +3783,7 @@
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>images/shimano_rods/OCEA JIGGER QUICKJERK_NATURALJERK_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/OCEA%20JIGGER%20QUICKJERK_NATURALJERK_main.jpg</v>
       </c>
       <c r="I94" t="str">
         <v/>
@@ -3819,7 +3819,7 @@
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>images/shimano_rods/NESSA LIMITED_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/NESSA%20LIMITED_main.jpg</v>
       </c>
       <c r="I95" t="str">
         <v/>
@@ -3855,7 +3855,7 @@
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>images/shimano_rods/DYNA DART XR_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/DYNA%20DART%20XR_main.jpg</v>
       </c>
       <c r="I96" t="str">
         <v/>
@@ -3891,7 +3891,7 @@
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>images/shimano_rods/Sephia SS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/Sephia%20SS%20METAL%20SUTTE_main.jpg</v>
       </c>
       <c r="I97" t="str">
         <v/>
@@ -3927,7 +3927,7 @@
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>images/shimano_rods/Sephia BB TIP EGING_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/Sephia%20BB%20TIP%20EGING_main.jpg</v>
       </c>
       <c r="I98" t="str">
         <v/>
@@ -3963,7 +3963,7 @@
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>images/shimano_rods/COLTSNIPER BB LSJ_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/COLTSNIPER%20BB%20LSJ_main.jpg</v>
       </c>
       <c r="I99" t="str">
         <v/>
@@ -4000,7 +4000,7 @@
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>images/shimano_rods/OCEA JIGGER LIMITED (直柄)_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/OCEA%20JIGGER%20LIMITED%20(%E7%9B%B4%E6%9F%84)_main.jpg</v>
       </c>
       <c r="I100" t="str">
         <v/>
@@ -4036,7 +4036,7 @@
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>images/shimano_rods/OCEA JIGGER (枪柄）_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/OCEA%20JIGGER%20(%E6%9E%AA%E6%9F%84%EF%BC%89_main.jpg</v>
       </c>
       <c r="I101" t="str">
         <v/>
@@ -4071,7 +4071,7 @@
         <v/>
       </c>
       <c r="H102" t="str">
-        <v>images/shimano_rods/MOONSHOT BS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/MOONSHOT%20BS_main.jpg</v>
       </c>
       <c r="I102" t="str">
         <v/>
@@ -4107,7 +4107,7 @@
         <v/>
       </c>
       <c r="H103" t="str">
-        <v>images/shimano_rods/Sephia BB METAL SUTTE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/Sephia%20BB%20METAL%20SUTTE_main.jpg</v>
       </c>
       <c r="I103" t="str">
         <v/>
@@ -4145,7 +4145,7 @@
         <v/>
       </c>
       <c r="H104" t="str">
-        <v>images/shimano_rods/FREEGAME_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/FREEGAME_main.jpg</v>
       </c>
       <c r="I104" t="str">
         <v/>
@@ -4181,7 +4181,7 @@
         <v/>
       </c>
       <c r="H105" t="str">
-        <v>images/shimano_rods/LUREMATIC (SALT)_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/LUREMATIC%20(SALT)_main.jpg</v>
       </c>
       <c r="I105" t="str">
         <v/>
@@ -4219,7 +4219,7 @@
         <v/>
       </c>
       <c r="H106" t="str">
-        <v>images/shimano_rods/DIALUNA_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/DIALUNA_main.jpg</v>
       </c>
       <c r="I106" t="str">
         <v/>
@@ -4255,7 +4255,7 @@
         <v/>
       </c>
       <c r="H107" t="str">
-        <v>images/shimano_rods/OCEA JIGGER LIMITED LJ_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/OCEA%20JIGGER%20LIMITED%20LJ_main.jpg</v>
       </c>
       <c r="I107" t="str">
         <v/>
@@ -4290,7 +4290,7 @@
         <v/>
       </c>
       <c r="H108" t="str">
-        <v>images/shimano_rods/OCEA JIGGER LIMITED SLJ_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/OCEA%20JIGGER%20LIMITED%20SLJ_main.jpg</v>
       </c>
       <c r="I108" t="str">
         <v/>
@@ -4326,7 +4326,7 @@
         <v/>
       </c>
       <c r="H109" t="str">
-        <v>images/shimano_rods/COLTSNIPER LIMITED_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/COLTSNIPER%20LIMITED%20BIG%20GAME_main.jpg</v>
       </c>
       <c r="I109" t="str">
         <v/>
@@ -4362,7 +4362,7 @@
         <v/>
       </c>
       <c r="H110" t="str">
-        <v>images/shimano_rods/EXSENCE INFINITY_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/EXSENCE%20INFINITY_main.jpg</v>
       </c>
       <c r="I110" t="str">
         <v/>
@@ -4398,7 +4398,7 @@
         <v/>
       </c>
       <c r="H111" t="str">
-        <v>images/shimano_rods/COLTSNIPER LIMITED LANDING SHAFT_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/COLTSNIPER%20LIMITED%20LANDING%20SHAFT_main.jpg</v>
       </c>
       <c r="I111" t="str">
         <v/>
@@ -4434,7 +4434,7 @@
         <v/>
       </c>
       <c r="H112" t="str">
-        <v>images/shimano_rods/OCEA JIGGER FULLBEND_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/OCEA%20JIGGER%20FULLBEND_main.jpg</v>
       </c>
       <c r="I112" t="str">
         <v/>
@@ -4470,7 +4470,7 @@
         <v/>
       </c>
       <c r="H113" t="str">
-        <v>images/shimano_rods/EXSENCE ZOOM_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/EXSENCE%20ZOOM_main.jpg</v>
       </c>
       <c r="I113" t="str">
         <v/>
@@ -4506,7 +4506,7 @@
         <v/>
       </c>
       <c r="H114" t="str">
-        <v>images/shimano_rods/Sephia XR TIP EGING_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/Sephia%20XR%20TIP%20EGING_main.jpg</v>
       </c>
       <c r="I114" t="str">
         <v/>
@@ -4542,7 +4542,7 @@
         <v/>
       </c>
       <c r="H115" t="str">
-        <v>images/shimano_rods/NESSA BB_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/NESSA%20BB_main.jpg</v>
       </c>
       <c r="I115" t="str">
         <v/>
@@ -4579,7 +4579,7 @@
         <v/>
       </c>
       <c r="H116" t="str">
-        <v>images/shimano_rods/Sephia BB_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/Sephia%20BB%20METAL%20SUTTE_main.jpg</v>
       </c>
       <c r="I116" t="str">
         <v/>
@@ -4615,7 +4615,7 @@
         <v/>
       </c>
       <c r="H117" t="str">
-        <v>images/shimano_rods/DYNA DART_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/DYNA%20DART%20XR_main.jpg</v>
       </c>
       <c r="I117" t="str">
         <v/>
@@ -4650,7 +4650,7 @@
         <v/>
       </c>
       <c r="H118" t="str">
-        <v>images/shimano_rods/COLTSNIPER SS LSJ_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/COLTSNIPER%20SS%20LSJ_main.jpg</v>
       </c>
       <c r="I118" t="str">
         <v/>
@@ -4686,7 +4686,7 @@
         <v/>
       </c>
       <c r="H119" t="str">
-        <v>images/shimano_rods/CROSSMISSION XR_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/CROSSMISSION%20XR_main.jpg</v>
       </c>
       <c r="I119" t="str">
         <v/>
@@ -4722,7 +4722,7 @@
         <v/>
       </c>
       <c r="H120" t="str">
-        <v>images/shimano_rods/OCEA PLUGGER FLEXDRIVE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/OCEA%20PLUGGER%20FLEXDRIVE_main.jpg</v>
       </c>
       <c r="I120" t="str">
         <v/>
@@ -4758,7 +4758,7 @@
         <v/>
       </c>
       <c r="H121" t="str">
-        <v>images/shimano_rods/COLTSNIPER XR MB_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/COLTSNIPER%20XR%20MB_main.jpg</v>
       </c>
       <c r="I121" t="str">
         <v/>
@@ -4794,7 +4794,7 @@
         <v/>
       </c>
       <c r="H122" t="str">
-        <v>images/shimano_rods/Sephia XR METAL SUTTE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/Sephia%20XR%20METAL%20SUTTE_main.jpg</v>
       </c>
       <c r="I122" t="str">
         <v/>
@@ -4829,7 +4829,7 @@
         <v/>
       </c>
       <c r="H123" t="str">
-        <v>images/shimano_rods/HARD ROCKER SS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/HARD%20ROCKER%20SS_main.jpg</v>
       </c>
       <c r="I123" t="str">
         <v/>
@@ -4865,7 +4865,7 @@
         <v/>
       </c>
       <c r="H124" t="str">
-        <v>images/shimano_rods/COLTSNIPER BB 振出_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/COLTSNIPER%20BB%20%E6%8C%AF%E5%87%BA_main.jpg</v>
       </c>
       <c r="I124" t="str">
         <v/>
@@ -4901,7 +4901,7 @@
         <v/>
       </c>
       <c r="H125" t="str">
-        <v>images/shimano_rods/MULTI LANDING SHAFT_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/MULTI%20LANDING%20SHAFT_main.jpg</v>
       </c>
       <c r="I125" t="str">
         <v/>
@@ -4936,7 +4936,7 @@
         <v/>
       </c>
       <c r="H126" t="str">
-        <v>images/shimano_rods/OCEA JIGGER LIMITED (枪柄)_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/OCEA%20JIGGER%20LIMITED%20(%E6%9E%AA%E6%9F%84)_main.jpg</v>
       </c>
       <c r="I126" t="str">
         <v/>
@@ -4974,7 +4974,7 @@
         <v/>
       </c>
       <c r="H127" t="str">
-        <v>images/shimano_rods/GAME TYPE EJ_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/GAME%20TYPE%20EJ_main.jpg</v>
       </c>
       <c r="I127" t="str">
         <v/>
@@ -5010,7 +5010,7 @@
         <v/>
       </c>
       <c r="H128" t="str">
-        <v>images/shimano_rods/NESSA XR_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/NESSA%20XR_main.jpg</v>
       </c>
       <c r="I128" t="str">
         <v/>
@@ -5046,7 +5046,7 @@
         <v/>
       </c>
       <c r="H129" t="str">
-        <v>images/shimano_rods/GRAPPLER TYPE C（枪柄）_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/GRAPPLER%20TYPE%20C%EF%BC%88%E6%9E%AA%E6%9F%84%EF%BC%89_main.jpg</v>
       </c>
       <c r="I129" t="str">
         <v/>
@@ -5082,7 +5082,7 @@
         <v/>
       </c>
       <c r="H130" t="str">
-        <v>images/shimano_rods/GRAPPLER BB TYPE C_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/GRAPPLER%20BB%20TYPE%20C_main.jpg</v>
       </c>
       <c r="I130" t="str">
         <v/>
@@ -5118,7 +5118,7 @@
         <v/>
       </c>
       <c r="H131" t="str">
-        <v>images/shimano_rods/Sephia XTUNE MB_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/Sephia%20XTUNE%20MB_main.jpg</v>
       </c>
       <c r="I131" t="str">
         <v/>
@@ -5154,7 +5154,7 @@
         <v/>
       </c>
       <c r="H132" t="str">
-        <v>images/shimano_rods/Sephia XR_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/Sephia%20XR%20METAL%20SUTTE_main.jpg</v>
       </c>
       <c r="I132" t="str">
         <v/>
@@ -5190,7 +5190,7 @@
         <v/>
       </c>
       <c r="H133" t="str">
-        <v>images/shimano_rods/GAME TYPE LJ_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/GAME%20TYPE%20LJ_main.jpg</v>
       </c>
       <c r="I133" t="str">
         <v/>
@@ -5226,7 +5226,7 @@
         <v/>
       </c>
       <c r="H134" t="str">
-        <v>images/shimano_rods/DIALUNA BS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/DIALUNA%20BS_main.jpg</v>
       </c>
       <c r="I134" t="str">
         <v/>
@@ -5262,7 +5262,7 @@
         <v/>
       </c>
       <c r="H135" t="str">
-        <v>images/shimano_rods/CROSSMISSION BB_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/CROSSMISSION%20BB_main.jpg</v>
       </c>
       <c r="I135" t="str">
         <v/>
@@ -5298,7 +5298,7 @@
         <v/>
       </c>
       <c r="H136" t="str">
-        <v>images/shimano_rods/OCEA PLUGGER LIMITED_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/OCEA%20PLUGGER%20LIMITED_main.jpg</v>
       </c>
       <c r="I136" t="str">
         <v/>
@@ -5334,7 +5334,7 @@
         <v/>
       </c>
       <c r="H137" t="str">
-        <v>images/shimano_rods/GRAPPLER TYPE J 3节_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/GRAPPLER%20TYPE%20J%203%E8%8A%82_main.jpg</v>
       </c>
       <c r="I137" t="str">
         <v/>
@@ -5370,7 +5370,7 @@
         <v/>
       </c>
       <c r="H138" t="str">
-        <v>images/shimano_rods/COLTSNIPER BB_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/COLTSNIPER%20BB%20LSJ_main.jpg</v>
       </c>
       <c r="I138" t="str">
         <v/>
@@ -5406,7 +5406,7 @@
         <v/>
       </c>
       <c r="H139" t="str">
-        <v>images/shimano_rods/MOONSHOT_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/MOONSHOT_main.jpg</v>
       </c>
       <c r="I139" t="str">
         <v/>
@@ -5442,7 +5442,7 @@
         <v/>
       </c>
       <c r="H140" t="str">
-        <v>images/shimano_rods/GRAPPLER TYPE C 3节_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/GRAPPLER%20TYPE%20C%203%E8%8A%82_main.jpg</v>
       </c>
       <c r="I140" t="str">
         <v/>
@@ -5478,7 +5478,7 @@
         <v/>
       </c>
       <c r="H141" t="str">
-        <v>images/shimano_rods/GRAPPLER BB TYPE J_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/GRAPPLER%20BB%20TYPE%20J_main.jpg</v>
       </c>
       <c r="I141" t="str">
         <v/>
@@ -5514,7 +5514,7 @@
         <v/>
       </c>
       <c r="H142" t="str">
-        <v>images/shimano_rods/GRAPPLER BB TYPE SLOW J_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/GRAPPLER%20BB%20TYPE%20SLOW%20J_main.jpg</v>
       </c>
       <c r="I142" t="str">
         <v/>
@@ -5550,7 +5550,7 @@
         <v/>
       </c>
       <c r="H143" t="str">
-        <v>images/shimano_rods/GRAPPLER BB TYPE LJ_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/GRAPPLER%20BB%20TYPE%20LJ_main.jpg</v>
       </c>
       <c r="I143" t="str">
         <v/>
@@ -5586,7 +5586,7 @@
         <v/>
       </c>
       <c r="H144" t="str">
-        <v>images/shimano_rods/NESSA XTUNE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/NESSA%20XTUNE_main.jpg</v>
       </c>
       <c r="I144" t="str">
         <v/>
@@ -5622,7 +5622,7 @@
         <v/>
       </c>
       <c r="H145" t="str">
-        <v>images/shimano_rods/EXSENCE MB_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/EXSENCE%20MB_main.jpg</v>
       </c>
       <c r="I145" t="str">
         <v/>
@@ -5658,7 +5658,7 @@
         <v/>
       </c>
       <c r="H146" t="str">
-        <v>images/shimano_rods/WORLD SHAULA BG_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/WORLD%20SHAULA%20BG_main.jpg</v>
       </c>
       <c r="I146" t="str">
         <v/>
@@ -5694,7 +5694,7 @@
         <v/>
       </c>
       <c r="H147" t="str">
-        <v>images/shimano_rods/LANDING SHAFT G FREE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/LANDING%20SHAFT%20G%20FREE_main.jpg</v>
       </c>
       <c r="I147" t="str">
         <v/>
@@ -5730,7 +5730,7 @@
         <v/>
       </c>
       <c r="H148" t="str">
-        <v>images/shimano_rods/GAME TYPE J_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/GAME%20TYPE%20J%20FULLBEND_main.jpg</v>
       </c>
       <c r="I148" t="str">
         <v/>
@@ -5765,7 +5765,7 @@
         <v/>
       </c>
       <c r="H149" t="str">
-        <v>images/shimano_rods/GAME TYPE SLOW J_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/GAME%20TYPE%20SLOW%20J_main.jpg</v>
       </c>
       <c r="I149" t="str">
         <v/>
@@ -5801,7 +5801,7 @@
         <v/>
       </c>
       <c r="H150" t="str">
-        <v>images/shimano_rods/Sephia TT_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/Sephia%20TT_main.jpg</v>
       </c>
       <c r="I150" t="str">
         <v/>
@@ -5836,7 +5836,7 @@
         <v/>
       </c>
       <c r="H151" t="str">
-        <v>images/shimano_rods/LUREMATIC MB_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/LUREMATIC%20MB_main.jpg</v>
       </c>
       <c r="I151" t="str">
         <v/>
@@ -5873,7 +5873,7 @@
         <v/>
       </c>
       <c r="H152" t="str">
-        <v>images/shimano_rods/HARD ROCKER XR_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/HARD%20ROCKER%20XR_main.jpg</v>
       </c>
       <c r="I152" t="str">
         <v/>
@@ -5909,7 +5909,7 @@
         <v/>
       </c>
       <c r="H153" t="str">
-        <v>images/shimano_rods/Brenious BB_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/BRENIOUS%20BB_main.jpg</v>
       </c>
       <c r="I153" t="str">
         <v/>
@@ -5945,7 +5945,7 @@
         <v/>
       </c>
       <c r="H154" t="str">
-        <v>images/shimano_rods/OCEA PLUGGER BG_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/OCEA%20PLUGGER%20BG_main.jpg</v>
       </c>
       <c r="I154" t="str">
         <v/>
@@ -5981,7 +5981,7 @@
         <v/>
       </c>
       <c r="H155" t="str">
-        <v>images/shimano_rods/CROSSMISSION_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/CROSSMISSION_main.jpg</v>
       </c>
       <c r="I155" t="str">
         <v/>
@@ -6017,7 +6017,7 @@
         <v/>
       </c>
       <c r="H156" t="str">
-        <v>images/shimano_rods/COLTSNIPER XR_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/COLTSNIPER%20XR%20MB_main.jpg</v>
       </c>
       <c r="I156" t="str">
         <v/>
@@ -6052,7 +6052,7 @@
         <v/>
       </c>
       <c r="H157" t="str">
-        <v>images/shimano_rods/LUNAMIS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/LUNAMIS_main.jpg</v>
       </c>
       <c r="I157" t="str">
         <v/>
@@ -6088,7 +6088,7 @@
         <v/>
       </c>
       <c r="H158" t="str">
-        <v>images/shimano_rods/OCEA JIGGER INFINITY_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/OCEA%20JIGGER%20INFINITY%20MOTIVE_main.jpg</v>
       </c>
       <c r="I158" t="str">
         <v/>
@@ -6125,7 +6125,7 @@
         <v/>
       </c>
       <c r="H159" t="str">
-        <v>images/shimano_rods/Brenious_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/Brenious_main.jpg</v>
       </c>
       <c r="I159" t="str">
         <v/>
@@ -6161,7 +6161,7 @@
         <v/>
       </c>
       <c r="H160" t="str">
-        <v>images/shimano_rods/COLTSNIPER XTUNE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/COLTSNIPER%20XTUNE_main.jpg</v>
       </c>
       <c r="I160" t="str">
         <v/>
@@ -6197,7 +6197,7 @@
         <v/>
       </c>
       <c r="H161" t="str">
-        <v>images/shimano_rods/OCEA JIGGER CONCEPT S_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/OCEA%20JIGGER%20CONCEPT%20S_main.jpg</v>
       </c>
       <c r="I161" t="str">
         <v/>
@@ -6233,7 +6233,7 @@
         <v/>
       </c>
       <c r="H162" t="str">
-        <v>images/shimano_rods/SALTY ADVANCE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/SALTY%20ADVANCE%20%E5%B2%B8%E9%92%93%E8%A7%84%E6%A0%BC_main.jpg</v>
       </c>
       <c r="I162" t="str">
         <v/>
@@ -6269,7 +6269,7 @@
         <v/>
       </c>
       <c r="H163" t="str">
-        <v>images/shimano_rods/GRAPPLER TYPE C_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/GRAPPLER%20TYPE%20C%203%E8%8A%82_main.jpg</v>
       </c>
       <c r="I163" t="str">
         <v/>
@@ -6305,7 +6305,7 @@
         <v/>
       </c>
       <c r="H164" t="str">
-        <v>images/shimano_rods/TRASTICK_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/TRASTICK_main.jpg</v>
       </c>
       <c r="I164" t="str">
         <v/>
@@ -6341,7 +6341,7 @@
         <v/>
       </c>
       <c r="H165" t="str">
-        <v>images/shimano_rods/Sephia LIMITED_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/SEPHIA%20LIMITED%20METAL%20SUTTE_main.jpg</v>
       </c>
       <c r="I165" t="str">
         <v/>
@@ -6377,7 +6377,7 @@
         <v/>
       </c>
       <c r="H166" t="str">
-        <v>images/shimano_rods/Sephia LIMITED METAL SUTTE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/SEPHIA%20LIMITED%20METAL%20SUTTE_main.jpg</v>
       </c>
       <c r="I166" t="str">
         <v/>
@@ -6413,7 +6413,7 @@
         <v/>
       </c>
       <c r="H167" t="str">
-        <v>images/shimano_rods/COLTSNIPER LIMITED BIG GAME_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/COLTSNIPER%20LIMITED%20BIG%20GAME_main.jpg</v>
       </c>
       <c r="I167" t="str">
         <v/>
@@ -6449,7 +6449,7 @@
         <v/>
       </c>
       <c r="H168" t="str">
-        <v>images/shimano_rods/EXSENCE GENOS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/EXSENCE%20GENOS%20(%E6%9E%AA%E6%9F%84)_main.jpg</v>
       </c>
       <c r="I168" t="str">
         <v/>
@@ -6485,7 +6485,7 @@
         <v/>
       </c>
       <c r="H169" t="str">
-        <v>images/shimano_rods/Sephia LIMITED TIP EGING_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/SEPHIA%20LIMITED%20TIP%20EGING_main.jpg</v>
       </c>
       <c r="I169" t="str">
         <v/>
@@ -6521,7 +6521,7 @@
         <v/>
       </c>
       <c r="H170" t="str">
-        <v>images/shimano_rods/EXSENCE GENOS (枪柄)_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/EXSENCE%20GENOS%20(%E6%9E%AA%E6%9F%84)_main.jpg</v>
       </c>
       <c r="I170" t="str">
         <v/>
@@ -6557,7 +6557,7 @@
         <v/>
       </c>
       <c r="H171" t="str">
-        <v>images/shimano_rods/OCEA PLUGGER FULL THROTTLE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/OCEA%20PLUGGER%20FULL%20THROTTLE_main.jpg</v>
       </c>
       <c r="I171" t="str">
         <v/>
@@ -6593,7 +6593,7 @@
         <v/>
       </c>
       <c r="H172" t="str">
-        <v>images/shimano_rods/OCEA JIGGER INFINITY MOTIVE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/OCEA%20JIGGER%20INFINITY%20MOTIVE_main.jpg</v>
       </c>
       <c r="I172" t="str">
         <v/>
@@ -6629,7 +6629,7 @@
         <v/>
       </c>
       <c r="H173" t="str">
-        <v>images/shimano_rods/Sephia XTUNE METAL SUTTE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/Sephia%20XTUNE%20METAL%20SUTTE_main.jpg</v>
       </c>
       <c r="I173" t="str">
         <v/>
@@ -6665,7 +6665,7 @@
         <v/>
       </c>
       <c r="H174" t="str">
-        <v>images/shimano_rods/Sephia XTUNE TIP EGING_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/Sephia%20XTUNE%20TIP%20EGING_main.jpg</v>
       </c>
       <c r="I174" t="str">
         <v/>
@@ -6702,7 +6702,7 @@
         <v/>
       </c>
       <c r="H175" t="str">
-        <v>images/shimano_rods/HARD ROCKER XTUNE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/HARD%20ROCKER%20XTUNE_main.jpg</v>
       </c>
       <c r="I175" t="str">
         <v/>
@@ -6738,7 +6738,7 @@
         <v/>
       </c>
       <c r="H176" t="str">
-        <v>images/shimano_rods/Sephia XTUNE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/Sephia%20XTUNE%20MB_main.jpg</v>
       </c>
       <c r="I176" t="str">
         <v/>
@@ -6774,7 +6774,7 @@
         <v/>
       </c>
       <c r="H177" t="str">
-        <v>images/shimano_rods/OCEA BLADE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/OCEA%20BLADE_main.jpg</v>
       </c>
       <c r="I177" t="str">
         <v/>
@@ -6810,7 +6810,7 @@
         <v/>
       </c>
       <c r="H178" t="str">
-        <v>images/shimano_rods/GAME TYPE J FULLBEND_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/GAME%20TYPE%20J%20FULLBEND_main.jpg</v>
       </c>
       <c r="I178" t="str">
         <v/>
@@ -6846,7 +6846,7 @@
         <v/>
       </c>
       <c r="H179" t="str">
-        <v>images/shimano_rods/Brenious XTUNE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/Brenious%20XTUNE_main.jpg</v>
       </c>
       <c r="I179" t="str">
         <v/>
@@ -6882,7 +6882,7 @@
         <v/>
       </c>
       <c r="H180" t="str">
-        <v>images/shimano_rods/NESSA SS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/NESSA%20SS_main.jpg</v>
       </c>
       <c r="I180" t="str">
         <v/>
@@ -6918,7 +6918,7 @@
         <v/>
       </c>
       <c r="H181" t="str">
-        <v>images/shimano_rods/DIALUNA (振出规格)_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/DIALUNA%20(%E6%8C%AF%E5%87%BA%E8%A7%84%E6%A0%BC)_main.jpg</v>
       </c>
       <c r="I181" t="str">
         <v/>
@@ -6954,7 +6954,7 @@
         <v/>
       </c>
       <c r="H182" t="str">
-        <v>images/shimano_rods/Sephia SS TIP EGING_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/Sephia%20SS%20TIP%20EGING_main.jpg</v>
       </c>
       <c r="I182" t="str">
         <v/>
@@ -6990,7 +6990,7 @@
         <v/>
       </c>
       <c r="H183" t="str">
-        <v>images/shimano_rods/GRAPPLER TYPE BLADE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/GRAPPLER%20TYPE%20BLADE_main.jpg</v>
       </c>
       <c r="I183" t="str">
         <v/>
@@ -7026,7 +7026,7 @@
         <v/>
       </c>
       <c r="H184" t="str">
-        <v>images/megabass_rods/ASL7117X_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_rods/ASL7117X_main.jpg</v>
       </c>
       <c r="I184" t="str">
         <v/>
@@ -7061,7 +7061,7 @@
         <v/>
       </c>
       <c r="H185" t="str">
-        <v>images/megabass_rods/TS79X_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_rods/TS79X_main.jpg</v>
       </c>
       <c r="I185" t="str">
         <v/>
@@ -7096,7 +7096,7 @@
         <v/>
       </c>
       <c r="H186" t="str">
-        <v>images/megabass_rods/F7-72XTZ_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_rods/F7-72XTZ_main.jpg</v>
       </c>
       <c r="I186" t="str">
         <v/>
@@ -7131,7 +7131,7 @@
         <v/>
       </c>
       <c r="H187" t="str">
-        <v>images/megabass_rods/F1-60XP_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_rods/F1-60XP_main.jpg</v>
       </c>
       <c r="I187" t="str">
         <v/>
@@ -7166,7 +7166,7 @@
         <v/>
       </c>
       <c r="H188" t="str">
-        <v>images/megabass_rods/ASL6401XS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_rods/ASL6401XS_main.jpg</v>
       </c>
       <c r="I188" t="str">
         <v/>
@@ -7201,7 +7201,7 @@
         <v/>
       </c>
       <c r="H189" t="str">
-        <v>images/megabass_rods/F0.1_2st-62XTS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_rods/F0.1_2st-62XTS_main.jpg</v>
       </c>
       <c r="I189" t="str">
         <v/>
@@ -7236,7 +7236,7 @@
         <v/>
       </c>
       <c r="H190" t="str">
-        <v>images/megabass_rods/F5.1_2-68ti_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_rods/F5.1_2-68ti_main.jpg</v>
       </c>
       <c r="I190" t="str">
         <v/>
@@ -7271,7 +7271,7 @@
         <v/>
       </c>
       <c r="H191" t="str">
-        <v>images/megabass_rods/GH93-2MS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_rods/GH93-2MS_main.jpg</v>
       </c>
       <c r="I191" t="str">
         <v/>
@@ -7306,7 +7306,7 @@
         <v/>
       </c>
       <c r="H192" t="str">
-        <v>images/megabass_rods/GHBF511-4L_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_rods/GHBF511-4L_main.jpg</v>
       </c>
       <c r="I192" t="str">
         <v/>
@@ -7341,7 +7341,7 @@
         <v/>
       </c>
       <c r="H193" t="str">
-        <v>images/megabass_rods/F4.1_2-71X_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_rods/F4.1_2-71X_main.jpg</v>
       </c>
       <c r="I193" t="str">
         <v/>
@@ -7376,7 +7376,7 @@
         <v/>
       </c>
       <c r="H194" t="str">
-        <v>images/megabass_rods/F9-711LV_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_rods/F9-711LV_main.jpg</v>
       </c>
       <c r="I194" t="str">
         <v/>
@@ -7411,7 +7411,7 @@
         <v/>
       </c>
       <c r="H195" t="str">
-        <v>images/megabass_rods/VKC-711XH-4_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_rods/VKC-711XH-4_main.jpg</v>
       </c>
       <c r="I195" t="str">
         <v/>
@@ -7446,7 +7446,7 @@
         <v/>
       </c>
       <c r="H196" t="str">
-        <v>images/megabass_rods/GHT610-M_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_rods/GHT610-M_main.jpg</v>
       </c>
       <c r="I196" t="str">
         <v/>
@@ -7481,7 +7481,7 @@
         <v/>
       </c>
       <c r="H197" t="str">
-        <v>images/megabass_rods/GHBF42-4UL_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_rods/GHBF42-4UL_main.jpg</v>
       </c>
       <c r="I197" t="str">
         <v/>
@@ -7516,7 +7516,7 @@
         <v/>
       </c>
       <c r="H198" t="str">
-        <v>images/megabass_rods/GH62-4ML-XG_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_rods/GH62-4ML-XG_main.jpg</v>
       </c>
       <c r="I198" t="str">
         <v/>
@@ -7551,7 +7551,7 @@
         <v/>
       </c>
       <c r="H199" t="str">
-        <v>images/daiwa_rods/モアザン ブランジーノ CGSmorethan BRANZINO CGS_morethan_BRANZINO_CGS_94ML_4550133545030.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%83%A2%E3%82%A2%E3%82%B6%E3%83%B3%20%E3%83%96%E3%83%A9%E3%83%B3%E3%82%B8%E3%83%BC%E3%83%8E%20CGSmorethan%20BRANZINO%20CGS_morethan_BRANZINO_CGS_94ML_4550133545030.jpg</v>
       </c>
       <c r="I199" t="str">
         <v/>
@@ -7586,7 +7586,7 @@
         <v/>
       </c>
       <c r="H200" t="str">
-        <v>images/daiwa_rods/モアザンMORETHAN_MORETHAN_93MLM_J_4550133452109.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%83%A2%E3%82%A2%E3%82%B6%E3%83%B3MORETHAN_MORETHAN_93MLM_J_4550133452109.jpg</v>
       </c>
       <c r="I200" t="str">
         <v/>
@@ -7621,7 +7621,7 @@
         <v/>
       </c>
       <c r="H201" t="str">
-        <v>images/daiwa_rods/ラブラックス AGS BS（ボートシーバス）LABRAX AGS BS（BOAT SEABASS）_LabraxAGS_BS_64MSQ.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%83%A9%E3%83%96%E3%83%A9%E3%83%83%E3%82%AF%E3%82%B9%20AGS%20BS%EF%BC%88%E3%83%9C%E3%83%BC%E3%83%88%E3%82%B7%E3%83%BC%E3%83%90%E3%82%B9%EF%BC%89LABRAX%20AGS%20BS%EF%BC%88BOAT%20SEABASS%EF%BC%89_LabraxAGS_BS_64MSQ.jpg</v>
       </c>
       <c r="I201" t="str">
         <v/>
@@ -7656,7 +7656,7 @@
         <v/>
       </c>
       <c r="H202" t="str">
-        <v>images/daiwa_rods/モアザン ブランジーノ EX AGS ベイトモデルMORETHAN BRANZINO EX AGS_MORETHAN_BRANZINO_EX_AGS_80HB_4550133384608.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%83%A2%E3%82%A2%E3%82%B6%E3%83%B3%20%E3%83%96%E3%83%A9%E3%83%B3%E3%82%B8%E3%83%BC%E3%83%8E%20EX%20AGS%20%E3%83%99%E3%82%A4%E3%83%88%E3%83%A2%E3%83%87%E3%83%ABMORETHAN%20BRANZINO%20EX%20AGS_MORETHAN_BRANZINO_EX_AGS_80HB_4550133384608.jpg</v>
       </c>
       <c r="I202" t="str">
         <v/>
@@ -7691,7 +7691,7 @@
         <v/>
       </c>
       <c r="H203" t="str">
-        <v>images/daiwa_rods/ラブラックス AGSLABRAX AGS_LabRaxAGS_86ML_1.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%83%A9%E3%83%96%E3%83%A9%E3%83%83%E3%82%AF%E3%82%B9%20AGSLABRAX%20AGS_LabRaxAGS_86ML_1.jpg</v>
       </c>
       <c r="I203" t="str">
         <v/>
@@ -7761,7 +7761,7 @@
         <v/>
       </c>
       <c r="H205" t="str">
-        <v>images/daiwa_rods/スカイハイSKYHIGH_SKYHIGH_90ML_4550133433894.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%82%B9%E3%82%AB%E3%82%A4%E3%83%8F%E3%82%A4SKYHIGH_SKYHIGH_90ML_4550133433894.jpg</v>
       </c>
       <c r="I205" t="str">
         <v/>
@@ -7796,7 +7796,7 @@
         <v/>
       </c>
       <c r="H206" t="str">
-        <v>images/daiwa_rods/モアザン ブランジーノ EX AGSMORETHAN BRANZINO EX AGS_Morethan_Brabzino_EX_AGS_87LML.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%83%A2%E3%82%A2%E3%82%B6%E3%83%B3%20%E3%83%96%E3%83%A9%E3%83%B3%E3%82%B8%E3%83%BC%E3%83%8E%20EX%20AGSMORETHAN%20BRANZINO%20EX%20AGS_Morethan_Brabzino_EX_AGS_87LML.jpg</v>
       </c>
       <c r="I206" t="str">
         <v/>
@@ -7831,7 +7831,7 @@
         <v/>
       </c>
       <c r="H207" t="str">
-        <v>images/daiwa_rods/シーバスフラットXSEABASS FLAT X_SeabassFlatX_86ML.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%82%B7%E3%83%BC%E3%83%90%E3%82%B9%E3%83%95%E3%83%A9%E3%83%83%E3%83%88XSEABASS%20FLAT%20X_SeabassFlatX_86ML.jpg</v>
       </c>
       <c r="I207" t="str">
         <v/>
@@ -7866,7 +7866,7 @@
         <v/>
       </c>
       <c r="H208" t="str">
-        <v>images/daiwa_rods/ラテオLATEO_LATEO_96MLMK_4550133384950.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%83%A9%E3%83%86%E3%82%AALATEO_LATEO_96MLMK_4550133384950.jpg</v>
       </c>
       <c r="I208" t="str">
         <v/>
@@ -7901,7 +7901,7 @@
         <v/>
       </c>
       <c r="H209" t="str">
-        <v>images/daiwa_rods/ラテオ BSLATEO BS_LATEO_BS_68MBW_4550133337994.png</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%83%A9%E3%83%86%E3%82%AA%20BSLATEO%20BS_LATEO_BS_68MBW_4550133337994.png</v>
       </c>
       <c r="I209" t="str">
         <v/>
@@ -7936,7 +7936,7 @@
         <v/>
       </c>
       <c r="H210" t="str">
-        <v>images/daiwa_rods/スカイハイ ボートゲームSKYHIGH BOATGAME_SKYHIGH_BOATGAME_68MB.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%82%B9%E3%82%AB%E3%82%A4%E3%83%8F%E3%82%A4%20%E3%83%9C%E3%83%BC%E3%83%88%E3%82%B2%E3%83%BC%E3%83%A0SKYHIGH%20BOATGAME_SKYHIGH_BOATGAME_68MB.jpg</v>
       </c>
       <c r="I210" t="str">
         <v/>
@@ -7971,7 +7971,7 @@
         <v/>
       </c>
       <c r="H211" t="str">
-        <v>images/daiwa_rods/ハートランド AGS（ベイトキャスティングモデル）HEARTLAND AGS（BAITCASTING MODELS）_HL741MHRB-SVAGS17.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%83%8F%E3%83%BC%E3%83%88%E3%83%A9%E3%83%B3%E3%83%89%20AGS%EF%BC%88%E3%83%99%E3%82%A4%E3%83%88%E3%82%AD%E3%83%A3%E3%82%B9%E3%83%86%E3%82%A3%E3%83%B3%E3%82%B0%E3%83%A2%E3%83%87%E3%83%AB%EF%BC%89HEARTLAND%20AGS%EF%BC%88BAITCASTING%20MODELS%EF%BC%89_HL741MHRB-SVAGS17.jpg</v>
       </c>
       <c r="I211" t="str">
         <v/>
@@ -8006,7 +8006,7 @@
         <v/>
       </c>
       <c r="H212" t="str">
-        <v>images/daiwa_rods/ハートランド AGS（スピニングモデル）HEARTLAND AGS（SPINNING MODELS）_6102LFS-AGS13.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%83%8F%E3%83%BC%E3%83%88%E3%83%A9%E3%83%B3%E3%83%89%20AGS%EF%BC%88%E3%82%B9%E3%83%94%E3%83%8B%E3%83%B3%E3%82%B0%E3%83%A2%E3%83%87%E3%83%AB%EF%BC%89HEARTLAND%20AGS%EF%BC%88SPINNING%20MODELS%EF%BC%89_6102LFS-AGS13.jpg</v>
       </c>
       <c r="I212" t="str">
         <v/>
@@ -8041,7 +8041,7 @@
         <v/>
       </c>
       <c r="H213" t="str">
-        <v>images/daiwa_rods/スティーズ（ベイトキャスティングモデル）STEEZ（BAITCASTING MODEL）_STEEZ_C64L-SV_ST_BF_4550133551437.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%EF%BC%88%E3%83%99%E3%82%A4%E3%83%88%E3%82%AD%E3%83%A3%E3%82%B9%E3%83%86%E3%82%A3%E3%83%B3%E3%82%B0%E3%83%A2%E3%83%87%E3%83%AB%EF%BC%89STEEZ%EF%BC%88BAITCASTING%20MODEL%EF%BC%89_STEEZ_C64L-SV_ST_BF_4550133551437.jpg</v>
       </c>
       <c r="I213" t="str">
         <v/>
@@ -8076,7 +8076,7 @@
         <v/>
       </c>
       <c r="H214" t="str">
-        <v>images/daiwa_rods/スティーズ （スピニングモデル）STEEZ（SPINNING MODEL）_STEEZ_S60XUL-SV_ST_4550133551550.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%20%EF%BC%88%E3%82%B9%E3%83%94%E3%83%8B%E3%83%B3%E3%82%B0%E3%83%A2%E3%83%87%E3%83%AB%EF%BC%89STEEZ%EF%BC%88SPINNING%20MODEL%EF%BC%89_STEEZ_S60XUL-SV_ST_4550133551550.jpg</v>
       </c>
       <c r="I214" t="str">
         <v/>
@@ -8111,7 +8111,7 @@
         <v/>
       </c>
       <c r="H215" t="str">
-        <v>images/daiwa_rods/スティーズ ショアコンペティション（ベイトキャスティングモデル）STEEZ SHORE COMPETITION（BAITCASTING MODEL）_STEEZSCC64MLLM4550133551451.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%20%E3%82%B7%E3%83%A7%E3%82%A2%E3%82%B3%E3%83%B3%E3%83%9A%E3%83%86%E3%82%A3%E3%82%B7%E3%83%A7%E3%83%B3%EF%BC%88%E3%83%99%E3%82%A4%E3%83%88%E3%82%AD%E3%83%A3%E3%82%B9%E3%83%86%E3%82%A3%E3%83%B3%E3%82%B0%E3%83%A2%E3%83%87%E3%83%AB%EF%BC%89STEEZ%20SHORE%20COMPETITION%EF%BC%88BAITCASTING%20MODEL%EF%BC%89_STEEZSCC64MLLM4550133551451.jpg</v>
       </c>
       <c r="I215" t="str">
         <v/>
@@ -8146,7 +8146,7 @@
         <v/>
       </c>
       <c r="H216" t="str">
-        <v>images/daiwa_rods/スティーズ リアルコントロールSTEEZ REAL CONTROL_SteezRC_S510XUL-SV_ST.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%20%E3%83%AA%E3%82%A2%E3%83%AB%E3%82%B3%E3%83%B3%E3%83%88%E3%83%AD%E3%83%BC%E3%83%ABSTEEZ%20REAL%20CONTROL_SteezRC_S510XUL-SV_ST.jpg</v>
       </c>
       <c r="I216" t="str">
         <v/>
@@ -8181,7 +8181,7 @@
         <v/>
       </c>
       <c r="H217" t="str">
-        <v>images/daiwa_rods/ハートランド（スピニングモデル）HEARTLAND（SPINNING MODELS）_HL_6102MLFS-19.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%83%8F%E3%83%BC%E3%83%88%E3%83%A9%E3%83%B3%E3%83%89%EF%BC%88%E3%82%B9%E3%83%94%E3%83%8B%E3%83%B3%E3%82%B0%E3%83%A2%E3%83%87%E3%83%AB%EF%BC%89HEARTLAND%EF%BC%88SPINNING%20MODELS%EF%BC%89_HL_6102MLFS-19.jpg</v>
       </c>
       <c r="I217" t="str">
         <v/>
@@ -8216,7 +8216,7 @@
         <v/>
       </c>
       <c r="H218" t="str">
-        <v>images/daiwa_rods/ハートランド（ベイトキャスティングモデル）HEARTLAND（BAITCASTING MODELS）_HEARTLAND_7112MRB-25_4550133434167.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%83%8F%E3%83%BC%E3%83%88%E3%83%A9%E3%83%B3%E3%83%89%EF%BC%88%E3%83%99%E3%82%A4%E3%83%88%E3%82%AD%E3%83%A3%E3%82%B9%E3%83%86%E3%82%A3%E3%83%B3%E3%82%B0%E3%83%A2%E3%83%87%E3%83%AB%EF%BC%89HEARTLAND%EF%BC%88BAITCASTING%20MODELS%EF%BC%89_HEARTLAND_7112MRB-25_4550133434167.jpg</v>
       </c>
       <c r="I218" t="str">
         <v/>
@@ -8251,7 +8251,7 @@
         <v/>
       </c>
       <c r="H219" t="str">
-        <v>images/daiwa_rods/ブラックレーベル トラベルBLACK LABEL TRAVEL_BlackLabelTravel_NC63MH-5-F.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%83%96%E3%83%A9%E3%83%83%E3%82%AF%E3%83%AC%E3%83%BC%E3%83%99%E3%83%AB%20%E3%83%88%E3%83%A9%E3%83%99%E3%83%ABBLACK%20LABEL%20TRAVEL_BlackLabelTravel_NC63MH-5-F.jpg</v>
       </c>
       <c r="I219" t="str">
         <v/>
@@ -8286,7 +8286,7 @@
         <v/>
       </c>
       <c r="H220" t="str">
-        <v>images/daiwa_rods/スティーズ ショアコンペティション（スピニングモデル）STEEZ SHORE COMPETITION（SPINNING MODEL）_STEEZ_SC_S69UL_4550133551604.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%20%E3%82%B7%E3%83%A7%E3%82%A2%E3%82%B3%E3%83%B3%E3%83%9A%E3%83%86%E3%82%A3%E3%82%B7%E3%83%A7%E3%83%B3%EF%BC%88%E3%82%B9%E3%83%94%E3%83%8B%E3%83%B3%E3%82%B0%E3%83%A2%E3%83%87%E3%83%AB%EF%BC%89STEEZ%20SHORE%20COMPETITION%EF%BC%88SPINNING%20MODEL%EF%BC%89_STEEZ_SC_S69UL_4550133551604.jpg</v>
       </c>
       <c r="I220" t="str">
         <v/>
@@ -8321,7 +8321,7 @@
         <v/>
       </c>
       <c r="H221" t="str">
-        <v>images/daiwa_rods/SWAGGERSWAGGER_SWAGGER_C66M-5_4550133500237.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/SWAGGERSWAGGER_SWAGGER_C66M-5_4550133500237.jpg</v>
       </c>
       <c r="I221" t="str">
         <v/>
@@ -8356,7 +8356,7 @@
         <v/>
       </c>
       <c r="H222" t="str">
-        <v>images/daiwa_rods/ブラックレーベルBLACK LABEL_BLX_C63MH-FR_4550133444241.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%83%96%E3%83%A9%E3%83%83%E3%82%AF%E3%83%AC%E3%83%BC%E3%83%99%E3%83%ABBLACK%20LABEL_BLX_C63MH-FR_4550133444241.jpg</v>
       </c>
       <c r="I222" t="str">
         <v/>
@@ -8391,7 +8391,7 @@
         <v/>
       </c>
       <c r="H223" t="str">
-        <v>images/daiwa_rods/タトゥーラ エリートTATULA ELITE_TATULA_ELITE_691MLRB_05807342.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%82%BF%E3%83%88%E3%82%A5%E3%83%BC%E3%83%A9%20%E3%82%A8%E3%83%AA%E3%83%BC%E3%83%88TATULA%20ELITE_TATULA_ELITE_691MLRB_05807342.jpg</v>
       </c>
       <c r="I223" t="str">
         <v/>
@@ -8426,7 +8426,7 @@
         <v/>
       </c>
       <c r="H224" t="str">
-        <v>images/daiwa_rods/タトゥーラTATULA_TATULA_6101MRB_4550133341472.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%82%BF%E3%83%88%E3%82%A5%E3%83%BC%E3%83%A9TATULA_TATULA_6101MRB_4550133341472.jpg</v>
       </c>
       <c r="I224" t="str">
         <v/>
@@ -8461,7 +8461,7 @@
         <v/>
       </c>
       <c r="H225" t="str">
-        <v>images/daiwa_rods/タトゥーラ トラベルTATULA TRAVEL_TATULA_TRAVEL_664MLRB_4550133544897.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%82%BF%E3%83%88%E3%82%A5%E3%83%BC%E3%83%A9%20%E3%83%88%E3%83%A9%E3%83%99%E3%83%ABTATULA%20TRAVEL_TATULA_TRAVEL_664MLRB_4550133544897.jpg</v>
       </c>
       <c r="I225" t="str">
         <v/>
@@ -8496,7 +8496,7 @@
         <v/>
       </c>
       <c r="H226" t="str">
-        <v>images/daiwa_rods/B.B.B（トリプルビー）B.B.B_BBB636TMLRB.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/B.B.B%EF%BC%88%E3%83%88%E3%83%AA%E3%83%97%E3%83%AB%E3%83%93%E3%83%BC%EF%BC%89B.B.B_BBB636TMLRB.jpg</v>
       </c>
       <c r="I226" t="str">
         <v/>
@@ -8531,7 +8531,7 @@
         <v/>
       </c>
       <c r="H227" t="str">
-        <v>images/daiwa_rods/ブレイゾンBLAZON_Blazon_C64L-2-BF.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%83%96%E3%83%AC%E3%82%A4%E3%82%BE%E3%83%B3BLAZON_Blazon_C64L-2-BF.jpg</v>
       </c>
       <c r="I227" t="str">
         <v/>
@@ -8566,7 +8566,7 @@
         <v/>
       </c>
       <c r="H228" t="str">
-        <v>images/daiwa_rods/カムイランケタムKAMUY RANKE TAM_KamuyRankeTam_121XH.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%82%AB%E3%83%A0%E3%82%A4%E3%83%A9%E3%83%B3%E3%82%B1%E3%82%BF%E3%83%A0KAMUY%20RANKE%20TAM_KamuyRankeTam_121XH.jpg</v>
       </c>
       <c r="I228" t="str">
         <v/>
@@ -8601,7 +8601,7 @@
         <v/>
       </c>
       <c r="H229" t="str">
-        <v>images/daiwa_rods/モバイルパックMOBILE PACK_MobilePack_766TML.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%83%A2%E3%83%90%E3%82%A4%E3%83%AB%E3%83%91%E3%83%83%E3%82%AFMOBILE%20PACK_MobilePack_766TML.jpg</v>
       </c>
       <c r="I229" t="str">
         <v/>
@@ -8636,7 +8636,7 @@
         <v/>
       </c>
       <c r="H230" t="str">
-        <v>images/daiwa_rods/ブレイゾン モバイルBLAZON MOBILE_BlazonMobile_6106TMHB.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%83%96%E3%83%AC%E3%82%A4%E3%82%BE%E3%83%B3%20%E3%83%A2%E3%83%90%E3%82%A4%E3%83%ABBLAZON%20MOBILE_BlazonMobile_6106TMHB.jpg</v>
       </c>
       <c r="I230" t="str">
         <v/>
@@ -8671,7 +8671,7 @@
         <v/>
       </c>
       <c r="H231" t="str">
-        <v>images/daiwa_rods/シルバークリーク AK（アキアジ）SILVER CREEK AK（AKIAJI）_SILVERCREEK_AK_130H.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%82%B7%E3%83%AB%E3%83%90%E3%83%BC%E3%82%AF%E3%83%AA%E3%83%BC%E3%82%AF%20AK%EF%BC%88%E3%82%A2%E3%82%AD%E3%82%A2%E3%82%B8%EF%BC%89SILVER%20CREEK%20AK%EF%BC%88AKIAJI%EF%BC%89_SILVERCREEK_AK_130H.jpg</v>
       </c>
       <c r="I231" t="str">
         <v/>
@@ -8706,7 +8706,7 @@
         <v/>
       </c>
       <c r="H232" t="str">
-        <v>images/daiwa_rods/シルバークリーク グラスプログレッシブSILVER CREEK GLASS PROGRESSIVE_SilverCreek_GP_48UL-G.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%82%B7%E3%83%AB%E3%83%90%E3%83%BC%E3%82%AF%E3%83%AA%E3%83%BC%E3%82%AF%20%E3%82%B0%E3%83%A9%E3%82%B9%E3%83%97%E3%83%AD%E3%82%B0%E3%83%AC%E3%83%83%E3%82%B7%E3%83%96SILVER%20CREEK%20GLASS%20PROGRESSIVE_SilverCreek_GP_48UL-G.jpg</v>
       </c>
       <c r="I232" t="str">
         <v/>
@@ -8741,7 +8741,7 @@
         <v/>
       </c>
       <c r="H233" t="str">
-        <v>images/daiwa_rods/タトゥーラ XTTATULA XT_TATULA_XT_6102MHRB_4550133169373.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%82%BF%E3%83%88%E3%82%A5%E3%83%BC%E3%83%A9%20XTTATULA%20XT_TATULA_XT_6102MHRB_4550133169373.jpg</v>
       </c>
       <c r="I233" t="str">
         <v/>
@@ -8776,7 +8776,7 @@
         <v/>
       </c>
       <c r="H234" t="str">
-        <v>images/daiwa_rods/プレッソ-LTD AGSPRESSO-LTD AGS_Presso-LTDAGS_55M-SMT.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%83%97%E3%83%AC%E3%83%83%E3%82%BD-LTD%20AGSPRESSO-LTD%20AGS_Presso-LTDAGS_55M-SMT.jpg</v>
       </c>
       <c r="I234" t="str">
         <v/>
@@ -8811,7 +8811,7 @@
         <v/>
       </c>
       <c r="H235" t="str">
-        <v>images/daiwa_rods/シルバークリーク トラッドSilver Creek Trad_SILVER_CREEK_TRAD_48UL_4550133340833.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%82%B7%E3%83%AB%E3%83%90%E3%83%BC%E3%82%AF%E3%83%AA%E3%83%BC%E3%82%AF%20%E3%83%88%E3%83%A9%E3%83%83%E3%83%89Silver%20Creek%20Trad_SILVER_CREEK_TRAD_48UL_4550133340833.jpg</v>
       </c>
       <c r="I235" t="str">
         <v/>
@@ -8846,7 +8846,7 @@
         <v/>
       </c>
       <c r="H236" t="str">
-        <v>images/daiwa_rods/シルバークリーク AurumSILVER CREEK AURUM_Silver_Creek_Aurum_410L_4550133444968.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%82%B7%E3%83%AB%E3%83%90%E3%83%BC%E3%82%AF%E3%83%AA%E3%83%BC%E3%82%AF%20AurumSILVER%20CREEK%20AURUM_Silver_Creek_Aurum_410L_4550133444968.jpg</v>
       </c>
       <c r="I236" t="str">
         <v/>
@@ -8881,7 +8881,7 @@
         <v/>
       </c>
       <c r="H237" t="str">
-        <v>images/daiwa_rods/プレッソ AIR AGSPRESSO AIR AGS_PressoAirAGS_510UL.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%83%97%E3%83%AC%E3%83%83%E3%82%BD%20AIR%20AGSPRESSO%20AIR%20AGS_PressoAirAGS_510UL.jpg</v>
       </c>
       <c r="I237" t="str">
         <v/>
@@ -8916,7 +8916,7 @@
         <v/>
       </c>
       <c r="H238" t="str">
-        <v>images/daiwa_rods/シルバークリーク レイクジギングSILVER CREEK LAKE JIGGING_SILVER_CREEK_LAKE_JIGGING_63LB-T_4550133453359.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%82%B7%E3%83%AB%E3%83%90%E3%83%BC%E3%82%AF%E3%83%AA%E3%83%BC%E3%82%AF%20%E3%83%AC%E3%82%A4%E3%82%AF%E3%82%B8%E3%82%AE%E3%83%B3%E3%82%B0SILVER%20CREEK%20LAKE%20JIGGING_SILVER_CREEK_LAKE_JIGGING_63LB-T_4550133453359.jpg</v>
       </c>
       <c r="I238" t="str">
         <v/>
@@ -8951,7 +8951,7 @@
         <v/>
       </c>
       <c r="H239" t="str">
-        <v>images/daiwa_rods/ピュアリストPURELIST_Purelist_53ULW.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%83%94%E3%83%A5%E3%82%A2%E3%83%AA%E3%82%B9%E3%83%88PURELIST_Purelist_53ULW.jpg</v>
       </c>
       <c r="I239" t="str">
         <v/>
@@ -8986,7 +8986,7 @@
         <v/>
       </c>
       <c r="H240" t="str">
-        <v>images/daiwa_rods/プレッソ MXPRESSO MX_PRESSO_MX_60UL_4550133544835.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%83%97%E3%83%AC%E3%83%83%E3%82%BD%20MXPRESSO%20MX_PRESSO_MX_60UL_4550133544835.jpg</v>
       </c>
       <c r="I240" t="str">
         <v/>
@@ -9021,7 +9021,7 @@
         <v/>
       </c>
       <c r="H241" t="str">
-        <v>images/daiwa_rods/イプリミIPRIMI_Iprimi56XXUL-S.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%82%A4%E3%83%97%E3%83%AA%E3%83%9FIPRIMI_Iprimi56XXUL-S.jpg</v>
       </c>
       <c r="I241" t="str">
         <v/>
@@ -9056,7 +9056,7 @@
         <v/>
       </c>
       <c r="H242" t="str">
-        <v>images/daiwa_rods/トラウト X NTTROUT X NT_Trout_X_NT_53ULN.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%83%88%E3%83%A9%E3%82%A6%E3%83%88%20X%20NTTROUT%20X%20NT_Trout_X_NT_53ULN.jpg</v>
       </c>
       <c r="I242" t="str">
         <v/>
@@ -9091,7 +9091,7 @@
         <v/>
       </c>
       <c r="H243" t="str">
-        <v>images/daiwa_rods/ロッホモア フライコンボLOCHMOR FLY COMBO_LochomorFlyCombo803.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%83%AD%E3%83%83%E3%83%9B%E3%83%A2%E3%82%A2%20%E3%83%95%E3%83%A9%E3%82%A4%E3%82%B3%E3%83%B3%E3%83%9CLOCHMOR%20FLY%20COMBO_LochomorFlyCombo803.jpg</v>
       </c>
       <c r="I243" t="str">
         <v/>
@@ -9126,7 +9126,7 @@
         <v/>
       </c>
       <c r="H244" t="str">
-        <v>images/daiwa_rods/ピュアリスト AKPURELIST AK_PurelistAK_126H-3.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%83%94%E3%83%A5%E3%82%A2%E3%83%AA%E3%82%B9%E3%83%88%20AKPURELIST%20AK_PurelistAK_126H-3.jpg</v>
       </c>
       <c r="I244" t="str">
         <v/>
@@ -9161,7 +9161,7 @@
         <v/>
       </c>
       <c r="H245" t="str">
-        <v>images/daiwa_rods/ワイズストリームWISE STREAM_WiseStream_46TULQ.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%83%AF%E3%82%A4%E3%82%BA%E3%82%B9%E3%83%88%E3%83%AA%E3%83%BC%E3%83%A0WISE%20STREAM_WiseStream_46TULQ.jpg</v>
       </c>
       <c r="I245" t="str">
         <v/>
@@ -9196,7 +9196,7 @@
         <v/>
       </c>
       <c r="H246" t="str">
-        <v>images/daiwa_rods/トラウト X ATTROUT X AT_TroutX_AT60UL.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%83%88%E3%83%A9%E3%82%A6%E3%83%88%20X%20ATTROUT%20X%20AT_TroutX_AT60UL.jpg</v>
       </c>
       <c r="I246" t="str">
         <v/>
@@ -9231,7 +9231,7 @@
         <v/>
       </c>
       <c r="H247" t="str">
-        <v>images/daiwa_rods/月下美人 MX アジングGEKKABIJIN MX AJING_GEKKABIJIN_MX_AJING_48L-S_4550133338359.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E6%9C%88%E4%B8%8B%E7%BE%8E%E4%BA%BA%20MX%20%E3%82%A2%E3%82%B8%E3%83%B3%E3%82%B0GEKKABIJIN%20MX%20AJING_GEKKABIJIN_MX_AJING_48L-S_4550133338359.jpg</v>
       </c>
       <c r="I247" t="str">
         <v/>
@@ -9266,7 +9266,7 @@
         <v/>
       </c>
       <c r="H248" t="str">
-        <v>images/daiwa_rods/月下美人 AIRGEKKABIJIN AIR_GEKKABIJIN_AIR_63XULB-T_W_4550133338298.png</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E6%9C%88%E4%B8%8B%E7%BE%8E%E4%BA%BA%20AIRGEKKABIJIN%20AIR_GEKKABIJIN_AIR_63XULB-T_W_4550133338298.png</v>
       </c>
       <c r="I248" t="str">
         <v/>
@@ -9301,7 +9301,7 @@
         <v/>
       </c>
       <c r="H249" t="str">
-        <v>images/daiwa_rods/月下美人 AIR AJINGBOATGEKKABIJIN AIR AJINGBOAT_GEKKABIJIN_AIR_AB_69L-SK_4550133338328.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E6%9C%88%E4%B8%8B%E7%BE%8E%E4%BA%BA%20AIR%20AJINGBOATGEKKABIJIN%20AIR%20AJINGBOAT_GEKKABIJIN_AIR_AB_69L-SK_4550133338328.jpg</v>
       </c>
       <c r="I249" t="str">
         <v/>
@@ -9336,7 +9336,7 @@
         <v/>
       </c>
       <c r="H250" t="str">
-        <v>images/daiwa_rods/月下美人 EXGEKKABIJIN EX_Gekka_EX_68LTQ.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E6%9C%88%E4%B8%8B%E7%BE%8E%E4%BA%BA%20EXGEKKABIJIN%20EX_Gekka_EX_68LTQ.jpg</v>
       </c>
       <c r="I250" t="str">
         <v/>
@@ -9371,7 +9371,7 @@
         <v/>
       </c>
       <c r="H251" t="str">
-        <v>images/daiwa_rods/月下美人 MXGEKKABIJIN MX_GEKKABIJIN_MX_68L-T_4550133338397.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E6%9C%88%E4%B8%8B%E7%BE%8E%E4%BA%BA%20MXGEKKABIJIN%20MX_GEKKABIJIN_MX_68L-T_4550133338397.jpg</v>
       </c>
       <c r="I251" t="str">
         <v/>
@@ -9406,7 +9406,7 @@
         <v/>
       </c>
       <c r="H252" t="str">
-        <v>images/daiwa_rods/月下美人 MX モバイルGEKKABIJIN MX MOBILE_GekkaMXMB_72UL-5.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E6%9C%88%E4%B8%8B%E7%BE%8E%E4%BA%BA%20MX%20%E3%83%A2%E3%83%90%E3%82%A4%E3%83%ABGEKKABIJIN%20MX%20MOBILE_GekkaMXMB_72UL-5.jpg</v>
       </c>
       <c r="I252" t="str">
         <v/>
@@ -9441,7 +9441,7 @@
         <v/>
       </c>
       <c r="H253" t="str">
-        <v>images/daiwa_rods/アジメバル ＸAJIMEBARU X_AJI_MEBARU_X_510UL-S_4550133164699.png</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%82%A2%E3%82%B8%E3%83%A1%E3%83%90%E3%83%AB%20%EF%BC%B8AJIMEBARU%20X_AJI_MEBARU_X_510UL-S_4550133164699.png</v>
       </c>
       <c r="I253" t="str">
         <v/>
@@ -9476,7 +9476,7 @@
         <v/>
       </c>
       <c r="H254" t="str">
-        <v>images/daiwa_rods/月下美人（メバルモデル）GEKKABIJIN MEBARUMODEL_Gekka_Mebaru_1.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E6%9C%88%E4%B8%8B%E7%BE%8E%E4%BA%BA%EF%BC%88%E3%83%A1%E3%83%90%E3%83%AB%E3%83%A2%E3%83%87%E3%83%AB%EF%BC%89GEKKABIJIN%20MEBARUMODEL_Gekka_Mebaru_1.jpg</v>
       </c>
       <c r="I254" t="str">
         <v/>
@@ -9511,7 +9511,7 @@
         <v/>
       </c>
       <c r="H255" t="str">
-        <v>images/daiwa_rods/月下美人 AJINGGEKKABIJIN AJING_GekkaAJing510UL-S_1.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E6%9C%88%E4%B8%8B%E7%BE%8E%E4%BA%BA%20AJINGGEKKABIJIN%20AJING_GekkaAJing510UL-S_1.jpg</v>
       </c>
       <c r="I255" t="str">
         <v/>
@@ -9546,7 +9546,7 @@
         <v/>
       </c>
       <c r="H256" t="str">
-        <v>images/daiwa_rods/月下美人 MX AJING BOATGEKKABIJIN MX AJING BOAT_Gekka_MxAjingBoat_64L-S.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E6%9C%88%E4%B8%8B%E7%BE%8E%E4%BA%BA%20MX%20AJING%20BOATGEKKABIJIN%20MX%20AJING%20BOAT_Gekka_MxAjingBoat_64L-S.jpg</v>
       </c>
       <c r="I256" t="str">
         <v/>
@@ -9581,7 +9581,7 @@
         <v/>
       </c>
       <c r="H257" t="str">
-        <v>pkgGear/images/rod/KEITECH/202602261642543817.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/KEITECH_rods/202602261642543817.jpg</v>
       </c>
       <c r="I257" t="str">
         <v>2026-04-10T05:56:19.503Z</v>
@@ -9619,7 +9619,7 @@
         <v/>
       </c>
       <c r="H258" t="str">
-        <v>pkgGear/images/rod/KEITECH/202407311709371706.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/KEITECH_rods/202407311709371706.jpg</v>
       </c>
       <c r="I258" t="str">
         <v>2026-04-10T05:56:22.101Z</v>
@@ -9662,7 +9662,7 @@
         <v/>
       </c>
       <c r="H259" t="str">
-        <v>pkgGear/images/rod/KEITECH/202506201737523566.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/KEITECH_rods/202506201737523566.jpg</v>
       </c>
       <c r="I259" t="str">
         <v>2026-04-10T05:56:24.964Z</v>
@@ -9700,7 +9700,7 @@
         <v/>
       </c>
       <c r="H260" t="str">
-        <v>pkgGear/images/rod/KEITECH/202208011647014321.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/KEITECH_rods/202208011647014321.jpg</v>
       </c>
       <c r="I260" t="str">
         <v>2026-04-10T05:56:26.942Z</v>

--- a/GearSage-client/rate/excel/rod.xlsx
+++ b/GearSage-client/rate/excel/rod.xlsx
@@ -478,7 +478,7 @@
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>bass,溪流,海鲈,岸投,船钓,旅行</v>
+        <v>bass,溪流,旅行</v>
       </c>
       <c r="I2" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_rods/WORLD%20SHAULA%20TECHNICAL%20EDITION_main.jpg</v>
@@ -12422,7 +12422,7 @@
         <v>2</v>
       </c>
       <c r="C212" t="str">
-        <v>【2025.01追加型號】HEARTLAND LIBERALIST</v>
+        <v>【2025.01追加】HEARTLAND LIBERALIST</v>
       </c>
       <c r="D212" t="str">
         <v>25 STEEZ TRAVEL</v>
@@ -12478,7 +12478,7 @@
         <v>2</v>
       </c>
       <c r="C213" t="str">
-        <v>【2025.01追加型號】EMERALDAS STOIST ST (外導環款)</v>
+        <v>【2025.01追加】EMERALDAS STOIST ST (外導環款)</v>
       </c>
       <c r="D213" t="str">
         <v>HEARTLAND LIBERALIST</v>
@@ -12534,7 +12534,7 @@
         <v>2</v>
       </c>
       <c r="C214" t="str">
-        <v>【2024.12追加型號】STEEZ (直柄款)</v>
+        <v>【2024.12追加】STEEZ (直柄款)</v>
       </c>
       <c r="D214" t="str">
         <v>EMERALDAS STOIST ST（OUT GUIDE MODEL）</v>
@@ -12590,7 +12590,7 @@
         <v>2</v>
       </c>
       <c r="C215" t="str">
-        <v>【2024.12追加型號】STEEZ (槍柄款)</v>
+        <v>【2024.12追加】STEEZ (槍柄款)</v>
       </c>
       <c r="D215" t="str">
         <v>STEEZ（SPINNING MODEL）</v>
@@ -12926,7 +12926,7 @@
         <v>2</v>
       </c>
       <c r="C221" t="str">
-        <v>【2024.07追加型號】EMERALDAS STOIST RT</v>
+        <v>【2024.07追加】EMERALDAS STOIST RT</v>
       </c>
       <c r="D221" t="str">
         <v>EMERALDAS AIR</v>
@@ -13150,7 +13150,7 @@
         <v>2</v>
       </c>
       <c r="C225" t="str">
-        <v>【2024追加型號】 OUTRAGE BR</v>
+        <v>【2024追加】OUTRAGE BR</v>
       </c>
       <c r="D225" t="str">
         <v>24 鏡牙 AIR (KYOHGA AIR)</v>
@@ -13206,7 +13206,7 @@
         <v>2</v>
       </c>
       <c r="C226" t="str">
-        <v>【2024追加型號】SALTIGA C (CASTING MODEL)</v>
+        <v>【2024追加】SALTIGA C (CASTING MODEL)</v>
       </c>
       <c r="D226" t="str">
         <v>OUTRAGE BR</v>

--- a/GearSage-client/rate/excel/rod.xlsx
+++ b/GearSage-client/rate/excel/rod.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R632"/>
+  <dimension ref="A1:R662"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -11712,7 +11712,7 @@
         <v>海鲈,岸投</v>
       </c>
       <c r="I199" t="str">
-        <v>https://www.daiwaseiko.com.tw/upload/product_m/twL_product_26C12_g35rge6h94.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1000_morethan_BRANZINO_CGS.jpg</v>
       </c>
       <c r="J199" t="str">
         <v/>
@@ -11768,7 +11768,7 @@
         <v>岸投</v>
       </c>
       <c r="I200" t="str">
-        <v>https://www.daiwaseiko.com.tw/upload/product_m/twL_product_26B12_cuu4u4we55.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1001_SILVER_WOLF_SX.jpg</v>
       </c>
       <c r="J200" t="str">
         <v/>
@@ -11824,7 +11824,7 @@
         <v>船钓</v>
       </c>
       <c r="I201" t="str">
-        <v>https://www.daiwaseiko.com.tw/upload/product_m/twL_product_26A29_mn4fd86v9c.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1002_SALTIGA_SLJ_EX.jpg</v>
       </c>
       <c r="J201" t="str">
         <v/>
@@ -11880,7 +11880,7 @@
         <v>船钓</v>
       </c>
       <c r="I202" t="str">
-        <v>https://www.daiwaseiko.com.tw/upload/product_m/twL_product_25L30_26tw4c4gmd.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1003_SALTIGA_J_LOWRESPONSE.jpg</v>
       </c>
       <c r="J202" t="str">
         <v/>
@@ -11921,7 +11921,7 @@
         <v>Outrage XV C</v>
       </c>
       <c r="D203" t="str">
-        <v>EMERALDAS LANDING GAFF</v>
+        <v>Outrage XV C</v>
       </c>
       <c r="E203" t="str">
         <v/>
@@ -11936,7 +11936,7 @@
         <v>船钓</v>
       </c>
       <c r="I203" t="str">
-        <v>https://www.daiwaseiko.com.tw/upload/product_m/twL_product_26C06_nq4ckf2fm8.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1004_Outrage_XV_C.jpg</v>
       </c>
       <c r="J203" t="str">
         <v/>
@@ -11960,10 +11960,10 @@
         <v>承襲 Outrage 系列引以為傲的高實戰性能，船拋進階入門竿的絕對首選。 全球化船竿系列「OUTRAGE XV」。 承襲 OUTRAGE 系列經典的調性與韌性，並針對全球各大釣場開發出更具通用性的規格與強度；全系列多元的陣容，具備足以正面對決、攻略目標魚種的強悍潛力。 其中，船拋竿型（Casting Model）特別優化了路亞拋投與操竿時的反覆動作流暢度，在搏魚過程中能順暢地彎曲，有效分散負擔，讓釣手在對抗大魚時更顯從容。</v>
       </c>
       <c r="Q203" t="str">
-        <v>配件 / 抄網搭鉤</v>
+        <v>近海船拋 / 青物鮪魚</v>
       </c>
       <c r="R203" t="str">
-        <v>軟絲起魚輔助工具 / 不對應獨立作釣竿路線</v>
+        <v>近海大型目標路線明確 / 船拋與搏魚支撐更完整</v>
       </c>
     </row>
     <row r="204">
@@ -11977,7 +11977,7 @@
         <v>TATULA TRAVEL</v>
       </c>
       <c r="D204" t="str">
-        <v>Outrage XV C</v>
+        <v>TATULA TRAVEL</v>
       </c>
       <c r="E204" t="str">
         <v/>
@@ -11992,7 +11992,7 @@
         <v>bass,旅行</v>
       </c>
       <c r="I204" t="str">
-        <v>https://www.daiwaseiko.com.tw/upload/product_m/twL_product_26A06_qqvpm7kwsf.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1005_TATULA_TRAVEL.jpg</v>
       </c>
       <c r="J204" t="str">
         <v/>
@@ -12016,10 +12016,10 @@
         <v>TATULA 系列 4pcs 型號誕生 世界級水準的鱸魚品牌「TATULA」 TATULA 品牌正式推出具備優異攜帶性的 4pcs 型號。 其輕盈手感讓人忘卻多節竿的結構限制，能高水準地應對鱸魚釣中的各項基礎操作。 憑藉 60cm 以內的收納長度所帶來的強大機動力，讓您隨時與世界各地的鱸魚對峙。 讓 TATULA TRAVEL 陪伴您捕獲值得紀念的夢幻巨物。 以鱸魚路亞釣核心需求所構建的規格陣容。 採用能帶來跨級別性能的「SVF」超高密度碳纖胚料。 搭載 V-Joint 技術，實現了毫無接節感且完美流暢的彎曲曲線。 傳承 TATULA 標誌性的設計風格，呈現出既奪目又剛毅洗鍊的外觀質感。</v>
       </c>
       <c r="Q204" t="str">
-        <v>近海船拋 / 青物鮪魚</v>
+        <v>bass / 淡水泛用 / 便攜</v>
       </c>
       <c r="R204" t="str">
-        <v>近海大型目標路線明確 / 船拋與搏魚支撐更完整</v>
+        <v>淡水路亞便攜路線明確 / 出行與多技法兼顧</v>
       </c>
     </row>
     <row r="205">
@@ -12033,7 +12033,7 @@
         <v>26 TATULA</v>
       </c>
       <c r="D205" t="str">
-        <v>TATULA TRAVEL</v>
+        <v>26 TATULA</v>
       </c>
       <c r="E205" t="str">
         <v/>
@@ -12048,7 +12048,7 @@
         <v>bass</v>
       </c>
       <c r="I205" t="str">
-        <v>https://www.daiwaseiko.com.tw/upload/product_m/twL_product_25K10_ityc95zmxk.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1006_26_TATULA.jpg</v>
       </c>
       <c r="J205" t="str">
         <v/>
@@ -12072,10 +12072,10 @@
         <v>Bass Rod TATULA：全新進化的世代 世界級水準的鱸魚竿系列「TATULA」 在拋投性能、感度、刺魚以及遛魚性能等各項基礎面向上，全面達到高水準完成度的高性能鱸魚竿系列。 針對日本釣場開發的多樣化陣容，從岸釣到船釣皆能靈活應對。 搭載帶來超越同級性能的高密度碳纖胚料「SVF」，以一本半設計為全系列主軸，並將其中幾款經典規格加入兩本的款式。 承襲 TATULA 特有的設計風格，外觀搶眼卻不失剛毅洗鍊的風格。</v>
       </c>
       <c r="Q205" t="str">
-        <v>bass / 淡水泛用 / 便攜</v>
+        <v>bass / 淡水泛用</v>
       </c>
       <c r="R205" t="str">
-        <v>淡水路亞便攜路線明確 / 出行與多技法兼顧</v>
+        <v>淡水路亞梯度完整 / 從技巧到泛用覆蓋清晰</v>
       </c>
     </row>
     <row r="206">
@@ -12089,7 +12089,7 @@
         <v>25 STEEZ (直柄款)</v>
       </c>
       <c r="D206" t="str">
-        <v>26 TATULA</v>
+        <v>25 STEEZ（BAITCASTING MODEL）</v>
       </c>
       <c r="E206" t="str">
         <v/>
@@ -12104,7 +12104,7 @@
         <v>bass</v>
       </c>
       <c r="I206" t="str">
-        <v>https://www.daiwaseiko.com.tw/upload/product_m/twL_product_25K06_8q8y7wf7j8.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1007_25_STEEZ.jpg</v>
       </c>
       <c r="J206" t="str">
         <v/>
@@ -12128,10 +12128,10 @@
         <v>為了那些認真看待鱸魚釣的人們 DAIWA致力創造出的產品，與那些將鱸魚釣視為生活重心、認真看待鱸魚釣的人們產生共鳴。 這是DAIWA開發團隊將對鱸魚釣的熱忱，透過產品和訊息與大家分享的品牌理念具體化。為此，DAIWA憑藉其技術和熱情，嚴謹地打造出這些產品。這不僅僅只是釣竿與捲線器，而是將信念與驢魚釣友的熱情一同寄託在釣鱸魚所需要的一切物品……這就是「STEEZ」。 朝向「感度」的更高境界 搭載最先端技術、實現水下可見化的競技用竿——26STEEZ。歷經15年，全面改款的21STEEZ以尖端科技重新誕生。 開發概念為「千里眼」。釣竿的永恆核心理念——感度 近年在黑鱸釣界備受矚目，利用 FFS(Forward Facing Sonar，前向聲納魚探設備)實現水下可見化的即時鎖定釣法，讓釣手能精準掌握水下動態。26STEEZ的目標，不僅是在船上，即便在岸釣時，沒有 FFS 也能透過極致的竿感，彷彿窺視水下世界，感知過去無法察覺的魚餌，按意願操作誘發魚咬鉤，實現過去難以達成的釣法，讓黑鱸釣更為刺激有趣。此外，所有型號的手把皆採可拆式設計，方便使用，並維持可靠的日本製品質(MADE IN JAPAN)。</v>
       </c>
       <c r="Q206" t="str">
-        <v>bass / 淡水泛用</v>
+        <v>淡水 Bass / 技法分工 / 软硬饵覆盖</v>
       </c>
       <c r="R206" t="str">
-        <v>淡水路亞梯度完整 / 從技巧到泛用覆蓋清晰</v>
+        <v>按子型号区分精细、卷阻、底操、cover 和大饵路线，适合依照钓组与作钓距离选型。</v>
       </c>
     </row>
     <row r="207">
@@ -12160,7 +12160,7 @@
         <v>bass</v>
       </c>
       <c r="I207" t="str">
-        <v>https://www.daiwaseiko.com.tw/upload/product_m/twL_product_25K06_qs2werja46.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1008_25_STEEZ.jpg</v>
       </c>
       <c r="J207" t="str">
         <v/>
@@ -12184,10 +12184,10 @@
         <v>為了那些認真看待鱸魚釣的人們 DAIWA致力創造出的產品，與那些將鱸魚釣視為生活重心、認真看待鱸魚釣的人們產生共鳴。 這是DAIWA開發團隊將對鱸魚釣的熱忱，透過產品和訊息與大家分享的品牌理念具體化。為此，DAIWA憑藉其技術和熱情，嚴謹地打造出這些產品。這不僅僅只是釣竿與捲線器，而是將信念與驢魚釣友的熱情一同寄託在釣鱸魚所需要的一切物品……這就是「STEEZ」。 朝向「感度」的更高境界 搭載最先端技術、實現水下可見化的競技用竿——26STEEZ。歷經15年，全面改款的21STEEZ以尖端科技重新誕生。 開發概念為「千里眼」。釣竿的永恆核心理念——感度 近年在黑鱸釣界備受矚目，利用 FFS(Forward Facing Sonar，前向聲納魚探設備)實現水下可見化的即時鎖定釣法，讓釣手能精準掌握水下動態。26STEEZ的目標，不僅是在船上，即便在岸釣時，沒有 FFS 也能透過極致的竿感，彷彿窺視水下世界，感知過去無法察覺的魚餌，按意願操作誘發魚咬鉤，實現過去難以達成的釣法，讓黑鱸釣更為刺激有趣。此外，所有型號的手把皆採可拆式設計，方便使用，並維持可靠的日本製品質(MADE IN JAPAN)。</v>
       </c>
       <c r="Q207" t="str">
-        <v>bass / 淡水泛用</v>
+        <v>淡水 Bass / 技法分工 / 软硬饵覆盖</v>
       </c>
       <c r="R207" t="str">
-        <v>淡水路亞梯度完整 / 從技巧到泛用覆蓋清晰</v>
+        <v>按子型号区分精细、卷阻、底操、cover 和大饵路线，适合依照钓组与作钓距离选型。</v>
       </c>
     </row>
     <row r="208">
@@ -12201,7 +12201,7 @@
         <v>Outrage XV SJ</v>
       </c>
       <c r="D208" t="str">
-        <v>25 STEEZ（BAITCASTING MODEL）</v>
+        <v>Outrage XV SJ</v>
       </c>
       <c r="E208" t="str">
         <v/>
@@ -12216,7 +12216,7 @@
         <v>船钓</v>
       </c>
       <c r="I208" t="str">
-        <v>https://www.daiwaseiko.com.tw/upload/product_m/twL_product_25G22_jisffqxkwe.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1009_Outrage_XV_SJ.jpg</v>
       </c>
       <c r="J208" t="str">
         <v/>
@@ -12240,10 +12240,10 @@
         <v>專為慢速鐵板釣法打造、擁有獨特高實用性的慢鐵竿。 全球off shore釣竿系列「OUTRAGE XV」。 承襲OUTRAGE系列特有的竿身調性，同時足以應對世界各地釣場的規格與強度，展開多樣化的款式。具備足以正面對決目標魚種的潛力。 其中的慢鐵竿（Slow Jigging）款式，實現了可輕鬆操控鐵板動作所需的反彈力，具備最適合的經常出線(下沉)的慢鐵竿身調性。</v>
       </c>
       <c r="Q208" t="str">
-        <v>bass / 淡水泛用</v>
+        <v>船釣 / 鐵板 / 海水專項</v>
       </c>
       <c r="R208" t="str">
-        <v>淡水路亞梯度完整 / 從技巧到泛用覆蓋清晰</v>
+        <v>船釣鐵板路線明確 / 從輕鐵到大物深場覆蓋清晰</v>
       </c>
     </row>
     <row r="209">
@@ -12257,7 +12257,7 @@
         <v>Outrage XV LJ</v>
       </c>
       <c r="D209" t="str">
-        <v>Outrage XV SJ</v>
+        <v>Outrage XV LJ</v>
       </c>
       <c r="E209" t="str">
         <v/>
@@ -12272,7 +12272,7 @@
         <v>船钓</v>
       </c>
       <c r="I209" t="str">
-        <v>https://www.daiwaseiko.com.tw/upload/product_m/twL_product_25G22_rf4rbna57w.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1010_Outrage_XV_LJ.jpg</v>
       </c>
       <c r="J209" t="str">
         <v/>
@@ -12313,7 +12313,7 @@
         <v>Outrage XV J</v>
       </c>
       <c r="D210" t="str">
-        <v>Outrage XV LJ</v>
+        <v>Outrage XV J</v>
       </c>
       <c r="E210" t="str">
         <v/>
@@ -12328,7 +12328,7 @@
         <v>船钓</v>
       </c>
       <c r="I210" t="str">
-        <v>https://www.daiwaseiko.com.tw/upload/product_m/twL_product_25G22_qz9jptctug.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1011_Outrage_XV_J.jpg</v>
       </c>
       <c r="J210" t="str">
         <v/>
@@ -12352,10 +12352,10 @@
         <v>Outrage系列特有的高實戰性能，是最強入門鐵板竿的決定版。 全球型off shore釣竿系列「OUTRAGE XV」，承襲Outrage系列特有的竿身調性，並具備足以應對世界各地釣場的規格與力量組成。是一款真正具備以征服為目標的實戰型竿款。其中的鐵板竿系列（Jigging Model），不僅具備能精準操控鐵板的操竿性能，更擁有能與青物正面對決的強大力量。</v>
       </c>
       <c r="Q210" t="str">
-        <v>船釣 / 鐵板 / 海水專項</v>
+        <v>綜合路亞泛用</v>
       </c>
       <c r="R210" t="str">
-        <v>船釣鐵板路線明確 / 從輕鐵到大物深場覆蓋清晰</v>
+        <v>路亞泛用取向 / 多場景適配</v>
       </c>
     </row>
     <row r="211">
@@ -12369,7 +12369,7 @@
         <v>25 STEEZ TRAVEL</v>
       </c>
       <c r="D211" t="str">
-        <v>Outrage XV J</v>
+        <v>25 STEEZ TRAVEL</v>
       </c>
       <c r="E211" t="str">
         <v/>
@@ -12384,7 +12384,7 @@
         <v>bass,旅行</v>
       </c>
       <c r="I211" t="str">
-        <v>https://www.daiwaseiko.com.tw/upload/product_m/twL_product_25C04_gcseavu6es.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1012_25_STEEZ_TRAVEL.jpg</v>
       </c>
       <c r="J211" t="str">
         <v/>
@@ -12408,10 +12408,10 @@
         <v>隆重介紹首款STEEZ多節竿，全新 Steez Travel 旅行竿來了！ 採用頂級元件並融合 DAIWA 最先進技術，為釣魚愛好者帶來前所未有的體驗。 釣魚旅行者不再需要為攜帶一本式釣竿的運輸問題而煩惱，無論是擔心運輸成本、損壞風險，或是不便攜帶的困擾。Steez Travel 旅行竿提供與一本式釣竿相同的整體手感與靈敏度，讓旅途中仍能享受高品質的釣魚體驗。 這款釣竿採用 DAIWA 頂級 SVF Nanoplus 碳纖維材料製成，該技術減少了樹脂含量，並均勻地分布於高密度碳纖維內。樹脂含量的降低使釣竿更加輕盈，提高靈敏度，而均勻的樹脂分佈則確保了竿身各部位的耐用性。 為了解決傳統多節釣竿常見的過節問題，DAIWA 採用了 V-JOINT 技術，確保各節之間的接點能夠與釣竿本體一同彎曲，讓整體受力與彈性均勻分佈，使其在拋投與搏魚時能夠擁有與一本竿相同的操控感與性能。 為了進一步提升釣者的成功率，Steez Travel 旅行竿提供 4 種針對特定技術的動作類型 以及 2 種多用途動作類型，可應對多種魚類與不同釣法，滿足各種需求。 作為一款頂歸多節釣竿，自然需要相應的頂級保護。全新 Steez Travel 旅行竿配備 時尚耐用的硬殼保護箱，尺寸設計完美適合隨身行李，讓您安心攜帶，無憂旅行！</v>
       </c>
       <c r="Q211" t="str">
-        <v>綜合路亞泛用</v>
+        <v>bass / 淡水泛用 / 便攜</v>
       </c>
       <c r="R211" t="str">
-        <v>路亞泛用取向 / 多場景適配</v>
+        <v>淡水路亞便攜路線明確 / 出行與多技法兼顧</v>
       </c>
     </row>
     <row r="212">
@@ -12425,7 +12425,7 @@
         <v>【2025.01追加】HEARTLAND LIBERALIST</v>
       </c>
       <c r="D212" t="str">
-        <v>25 STEEZ TRAVEL</v>
+        <v>HEARTLAND LIBERALIST</v>
       </c>
       <c r="E212" t="str">
         <v>2025</v>
@@ -12440,7 +12440,7 @@
         <v>bass,旅行</v>
       </c>
       <c r="I212" t="str">
-        <v>https://www.daiwaseiko.com.tw/upload/product_m/twL_product_25A06_avsst5fsku.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1013_HEARTLAND_LIBERALIST.jpg</v>
       </c>
       <c r="J212" t="str">
         <v/>
@@ -12481,7 +12481,7 @@
         <v>【2025.01追加】EMERALDAS STOIST ST (外導環款)</v>
       </c>
       <c r="D213" t="str">
-        <v>HEARTLAND LIBERALIST</v>
+        <v>EMERALDAS STOIST ST（OUT GUIDE MODEL）</v>
       </c>
       <c r="E213" t="str">
         <v>2025</v>
@@ -12496,7 +12496,7 @@
         <v>岸投</v>
       </c>
       <c r="I213" t="str">
-        <v>https://www.daiwaseiko.com.tw/upload/product_m/twL_product_25A06_pb9xk3nbyf.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1014_EMERALDAS_STOIST_ST.jpg</v>
       </c>
       <c r="J213" t="str">
         <v/>
@@ -12520,10 +12520,10 @@
         <v>迷人且妖豔的翡翠色雙眼 軟絲，擁有翡翠綠寶石般的雙眸，讓釣者們深深著迷。DAIWA推出了世界首創的專用品牌『Emeraldas』，專門用於頭足類的攻略。包括突破性的釣竿、主打PE線的捲線器，以及獨創的木蝦。所有這些嶄新的產品，利用其新穎性確立了花軟釣的基礎。其核心是對細節的堅持。DAIWA的開發團隊以及DAIWA自豪的測試員團隊，這些多才多藝的成員們堅持不懈地專注於花軟釣法，不斷追求進步。探索花軟釣的便利性與深度，探索這看似矛盾卻吸引人的魅力。為了見上翡翠色的雙眸而竭盡全力。 將山田測試員的木蝦理論具現化的軟絲竿顛峰之作 「STOIST ST（Stream Tune）」是一款相對於專注敏捷操作的 RT重視柔韌性的設計 ■搭載「AGS」導環(C環・N環) ■AGS使用 CWS 固定技術 ■配備DAIWA獨家原創的 AIR SENSOR 握把 ■前握柄短化設計藉此可指尖碰觸竿身，吸收、感受震動。 ■2025.01追加型號 70ＭＭＨ-S 針對南方地區（如沖繩）的船釣場景，設計用於對付目標「Red Monster」，為了精確捕捉微弱的魚訊竿尾雖然纖細，但是竿尾從比較重的船釣木蝦到木蝦+鉛的重量級調組都能對應。 能以強力的操竿動作靈活控制木蝦，擁有卓越的力量從深海中拉起怪物級的獵物。從剛開始時就對這個釣種十分講究的山田測試員所集大成之作。 「RT」與性格不同的新旗艦「ST」誕生 在介紹ST之前，首先想回顧RT的概念。RT是一根經過極致調整、能夠體驗輕盈與操作性極致的競速般調校竿。為此，我們選用了管狀結構與SVF編織X這種材料的組合。結果，高彈性竿身所帶來的敏銳與鋼硬的感覺，無疑讓這根竿子帶有一種仿若競速般的鋒利感。自從發售以來，得到了許多釣魚愛好者的支持。 然而，傳統STOIST系列的概念則是「在柔軟中擁有敏捷感」，這種感覺只有在柔韌的錐形設計、極細的SMT（SuperMetalTop）和MEGA TOP的搭配中才能體現。這一概念被完美延續並進化為ST「Stream Tune」。</v>
       </c>
       <c r="Q213" t="str">
-        <v>bass / 淡水泛用 / 便攜</v>
+        <v>木蝦 / 烏賊</v>
       </c>
       <c r="R213" t="str">
-        <v>淡水路亞便攜路線明確 / 出行與多技法兼顧</v>
+        <v>軟絲與岸拋木蝦路線明確 / 從入門到高階覆蓋清晰</v>
       </c>
     </row>
     <row r="214">
@@ -12537,7 +12537,7 @@
         <v>【2024.12追加】STEEZ (直柄款)</v>
       </c>
       <c r="D214" t="str">
-        <v>EMERALDAS STOIST ST（OUT GUIDE MODEL）</v>
+        <v>STEEZ（SPINNING MODEL）</v>
       </c>
       <c r="E214" t="str">
         <v>2024</v>
@@ -12552,7 +12552,7 @@
         <v>bass</v>
       </c>
       <c r="I214" t="str">
-        <v>https://www.daiwaseiko.com.tw/upload/product_m/twL_product_24K11_radidby4e2.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1015_STEEZ.jpg</v>
       </c>
       <c r="J214" t="str">
         <v/>
@@ -12576,10 +12576,10 @@
         <v>為了那些認真看待鱸魚釣的人們 DAIWA致力創造出的產品，與那些將鱸魚釣視為生活重心、認真看待鱸魚釣的人們產生共鳴。 這是DAIWA開發團隊將對鱸魚釣的熱忱，透過產品和訊息與大家分享的品牌理念具體化。為此，DAIWA憑藉其技術和熱情，嚴謹地打造出這些產品。這不僅僅只是釣竿與捲線器，而是將信念與驢魚釣友的熱情一同寄託在釣鱸魚所需要的一切物品……這就是「STEEZ」。 實釣至上主義 眼前豎立的障壁，是通往榮耀的路標。 為了遇見那條尚未見過的魚，釣者便勇敢地走上無人踏足的道路。 遊戲是生物，壓力被當作養分消化。 壓抑著鋒利的目光挑戰，當開辟新天地後，迎接的將是忘我般的熱狂與全新的境界。 勝利之神，隱匿於自己與細節之中。 2021年，層次更加豐富的STEEZ新篇章正式開啟。 去吧，用你的雙手書寫全新的一頁。</v>
       </c>
       <c r="Q214" t="str">
-        <v>木蝦 / 烏賊</v>
+        <v>淡水 Bass / 技法分工 / 软硬饵覆盖</v>
       </c>
       <c r="R214" t="str">
-        <v>軟絲與岸拋木蝦路線明確 / 從入門到高階覆蓋清晰</v>
+        <v>按子型号区分精细、卷阻、底操、cover 和大饵路线，适合依照钓组与作钓距离选型。</v>
       </c>
     </row>
     <row r="215">
@@ -12593,7 +12593,7 @@
         <v>【2024.12追加】STEEZ (槍柄款)</v>
       </c>
       <c r="D215" t="str">
-        <v>STEEZ（SPINNING MODEL）</v>
+        <v>STEEZ（BAITCASTING MODEL）</v>
       </c>
       <c r="E215" t="str">
         <v>2024</v>
@@ -12608,7 +12608,7 @@
         <v>bass</v>
       </c>
       <c r="I215" t="str">
-        <v>https://www.daiwaseiko.com.tw/upload/product_m/twL_product_24K11_45qz7zb5kp.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1016_STEEZ.jpg</v>
       </c>
       <c r="J215" t="str">
         <v/>
@@ -12632,10 +12632,10 @@
         <v>為了那些認真看待鱸魚釣的人們 DAIWA致力創造出的產品，與那些將鱸魚釣視為生活重心、認真看待鱸魚釣的人們產生共鳴。 這是DAIWA開發團隊將對鱸魚釣的熱忱，透過產品和訊息與大家分享的品牌理念具體化。為此，DAIWA憑藉其技術和熱情，嚴謹地打造出這些產品。這不僅僅只是釣竿與捲線器，而是將信念與驢魚釣友的熱情一同寄託在釣鱸魚所需要的一切物品……這就是「STEEZ」。 實釣至上主義 眼前豎立的障壁，是通往榮耀的路標。 為了遇見那條尚未見過的魚，釣者便勇敢地走上無人踏足的道路。 遊戲是生物，壓力被當作養分消化。 壓抑著鋒利的目光挑戰，當開辟新天地後，迎接的將是忘我般的熱狂與全新的境界。 勝利之神，隱匿於自己與細節之中。 2021年，層次更加豐富的STEEZ新篇章正式開啟。 去吧，用你的雙手書寫全新的一頁。</v>
       </c>
       <c r="Q215" t="str">
-        <v>bass / 淡水泛用</v>
+        <v>淡水 Bass / 技法分工 / 软硬饵覆盖</v>
       </c>
       <c r="R215" t="str">
-        <v>淡水路亞梯度完整 / 從技巧到泛用覆蓋清晰</v>
+        <v>按子型号区分精细、卷阻、底操、cover 和大饵路线，适合依照钓组与作钓距离选型。</v>
       </c>
     </row>
     <row r="216">
@@ -12649,7 +12649,7 @@
         <v>STEEZ Real Control</v>
       </c>
       <c r="D216" t="str">
-        <v>STEEZ（BAITCASTING MODEL）</v>
+        <v>STEEZ REAL CONTROL</v>
       </c>
       <c r="E216" t="str">
         <v>2024</v>
@@ -12664,7 +12664,7 @@
         <v>bass</v>
       </c>
       <c r="I216" t="str">
-        <v>https://www.daiwaseiko.com.tw/upload/product_m/twL_product_24K04_6ckpcrjmbg.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1017_STEEZ_Real_Control.jpg</v>
       </c>
       <c r="J216" t="str">
         <v/>
@@ -12705,7 +12705,7 @@
         <v>BLACK LABEL</v>
       </c>
       <c r="D217" t="str">
-        <v>STEEZ REAL CONTROL</v>
+        <v>BLACK LABEL</v>
       </c>
       <c r="E217" t="str">
         <v/>
@@ -12720,7 +12720,7 @@
         <v>bass</v>
       </c>
       <c r="I217" t="str">
-        <v>https://www.daiwaseiko.com.tw/upload/product_m/twL_product_24K01_zwv98rjinz.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1018_BLACK_LABEL.jpg</v>
       </c>
       <c r="J217" t="str">
         <v/>
@@ -12761,7 +12761,7 @@
         <v>OUTRAGE SJ</v>
       </c>
       <c r="D218" t="str">
-        <v>BLACK LABEL</v>
+        <v>OUTRAGE SJ</v>
       </c>
       <c r="E218" t="str">
         <v/>
@@ -12776,7 +12776,7 @@
         <v>船钓</v>
       </c>
       <c r="I218" t="str">
-        <v>https://www.daiwaseiko.com.tw/upload/product_m/twL_product_24K07_6razqj8j3t.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1019_OUTRAGE_SJ.jpg</v>
       </c>
       <c r="J218" t="str">
         <v/>
@@ -12800,10 +12800,10 @@
         <v>繼承了SALTIGA設計理念的高標準慢鐵竿。 繼承了旗艦款SALTIGA設計理念的高標準系列。 除了SALTIGA傳承的調性設計外，還在敏感度、操作性、強度和舒適性等慢鐵竿所需的性能上進行了高水平融合。最大限度提高竿子反彈力的X45全覆蓋技術，與圓型捲線器具有極佳相容性的新型ZERO SEAT，融合輕量性與力量的HVF NANO PLUS技術，追求極致調性的1PCS設計，外觀以黑色為主調，展現高級感，大幅提升質感。</v>
       </c>
       <c r="Q218" t="str">
-        <v>bass / 淡水泛用</v>
+        <v>船釣 / 鐵板 / 海水專項</v>
       </c>
       <c r="R218" t="str">
-        <v>淡水路亞梯度完整 / 從技巧到泛用覆蓋清晰</v>
+        <v>船釣鐵板路線明確 / 從輕鐵到大物深場覆蓋清晰</v>
       </c>
     </row>
     <row r="219">
@@ -12817,7 +12817,7 @@
         <v>LATEO (K)</v>
       </c>
       <c r="D219" t="str">
-        <v>OUTRAGE SJ</v>
+        <v>LATEO (K)</v>
       </c>
       <c r="E219" t="str">
         <v/>
@@ -12832,7 +12832,7 @@
         <v>海鲈,岸投</v>
       </c>
       <c r="I219" t="str">
-        <v>https://www.daiwaseiko.com.tw/upload/product_m/twL_product_24G10_j2k5q732n4.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1020_LATEO_K.jpg</v>
       </c>
       <c r="J219" t="str">
         <v/>
@@ -12856,10 +12856,10 @@
         <v>大幅提升標準釣竿水準的標準型號。 大幅提高飛距離和操作性的海鱸釣竿。 標準海鱸釣竿「LATEO」經歷了“革新”的進化。利用各種釣場和釣餌不同來展現釣法是釣海鱸的樂趣所在。為了實現這一點，竿身的高彈性化和細身化，以及握柄部分的剛性提高，使得投擲更加銳利。結合「CC GRIP」概念，提供精確且遙遠的投擲性能，使釣者能夠自由操作。這款竿具備高水準的基本款，不僅適合釣海鱸，也能應對多種目標魚種。</v>
       </c>
       <c r="Q219" t="str">
-        <v>船釣 / 鐵板 / 海水專項</v>
+        <v>海鱸 / 岸投 / 遠投</v>
       </c>
       <c r="R219" t="str">
-        <v>船釣鐵板路線明確 / 從輕鐵到大物深場覆蓋清晰</v>
+        <v>海鱸岸投路線完整 / 港灣河川到遠投場景覆蓋清晰</v>
       </c>
     </row>
     <row r="220">
@@ -12873,7 +12873,7 @@
         <v>EMERALDAS AIR</v>
       </c>
       <c r="D220" t="str">
-        <v>LATEO (K)</v>
+        <v>EMERALDAS AIR</v>
       </c>
       <c r="E220" t="str">
         <v/>
@@ -12888,7 +12888,7 @@
         <v>岸投</v>
       </c>
       <c r="I220" t="str">
-        <v>https://www.daiwaseiko.com.tw/upload/product_m/twL_product_24F25_34qed9hu2t.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1021_EMERALDAS_AIR.jpg</v>
       </c>
       <c r="J220" t="str">
         <v/>
@@ -12912,10 +12912,10 @@
         <v>迷人且妖豔的翡翠色雙眼 軟絲，擁有翡翠綠寶石般的雙眸，讓釣者們深深著迷。DAIWA推出了世界首創的專用品牌『Emeraldas』，專門用於頭足類的攻略。包括突破性的釣竿、主打PE線的捲線器，以及獨創的木蝦。所有這些嶄新的產品，利用其新穎性確立了花軟釣的基礎。其核心是對細節的堅持。DAIWA的開發團隊以及DAIWA自豪的測試員團隊，這些多才多藝的成員們堅持不懈地專注於花軟釣法，不斷追求進步。探索花軟釣的便利性與深度，探索這看似矛盾卻吸引人的魅力。為了見上翡翠色的雙眸而竭盡全力。 正如其名「AIR」，其輕量化已達到異次元的境界。 徹底追求輕量化的「EMERALDAS AIR」釣竿， 帶來了大幅度的感度提升和無疲勞的操作性， 使每一次拋竿和操竿都充滿快感。 此外，這種輕量化支持釣魚者從各個角度的動作， 顛覆了以往對輕量化的認識， 完成了一款真正讓人感受到「AIR」的釣竿。 ■更進一步輕量化的AIR系列： 86M型號實現了驚人的90克以下，即僅86克。 ■聯名款： 由岡隆之、木森直樹、福島芳宏等各領域的測試員監製的聯名款。 ■AGS導環： 導環採用『AGS』技術。 ■提升強度與輕量化的竿身： 竿身不僅輕盈，強度也因SVF Nano Plus技術而提高。 並且，最適結構X45防止扭轉，進一步提升操作性。 ■輕量且握力優秀的AIR SENSOR： 使用輕便且握力優越的AIR SENSOR(SLIM FIT)， 並採用向下鎖設計，讓食指可以直接接觸竿身。 ■V-JOINTα技術： 實現近乎一體式的操竿感受。 ■實心尾（-S）型號：配備細膩且高感度的MEGA TOP。</v>
       </c>
       <c r="Q220" t="str">
-        <v>海鱸 / 岸投 / 遠投</v>
+        <v>木蝦 / 烏賊</v>
       </c>
       <c r="R220" t="str">
-        <v>海鱸岸投路線完整 / 港灣河川到遠投場景覆蓋清晰</v>
+        <v>軟絲與岸拋木蝦路線明確 / 從入門到高階覆蓋清晰</v>
       </c>
     </row>
     <row r="221">
@@ -12929,7 +12929,7 @@
         <v>【2024.07追加】EMERALDAS STOIST RT</v>
       </c>
       <c r="D221" t="str">
-        <v>EMERALDAS AIR</v>
+        <v>EMERALDAS STOIST RT（OUT GUIDE MODEL）</v>
       </c>
       <c r="E221" t="str">
         <v>2024</v>
@@ -12944,7 +12944,7 @@
         <v>岸投</v>
       </c>
       <c r="I221" t="str">
-        <v>https://www.daiwaseiko.com.tw/upload/product_m/twL_product_24F24_bnfruixakm.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1022_EMERALDAS_STOIST_RT.jpg</v>
       </c>
       <c r="J221" t="str">
         <v/>
@@ -12985,7 +12985,7 @@
         <v>24 OVERTHERE</v>
       </c>
       <c r="D222" t="str">
-        <v>EMERALDAS STOIST RT（OUT GUIDE MODEL）</v>
+        <v>24 OVERTHERE</v>
       </c>
       <c r="E222" t="str">
         <v>2024</v>
@@ -13000,7 +13000,7 @@
         <v>岸投</v>
       </c>
       <c r="I222" t="str">
-        <v>https://www.daiwaseiko.com.tw/upload/product_m/twL_product_24F12_6qrs8cgsjw.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1023_24_OVERTHERE.jpg</v>
       </c>
       <c r="J222" t="str">
         <v/>
@@ -13024,10 +13024,10 @@
         <v>講究「遠投性與操作性」的多功能路亞竿標準系列 將竿身升級為輕量且高強度的HVF碳纖維，實現爽快的拋投體驗。 遠投性能和路亞控制性能得到提升。 由於竿身性能的提升和K型導環的配合，即使在逆風中反覆投擲也不易出現纏線問題。 隨著釣魚者的增多，逐漸高壓化的拋投中能比對手投得更遠。 精確的路亞操作讓你可以嚴謹地展開釣魚活動，因為不會發生問題就不會浪費時間。 這就是新的OVERTHERE，在釣遊中帶來巨大優勢。</v>
       </c>
       <c r="Q222" t="str">
-        <v>木蝦 / 烏賊</v>
+        <v>岸投 / 遠投 / 海鱸青物</v>
       </c>
       <c r="R222" t="str">
-        <v>軟絲與岸拋木蝦路線明確 / 從入門到高階覆蓋清晰</v>
+        <v>海水岸拋與遠投路線明確 / 大場景搜索覆蓋更強</v>
       </c>
     </row>
     <row r="223">
@@ -13041,7 +13041,7 @@
         <v>OUTRAGE BR LJ</v>
       </c>
       <c r="D223" t="str">
-        <v>24 OVERTHERE</v>
+        <v>OUTRAGE BR LJ</v>
       </c>
       <c r="E223" t="str">
         <v/>
@@ -13056,7 +13056,7 @@
         <v>船钓</v>
       </c>
       <c r="I223" t="str">
-        <v>https://www.daiwaseiko.com.tw/upload/product_m/twL_product_24F05_3w95kbp4y5.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1024_OUTRAGE_BR_LJ.jpg</v>
       </c>
       <c r="J223" t="str">
         <v/>
@@ -13080,10 +13080,10 @@
         <v>繼承了OUTRAGE系列的血統，以卓越實釣性能為傲的基礎輕型鐵板竿。 高度融合輕型鐵板所需性能的基礎機型。 竿身有高密度碳纖維HVF和X45結構的輔助， 具有高靈敏度且纖細， 同時也具備能應對突如其來的大物所需之力量。 ■通過X45提高搏魚性能和操作性 ■MEGA TOP實心尾能穩定的操晃鐵板，增加上鉤率（僅MEGA TOP 機型） ■追求輕量、高靈敏度和良好手感的Air Sensor捲座（僅限槍柄款式） ■如同一本竿般的V JOINT（僅兩本竿版本） ■輕量與力量的融合的HVF ■擁有兩種接合模式： 1.採用幾乎跟一本竿調子相同的一本半握把連接。 2.使用不易鬆脫轉動、高攜帶性的兩節式竿身。 ▲採用了不易鬆動或旋轉的接節構造 這使得即使在長時間的釣行中，也能夠放心使用。對於並繼二節竿可能出現的接合處鬆動或旋轉的問題，特別設計了接合結構，減少了尾一偏移的風險。</v>
       </c>
       <c r="Q223" t="str">
-        <v>岸投 / 遠投 / 海鱸青物</v>
+        <v>近海船拋 / 青物鮪魚</v>
       </c>
       <c r="R223" t="str">
-        <v>海水岸拋與遠投路線明確 / 大場景搜索覆蓋更強</v>
+        <v>近海大型目標路線明確 / 船拋與搏魚支撐更完整</v>
       </c>
     </row>
     <row r="224">
@@ -13097,7 +13097,7 @@
         <v>24 鏡牙 AIR</v>
       </c>
       <c r="D224" t="str">
-        <v>OUTRAGE BR LJ</v>
+        <v>24 鏡牙 AIR (KYOHGA AIR)</v>
       </c>
       <c r="E224" t="str">
         <v/>
@@ -13112,7 +13112,7 @@
         <v>船钓</v>
       </c>
       <c r="I224" t="str">
-        <v>https://www.daiwaseiko.com.tw/upload/product_m/twL_product_24F05_3s2sa3vjei.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1025_24_AIR.jpg</v>
       </c>
       <c r="J224" t="str">
         <v/>
@@ -13136,10 +13136,10 @@
         <v>讓船上的體驗更加愉快，真正的豐收。 專為白帶魚而打造的綜合品牌「鏡牙」。擁有像刀一樣鏡銀色身體，鋒利的牙齒，以及神秘的生態，與其他魚類完全不同。充分享受白帶魚的魅力。在這個理念下，通過深入的現場測試打造而成的產品。品牌標誌以尖銳牙齒為靈感。 鏡牙針對分佈於世界各地的海釣愛好者而設計，專門用於近海釣魚。其釣具的選擇範圍廣泛，從某種意義上來說，即使是流行的釣具也可能無法保證豐收。因此，鏡牙推出了專用的釣具，讓釣手在一整天的釣魚中可以輕鬆集中精力，無壓力地應對。這樣一來，看不見的世界將會展現在眼前。 各個品項其獨特個性都大放異彩，鐵板白帶竿 為了白帶魚鐵板釣法而開發的鏡牙系列高標準型號。 追求最適合白帶魚釣餌釣法的調子， 展現了專用竿所獨有的動作，同時實現以高通用性為傲， 無論是怎樣的白帶魚尺寸、鐵板重量或水深都適用的號數系列。 ■導環使用輕量化和高靈敏度的『AGS』導環 ■獨一無二的高靈敏度金屬尾（僅MT型號） ■竿身有防止扭曲的X45構造 ■超人氣的竿身超彎曲搏魚，搭載 MEGA TOP芯材的刺激釣遊 （僅TG） ■輕量和力量的融合 HVF Nano Plus ■實現理想的彎曲調性的一本半插節構造</v>
       </c>
       <c r="Q224" t="str">
-        <v>近海船拋 / 青物鮪魚</v>
+        <v>船釣 / 鐵板 / 海水專項</v>
       </c>
       <c r="R224" t="str">
-        <v>近海大型目標路線明確 / 船拋與搏魚支撐更完整</v>
+        <v>船釣鐵板路線明確 / 從輕鐵到大物深場覆蓋清晰</v>
       </c>
     </row>
     <row r="225">
@@ -13153,7 +13153,7 @@
         <v>【2024追加】OUTRAGE BR</v>
       </c>
       <c r="D225" t="str">
-        <v>24 鏡牙 AIR (KYOHGA AIR)</v>
+        <v>OUTRAGE BR</v>
       </c>
       <c r="E225" t="str">
         <v>2024</v>
@@ -13168,7 +13168,7 @@
         <v>岸投,船钓</v>
       </c>
       <c r="I225" t="str">
-        <v>https://www.daiwaseiko.com.tw/upload/product_m/twL_product_24F05_pn44nivdpp.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1026_OUTRAGE_BR.jpg</v>
       </c>
       <c r="J225" t="str">
         <v/>
@@ -13192,10 +13192,10 @@
         <v>輕鬆體驗近海船拋釣遊！基本款近海釣竿 儘管是基本款，但這款近海釣竿以優異的性能接近更高等級的款式，性價比極高，非常吸引人。 ■ 垂釣模式（J） 追求易於搖擺的垂釣模式。在戰鬥時，設計以減輕體力負擔為主，同時保留了足夠的提升力，實現最佳的錐形平衡。而旋轉模式則採用了氣感式捲線座，實現了輕量化，使您能夠在長時間的搖擺中不感到疲勞。這是一款超越基本級別的下一代垂釣竿。 ■ 拋投模式（C） 設計為一款在處理飛行距離、操作性等方面都能舒適應對的投擲竿，同時在戰鬥時，能夠減輕體力負擔，保留足夠的提升力，實現最佳的平衡。 ■ 輕拋投模式（LC） 針對瞄準1到2號PE線的鰤魚和中小型青魚等目標進行開發。適用於港口、海灣和近海地區常見的鐵板魚、小型浮潛、小型頂水塞、30到50克左右的鉤和刀片鉤等遠投、快速收捲。這款輕巧的投擲竿填補了傳統投擲竿和專業青魚投擲竿之間的空白。與普通的投擲竿不同，它採用了氣感式捲線座，實現了輕量化和操作性的追求。 追加品項-中量克數鐵板竿與大型船拋竿 ■J60B-5 J60B-5 適合PE4～5號、重量約200克±20克的鐵板，釣深度80～160米，適用於雙層流迅速的區域或瞄準深層的竿型。大幅度降低鐵板竿中魚時竿身張力所對人體帶來的負擔，同時藉由施加強勁的扭力平衡設計，使得在搏魚時能夠穩健地起魚。目標為10～15公斤級的大型青物，或使用更重的鐵板瞄準大型黃鰭鮪和長鰭鮪，同時也適用於阿兵哥釣法。 ■C83-6 C83-6 適合PE5～6號、長度約160～200mm的PLUG釣法，針對黃尾鰤或黃鰭鮪的標準竿型。對於即將開始釣黃尾鰤和黃鰭鮪的釣友來說非常推薦的竿款。 ■C82-8 C82-8 適合PE6～8號、長度超過200mm的PLUG釣法，瞄準大型黃尾鰤、黃鰭鮪和GT魚的高強度竿型。雖然是高力量等級，卻設定為柔軟調性，對體力沒有自信的釣友也能容易操作。</v>
       </c>
       <c r="Q225" t="str">
-        <v>船釣 / 鐵板 / 海水專項</v>
+        <v>近海船拋 / 青物鮪魚</v>
       </c>
       <c r="R225" t="str">
-        <v>船釣鐵板路線明確 / 從輕鐵到大物深場覆蓋清晰</v>
+        <v>近海大型目標路線明確 / 船拋與搏魚支撐更完整</v>
       </c>
     </row>
     <row r="226">
@@ -13209,7 +13209,7 @@
         <v>【2024追加】SALTIGA C (CASTING MODEL)</v>
       </c>
       <c r="D226" t="str">
-        <v>OUTRAGE BR</v>
+        <v>SALTIGA C (CASTING MODEL)</v>
       </c>
       <c r="E226" t="str">
         <v>2024</v>
@@ -13224,7 +13224,7 @@
         <v>船钓</v>
       </c>
       <c r="I226" t="str">
-        <v>https://www.daiwaseiko.com.tw/upload/product_m/twL_product_24F04_iu8eyrqmx6.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1027_SALTIGA_C_CASTING_MODEL.jpg</v>
       </c>
       <c r="J226" t="str">
         <v/>
@@ -13265,7 +13265,7 @@
         <v>24 HARDROCK X</v>
       </c>
       <c r="D227" t="str">
-        <v>SALTIGA C (CASTING MODEL)</v>
+        <v>24 HARDROCK X</v>
       </c>
       <c r="E227" t="str">
         <v>2024</v>
@@ -13280,7 +13280,7 @@
         <v>根钓,岸投</v>
       </c>
       <c r="I227" t="str">
-        <v>https://www.daiwaseiko.com.tw/upload/product_m/twL_product_24F04_xmsxk2t2zd.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1028_24_HARDROCK_X.jpg</v>
       </c>
       <c r="J227" t="str">
         <v/>
@@ -13304,10 +13304,10 @@
         <v>力量與操作性的魅力。HARDROCK釣魚的入門竿。 技術性高的魚餌操作和果斷開槍後的強力搏魚是岩魚魅力所在。 HARDROCK X藉由高度敏感度，感受誘餌敲底， 並緊密地用軟蟲餌探索根魚潛藏的區域。 當岩魚咬餌時，能用堅固的魚竿將其拉離礁岩區， 不讓魚有逃入岩石縫隙的機會。 ■BRADING X ■竿袋 DAIWA技術 ■BRAIDING X 透過將竿身最外層用碳纖維帶X形的纏繞，形成強化結構，以抑制在操作釣竿時可能導致的功率損失的捲曲。儘管纖維細緻，但確保高強度，並通過減少重心感的偏移提高了操作性。</v>
       </c>
       <c r="Q227" t="str">
-        <v>近海船拋 / 青物鮪魚</v>
+        <v>岩魚 / 海水路亞</v>
       </c>
       <c r="R227" t="str">
-        <v>近海大型目標路線明確 / 船拋與搏魚支撐更完整</v>
+        <v>結構區與硬底環境適配 / 岩魚路線明確</v>
       </c>
     </row>
     <row r="228">
@@ -13321,7 +13321,7 @@
         <v>DRAGGER X SLSJ</v>
       </c>
       <c r="D228" t="str">
-        <v>24 HARDROCK X</v>
+        <v>DRAGGER X SLSJ</v>
       </c>
       <c r="E228" t="str">
         <v/>
@@ -13336,7 +13336,7 @@
         <v>根钓,岸投</v>
       </c>
       <c r="I228" t="str">
-        <v>https://www.daiwaseiko.com.tw/upload/product_m/twL_product_24F04_gc286mcd4q.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1029_DRAGGER_X_SLSJ.jpg</v>
       </c>
       <c r="J228" t="str">
         <v/>
@@ -13360,10 +13360,10 @@
         <v>FINESSE加上青物！ 敏銳且強力的超級輕量岸拋鐵板竿 在岸拋鐵板竿系列「DRAGGER」中， 特別強化輕快操作性的超輕岸拋鐵板設計。 如鐵板竿的輕快操作性卻深藏不露， 蘊含豐沛的力量和強度，能夠應對青物等大型魚， 可以完全投出30克的鐵鉤。 其纖細的穗先即便使用0.6號細PE線也不易出現問題的設計， 可以將輕量的鐵板自在地探測，吸引青物和根魚。 作為入門款的X系列釣竿是主流且正統的調子。 易於抓取拋投時機以及操竿。</v>
       </c>
       <c r="Q228" t="str">
-        <v>岩魚 / 海水路亞</v>
+        <v>岸投 / 遠投 / 海鱸青物</v>
       </c>
       <c r="R228" t="str">
-        <v>結構區與硬底環境適配 / 岩魚路線明確</v>
+        <v>海水岸拋與遠投路線明確 / 大場景搜索覆蓋更強</v>
       </c>
     </row>
     <row r="229">
@@ -13377,7 +13377,7 @@
         <v>DRAGGER SX SLSJ</v>
       </c>
       <c r="D229" t="str">
-        <v>DRAGGER X SLSJ</v>
+        <v>DRAGGER SX SLSJ</v>
       </c>
       <c r="E229" t="str">
         <v/>
@@ -13392,7 +13392,7 @@
         <v>根钓,岸投</v>
       </c>
       <c r="I229" t="str">
-        <v>https://www.daiwaseiko.com.tw/upload/product_m/twL_product_24F04_kfmv2uwbvx.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1030_DRAGGER_SX_SLSJ.jpg</v>
       </c>
       <c r="J229" t="str">
         <v/>
@@ -13433,7 +13433,7 @@
         <v>23 WILDERNESS X</v>
       </c>
       <c r="D230" t="str">
-        <v>DRAGGER SX SLSJ</v>
+        <v>23 WILDERNESS X</v>
       </c>
       <c r="E230" t="str">
         <v/>
@@ -13448,7 +13448,7 @@
         <v>bass,旅行</v>
       </c>
       <c r="I230" t="str">
-        <v>https://www.daiwaseiko.com.tw/upload/product_m/twL_product_25C27_34utshix3d.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1031_23_WILDERNESS_X.jpg</v>
       </c>
       <c r="J230" t="str">
         <v/>
@@ -13472,10 +13472,10 @@
         <v>最泛用的平價多節竿強勢登場！ 最泛用的平價多節竿強勢登場，設定上為最適合初學者及一般釣友拋投及操作的7呎長度， 並採用多項DAIWA先進技術，無論是在重量、強度、感度和過節表現上都能在作釣時感受到無比的安心感， 並繼5節的設計讓釣友方便攜帶，摺疊收納後僅有48公分，即使騎乘摩托車也可以方便的移動到釣場，避免難以攜帶的問題， 一把創造無限自由的路亞竿登場！</v>
       </c>
       <c r="Q230" t="str">
-        <v>岸投 / 遠投 / 海鱸青物</v>
+        <v>淡海水泛用 / 入門</v>
       </c>
       <c r="R230" t="str">
-        <v>海水岸拋與遠投路線明確 / 大場景搜索覆蓋更強</v>
+        <v>入門泛用路線明確 / 多場景基礎作釣覆蓋較廣</v>
       </c>
     </row>
     <row r="231">
@@ -13489,7 +13489,7 @@
         <v>EMERALDAS X</v>
       </c>
       <c r="D231" t="str">
-        <v>23 WILDERNESS X</v>
+        <v>EMERALDAS X</v>
       </c>
       <c r="E231" t="str">
         <v/>
@@ -13504,7 +13504,7 @@
         <v>岸投</v>
       </c>
       <c r="I231" t="str">
-        <v>https://www.daiwaseiko.com.tw/upload/product_m/twL_product_24D26_c48xugrpgs.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1032_EMERALDAS_X.jpg</v>
       </c>
       <c r="J231" t="str">
         <v/>
@@ -13528,10 +13528,10 @@
         <v>製品特徴 ■ 基本性能占比較高的高性價比花軟釣竿款 ■ 透過Braiding X進行補強 ■ 選用了高端產品中常見的FUJI VSS捲線座 ■BRAIDING X 透過將竿身最外層用碳纖維帶X形的纏繞，形成強化結構，以抑制在操作釣竿時可能導致的功率損失的捲曲。儘管纖維細緻，但確保高強度，並通過減少重心感的偏移提高了操作性。</v>
       </c>
       <c r="Q231" t="str">
-        <v>淡海水泛用 / 入門</v>
+        <v>木蝦 / 烏賊</v>
       </c>
       <c r="R231" t="str">
-        <v>入門泛用路線明確 / 多場景基礎作釣覆蓋較廣</v>
+        <v>軟絲與岸拋木蝦路線明確 / 從入門到高階覆蓋清晰</v>
       </c>
     </row>
     <row r="232">
@@ -13545,7 +13545,7 @@
         <v>EMERALDAS MX</v>
       </c>
       <c r="D232" t="str">
-        <v>EMERALDAS X</v>
+        <v>EMERALDAS MX</v>
       </c>
       <c r="E232" t="str">
         <v/>
@@ -13560,7 +13560,7 @@
         <v>岸投</v>
       </c>
       <c r="I232" t="str">
-        <v>https://www.daiwaseiko.com.tw/upload/product_m/twL_product_24D26_eeb3eewime.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1033_EMERALDAS_MX.jpg</v>
       </c>
       <c r="J232" t="str">
         <v/>
@@ -13601,7 +13601,7 @@
         <v>BLACK LABEL TRAVEL</v>
       </c>
       <c r="D233" t="str">
-        <v>EGING X</v>
+        <v>BLACK LABEL TRAVEL</v>
       </c>
       <c r="E233" t="str">
         <v/>
@@ -13616,7 +13616,7 @@
         <v>bass,旅行</v>
       </c>
       <c r="I233" t="str">
-        <v>https://www.daiwaseiko.com.tw/upload/product_m/twL_product_21D13_4kitku3igp.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1035_BLACK_LABEL_TRAVEL.jpg</v>
       </c>
       <c r="J233" t="str">
         <v/>
@@ -13640,10 +13640,10 @@
         <v>BLACK LABEL TRAVEL ■NEON C63MH-5・FR 【NEON LIMITED・FROG SPECIAL】 便於攜帶的短竿FROG特仕竿款｡承襲BLX的Extre先調子設計思維,融合了應對全尺寸Frog擬餌的易拋投性,能做出極具誘魚力之Frog泳姿的易操作性,以及不讓出主導權給大物的手把節竿身力量,強力壓制獵物｡在鱸魚釣遊時,除了Frog擬餌或重視操控性的硬質路亞之外,連使用鐵板､軟蟲釣組時也能自動地做出滯線,是把能提升釣果的竿款｡除了鱸魚之外,針對底棲魚類或是競艇海鱸釣遊也能以高次元的水準來應對｡ ■C66M-5 【VERSATILE SPECIAL】 以高次元的水準應對所有路亞的萬用特仕竿款｡承襲BLX的先調子設計思維,完美融合了易拋投性､感度､以及不讓出主導權給大物的手把節竿身力量,強力壓制獵物｡確保水表系路亞及米諾等操控系路亞的操控性,軟蟲釣法所要求的感度自不在話下,在移動式路亞釣法中也能自動地做出滯線,是把能提升釣果的竿款｡除了鱸魚之外,針對底棲魚類,競艇海鱸釣遊,青物等也都能對應｡ ■C70MH-5 【POWER VERSATILE SPECIAL】 能對應各種重量級路亞的力量萬用特仕竿款｡承襲BLX的Regular先調子設計思維,融合了應對各種路亞的易拋投性､感度､以及不讓出主導權給大物的手把節竿身力量,強力壓制獵物｡在鱸魚釣遊時,除了鐵板､軟蟲釣法之外,使用顫泳型路亞也能自動地做出滯線,是把能提升釣果的竿款｡除了鱸魚之外,針對底棲魚類或是競艇海鱸釣遊也能以高次元的水準來應對｡ ■C73H-5 【WORLD WIDE VERSATILE】 強力特仕竿款,除了日本國內的鱸魚戰,也能以高次元應對在海外的終極大物釣遊｡承襲BLX先調子設計思維,完美融合在獵物對重型路亞不感興趣時,還能投其所好改以輕量路亞作戰的竿尾設計與易操作性,感度以及不讓出主導權給大物的手把節竿身力量,強力壓制獵物｡操控軟蟲時所需的感度自不在話下,能自動地做出滯線的調性,無論是大型路亞或操控型路亞都能輕鬆捲收滯線,除了鱸魚之外,也能與終極大物一較高下的強力竿款｡ ■C61XXH-5・SB 【MONSTER FISH CUSTOM】 SB竿款(Swim Bait/Big Bait),可搭配至10oz､的軟質魚型路亞､大型路亞｡承襲BLX先調子的設計思維,可精準地執行旋轉竿尾的拋竿技巧｡面對超短距離或是突然咬餌的情況時也能巧妙地掌握做合的時機,以強韌的竿身及手把節力量攻擊,掌控主導權｡除了軟質魚型路亞與大型路亞之外,也能搭配顫泳型路亞､大型鉛筆或鋼絲路亞都能搭配,是把實力深不可測的竿款｡除了鱸魚之外,跟全世界的怪魚對峙時,都可以用上這款超強力短竿｡ ■C64XH-5・SB【MONSTER FISH CUSTOM】 SB竿款(Swim Bait/Big Bait),可搭配至60oz､的軟質魚型路亞､大型路亞｡承襲BLX的Regular先調子的設計思維,竿身雖短卻具備遠投性能,完美融合搭配包含重量級路亞在內,針對所有路亞的易拋投性,操控性,以及不讓出主導權給大物的手把節竿身力量,強力壓制獵物｡不只軟質魚型路亞､大型路亞,也能搭配顫泳型路亞､大型鉛筆或鋼絲路亞,Frog擬餌等,是把實力深不可測的竿款｡一竿在手,鱸魚自不在話下,是能以一把之力挑戰世界各地之怪物大魚的強力短竿｡ ■S66L-5【VERSATILE SPECIAL】 以高次元的水準應對所有路亞的萬用特仕竿款｡承襲BLX先調子設計思維,完美融合了易拋投性､操作性､感度､以及不讓出主導權給大物的手把節竿身力量,強力壓制獵物｡不但確保水面系路亞與顫泳型路亞等操作系路亞的操控性,也兼顧了回捲時利用水花的泳姿操控｡軟蟲釣法所需的感度自不在話下,更能自動地做出滯線,提高咬餌的機,是把能確實提升釣果的竿款｡除了鱸魚之外,針對底棲魚類､競艇海鱸釣遊､青物等也都能對應｡</v>
       </c>
       <c r="Q233" t="str">
-        <v>木蝦 / 烏賊</v>
+        <v>bass / 淡水泛用 / 便攜</v>
       </c>
       <c r="R233" t="str">
-        <v>軟絲與岸拋木蝦路線明確 / 從入門到高階覆蓋清晰</v>
+        <v>淡水路亞便攜路線明確 / 出行與多技法兼顧</v>
       </c>
     </row>
     <row r="234">
@@ -13657,7 +13657,7 @@
         <v>月下美人</v>
       </c>
       <c r="D234" t="str">
-        <v>CROSSFIRE</v>
+        <v>月下美人</v>
       </c>
       <c r="E234" t="str">
         <v/>
@@ -13672,7 +13672,7 @@
         <v>岸投</v>
       </c>
       <c r="I234" t="str">
-        <v>https://www.daiwaseiko.com.tw/upload/product_m/twL_product_20C24_5cauqyn8fx.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1038_main.jpg</v>
       </c>
       <c r="J234" t="str">
         <v/>
@@ -13696,10 +13696,10 @@
         <v>月下美人 更高一級的輕巧､更上一層的操控性｡無備平鮋入門竿款｡ ■610L-S 活躍於低提防與小型磯場實心竿尾短竿款｡好操控､便於施展細緻技巧,從使用輕量汲鉤頭釣組或小型栓型路亞的夜釣,到運用釣竿進行細微地路亞操控誘導獵物的日間攻防,無一不適用｡船釣也可以派上用場｡ ■76L-T 高反饋竿款,高操控性空心竿尾設計｡栓型路亞､5g漂浮釣組的操作都能得心應手｡調性不刁鑽,鐵板路亞､汲鉤頭釣組也都合用｡重視咬鉤力的調性､上鉤後將力量分散至胴部,推薦給想避免魚逃脫的釣友｡ ■83M-T 超強力竿款｡在小型磯場､沙灘､圓石岸等釣點,搭配較重的汲鉤頭釣組､漂浮釣組､大型栓型路亞,獵捕藏身於浪高流急處､水域底層的大型無備平鮋｡不只無備平鮋,配合釣點位置還能攻略海鱸､黑鯛｡ 日本官網</v>
       </c>
       <c r="Q234" t="str">
-        <v>淡海水泛用 / 入門</v>
+        <v>轻海水 / Ajing・Mebaring / 港湾精细</v>
       </c>
       <c r="R234" t="str">
-        <v>入門泛用路線明確 / 多場景基礎作釣覆蓋較廣</v>
+        <v>以轻量 jighead、小软饵和 micro plug 为核心，适合港湾、堤防和小型岩礁的细线控饵。</v>
       </c>
     </row>
     <row r="235">
@@ -13713,7 +13713,7 @@
         <v>CROSSBEAT SW</v>
       </c>
       <c r="D235" t="str">
-        <v>月下美人</v>
+        <v>CROSSBEAT SW</v>
       </c>
       <c r="E235" t="str">
         <v/>
@@ -13728,7 +13728,7 @@
         <v>岸投,旅行</v>
       </c>
       <c r="I235" t="str">
-        <v>https://www.daiwaseiko.com.tw/upload/product_m/twL_product_21D14_rwpvy6965f.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1039_CROSSBEAT_SW.jpg</v>
       </c>
       <c r="J235" t="str">
         <v/>
@@ -13752,10 +13752,10 @@
         <v>CROSSBEAT SW 適合日常的閒暇或者旅行等，方便攜帶的小繼振出路亞竿。6種型號基本網羅了最近人氣暴漲的海上路亞的需求。導環是可安心使用的SIC導環。 ■666TUL 最適合釣竹莢魚和鮶魚，能使用輕型軟蟲做出細微動作從而引誘上魚。 ■746TUL 能遠投輕餌的鮶魚用長款竿。 也能對應竹莢魚。 ■766TML 適合堤防釣鱸魚使用， 也適用於河中釣黑鯛 ■836TML 能很順暢的完成拋竿和抽竿的動作。 最適合木蝦釣法和WIND釣法。 ■907TM 搭載強力手把節，能遠投重型米諾和VIB的海鱸竿。 ■967TMH 最適合小型青背魚和比目魚。能將金屬JIG遠擲並且抽竿的設計。</v>
       </c>
       <c r="Q235" t="str">
-        <v>輕型海水 / 精細</v>
+        <v>淡海水泛用 / 便攜</v>
       </c>
       <c r="R235" t="str">
-        <v>竹莢魚與根魚小餌路線明確 / 感度與操作性取向清晰</v>
+        <v>小繼振出便攜路線明確 / 輕海水到岸拋覆蓋較廣</v>
       </c>
     </row>
     <row r="236">
@@ -13769,7 +13769,7 @@
         <v>IPRIMI</v>
       </c>
       <c r="D236" t="str">
-        <v>CROSSBEAT SW</v>
+        <v>IPRIMI</v>
       </c>
       <c r="E236" t="str">
         <v/>
@@ -13784,7 +13784,7 @@
         <v>溪流,旅行</v>
       </c>
       <c r="I236" t="str">
-        <v>https://www.daiwaseiko.com.tw/upload/product_m/twL_product_20C24_zkzd5dtzaf.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1040_IPRIMI.jpg</v>
       </c>
       <c r="J236" t="str">
         <v/>
@@ -13808,10 +13808,10 @@
         <v>以想更享受釣鱒魚的想法為出發點產生的基本釣竿款。黑色中輝映出鮮豔的橘色提振釣友的心。良好的拋竿感、靈活傳達路亞移動的感度可柔軟的捕獲魚類。為享受管理池釣的您作出的所有動作提供最佳輔助。 日本官網</v>
       </c>
       <c r="Q236" t="str">
-        <v>淡海水泛用 / 便攜</v>
+        <v>鱒魚 / 管釣</v>
       </c>
       <c r="R236" t="str">
-        <v>小繼振出便攜路線明確 / 輕海水到岸拋覆蓋較廣</v>
+        <v>管理釣場鱒魚路線明確 / 輕量精細更友好</v>
       </c>
     </row>
     <row r="237">
@@ -13825,7 +13825,7 @@
         <v>WIND X</v>
       </c>
       <c r="D237" t="str">
-        <v>IPRIMI</v>
+        <v>WIND X</v>
       </c>
       <c r="E237" t="str">
         <v/>
@@ -13840,7 +13840,7 @@
         <v/>
       </c>
       <c r="I237" t="str">
-        <v>https://www.daiwaseiko.com.tw/upload/product_m/twL_product_20C24_fynxqm67wx.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1041_WIND_X.jpg</v>
       </c>
       <c r="J237" t="str">
         <v/>
@@ -13864,10 +13864,10 @@
         <v>裝備BRAIDING X竿節，能承受強力扭轉力道並延伸飛行距離。配備SiC Top導環能有效減輕母線負擔。纖細握把更好持竿，竿尾可對應較大動作的晃餌，新手極佳入門竿款。 日本官網</v>
       </c>
       <c r="Q237" t="str">
-        <v>鱒魚 / 管釣</v>
+        <v>岸投 / WIND / 白帶魚</v>
       </c>
       <c r="R237" t="str">
-        <v>管理釣場鱒魚路線明確 / 輕量精細更友好</v>
+        <v>岸拋 WIND 路線明確 / 入門友好且操作節奏清晰</v>
       </c>
     </row>
     <row r="238">
@@ -13881,7 +13881,7 @@
         <v>月下美人 MX MOBILE</v>
       </c>
       <c r="D238" t="str">
-        <v>WIND X</v>
+        <v>月下美人 MX MOBILE</v>
       </c>
       <c r="E238" t="str">
         <v/>
@@ -13896,7 +13896,7 @@
         <v>岸投,旅行</v>
       </c>
       <c r="I238" t="str">
-        <v>https://www.daiwaseiko.com.tw/upload/product_m/twL_product_20C24_qbri79a5e9.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1042_MX_MOBILE.jpg</v>
       </c>
       <c r="J238" t="str">
         <v/>
@@ -13920,10 +13920,10 @@
         <v>配備了正統竿材的竹莢魚&amp;無備平鮋便攜型竿款｡</v>
       </c>
       <c r="Q238" t="str">
-        <v>岸投 / WIND / 白帶魚</v>
+        <v>輕型海水 / 精細</v>
       </c>
       <c r="R238" t="str">
-        <v>岸拋 WIND 路線明確 / 入門友好且操作節奏清晰</v>
+        <v>竹莢魚與根魚小餌路線明確 / 感度與操作性取向清晰</v>
       </c>
     </row>
     <row r="239">
@@ -13937,7 +13937,7 @@
         <v>HEARTLAND (BAITCASTING MODEL)</v>
       </c>
       <c r="D239" t="str">
-        <v>月下美人 MX MOBILE</v>
+        <v>HEARTLAND (BAITCASTING MODEL)</v>
       </c>
       <c r="E239" t="str">
         <v/>
@@ -13952,7 +13952,7 @@
         <v>bass</v>
       </c>
       <c r="I239" t="str">
-        <v>https://www.daiwaseiko.com.tw/upload/product_m/twL_product_20C24_ggq85nvbqy.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1043_HEARTLAND_BAITCASTING_MODEL.jpg</v>
       </c>
       <c r="J239" t="str">
         <v/>
@@ -13976,10 +13976,10 @@
         <v>■HL 651M/MHRB-RR17 【REAL VERSATILE】 以Neko釣組為首,從Bait Finesse、10z.級的大型Bait或Wake Bait釣組只要這一把釣竿就足夠,具體實現不僅是甩投容易,更具備高靈敏度的竿款,利用DAIWA的感性領域設計系統「ESS」而完成的竿款。 ‧感性領域設計系統「ESS」/X45(=X扭矩)/高密度HVF碳纖/全鈦框SiC導環/竿袋 ■HL 6101MRB-18Heartland 表示將製作可用於全國各地的多功能釣竿,而這即為解答。在Heartland的系列作品中,以所支援的疾風/白疾風/疾風MH的調子平衡來降強度,將管狀設計改為先調子竿設計。由村上晴彥和Heartland設計的調子已經成為村上色調,從竿尾節到手把的弧度形成了一條不動的曲線,是徹底考量到如何使用路亞擬餌來捕捉獵物的款式。 ​​​​​​‧感性領域設計系統「ESS」/X45(=X扭矩)/3DX /HVF nano Plus全鈦框SiC導環/竿袋 ■HL 6101H/XHFB-RR17 【EXTRA HEAVY VERSATILE】 適用範圍中包含岸釣中使用大型Bait的最大級尺寸(40z級)重擊穿越水草區到經常使用的5g輕量刑德州釣組或Punch shot系釣組都能使用,兼具纖細度竿款。以Rod&amp;Reel雜誌讀者提出的意見為基礎利用DAIWA的最先端技術打造而成的竿款。 ‧感性領域設計系統「ESS」/X45(=X扭矩)/3DX/HVF全鈦框SiC導環/竿袋 ■722ML+FB-ST20 鱸釣世界常有的獨自創意持續派生出新釣法的HEARTLAND 20款，就是722ML+FB-ST20。 ■722MRB-20 鱸釣世界常有的獨自創意持續派生出新釣法的HEARTLAND 20款，就是722MRB-20。以軟疾風概念1/4oz.Class的Rubber Jig為主的體現村上流派微物餌的第二代·3(···)為基準，把當今作為獨立分類而存在的Small Rubber最初公諸於世的村上晴彥，以PEPERFORMANC概念精髓、DAIWA最先端技術，創造了現在的Small Rubber釣竿。融合了第二代·3沒有的遠投性能和Stroke機能。在Tubula Power Slim的中心切割2PCS的設計上，搭載了HEARTLAND傳統的鯽魚竿結合方式和V-Joint，呈現出不遜於獨節竿的完美弧度的村上調性。 ​​​​​​​‧感度領域設計系統「ESS」/X45（=X扭矩）/3DX/MegaTop/HVF nanoplus/V-joint/AirSensor Seat（感度型）/TUBULAPOWERSLIM/All Titanium Frame/SiC Guide/竿袋 ■HL 722MHRB-19 以HEARTLAND歷代作品中受到極高支持的04白疾風和07白疾風為原型,並將主素材從HVF昇華成HVF nanoplus,為TUBULAR SUPER SLIM的2 PIECES規格。搭載HEARTLAND和V-Joint,描繪出絲毫不遜色於1本竿的漂亮彎曲曲線的村上調子。除了無鉛釣組、德州釣組以及RUBBERJIG之外,也可對應顫泳釣組、搖擺路亞、米諾等,和04&amp;07白疾風的設定上有所分別。 ​​​​​​​‧感度領域設計系統「ESS」/X45(=X扭矩)/3DX/HVF nanoplus / V-JointTUBULARPOWERSLIM/全鈦框SiC導環/竿袋 ■HL 721HRB-18HL 721HRB-18 是一款結合了具疾風、疾風七貳Type-E血統的Daiwa最先端技術與村上晴彥開發的釣竿。在較少玻璃區域遮蔽範圍中,為了能最大限度地發揮路亞擬餌的操作性,將竿尾端保持精巧的設計,搭載具備能夠抑制扭力的X45與可快速回復原狀的3DX,使釣竿在投餌及拉鈎時可以抑制由於扭力所造成的功率強度損失,另外,藉由3DX的輔助,可以提升遠投性能。由村上晴彥和Heartland設計的調子已經成為村上色調,從竿尾節到手把的弧度形成了一條不動的曲線,是徹底考量到如何使用路亞擬餌來捕捉獵物的款式。 ​​​​​​​‧感性領域設計系統「ESS」/X45(=X扭矩)/3DX /HVF nanoplusV-JOINT/全鈦框SiC導環/竿袋 ■HL 742HRB-SV12 【疾風 BIWAKO SPEC.】 吸取海濱特別的血統以「為了飛得更遠」為主要目的,注入了最先進技術的超遠投2節竿。在攻略廣闊的水域時把路亞極限遠拋出去再把魚給拉上岸的琵琶湖專用竿。SVF COMPILE-X X45(=X扭矩) /V-JOINT/MAGNUM TAPERTUBULARPOWERSLIM/全鈦框SiC導環/竿袋把當今作為獨立分類而存在的Small Rubber最初公諸於世的村上晴彥，以PEPERFORMANC概念精髓、DAIWA最先端技術，創造了展現當今村上流派微物餌風尚的Small Rubber釣竿。與以往HEARTLAND不同的是，以硬質高彈性的MegaTop實心竿稍和中空力量纖細的細長厚壁材質，可實現微物餌的輕盈做釣。此外，作品HEARTLAND實現了從未有過的柔與剛這兩個相反要素的完美結合。 ‧感度領域設計系統「ESS」/X45（=X扭矩）/3DX/MegaTop/HVF nanoplus/V-joint/AirSensor Seat（感度型）/TUBULAPOWERSLIM/All Titanium Frame/SiC Guide/竿袋 日本官網</v>
       </c>
       <c r="Q239" t="str">
-        <v>輕型海水 / 精細</v>
+        <v>bass / 淡水泛用</v>
       </c>
       <c r="R239" t="str">
-        <v>竹莢魚與根魚小餌路線明確 / 感度與操作性取向清晰</v>
+        <v>淡水路亞梯度完整 / 從技巧到泛用覆蓋清晰</v>
       </c>
     </row>
     <row r="240">
@@ -13993,7 +13993,7 @@
         <v>AIREDGE MOBILE</v>
       </c>
       <c r="D240" t="str">
-        <v>HEARTLAND (BAITCASTING MODEL)</v>
+        <v>AIREDGE MOBILE</v>
       </c>
       <c r="E240" t="str">
         <v/>
@@ -14008,7 +14008,7 @@
         <v>bass,旅行</v>
       </c>
       <c r="I240" t="str">
-        <v>https://www.daiwaseiko.com.tw/upload/product_m/twL_product_20C24_pdw4kgzy7h.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1044_AIREDGE_MOBILE.jpg</v>
       </c>
       <c r="J240" t="str">
         <v/>
@@ -14032,10 +14032,10 @@
         <v>■664MLB 此竿為具有強韌竿身的輕型強力路亞竿。進攻躲藏在高低差較大的礁石區以及淺灘障礙區，出眾的敏感度可適用於軟蟲釣組及軟蟲汲鉤頭，輕拋投的高比重無鉛釣組、小型CRANK、3/8盎司左右的硬餌以及複合式旋轉亮片。 ■664M/MLB 使用鉛錘時整體呈現均衡受力調性，低負擔且快速的萬用竿。搭配FINESSE釣組後更易於作釣，即使緊湊的晃餌也能保持拋投精準度。除了快速沉底及輕德州釣組之外，也適合3/8盎司～1/2盎司的CRANKS或旋轉亮片，甚至11公分左右的SHARK。 ■694HB-SBS 調大型餌理想專用竿，適合搭配多節大型餌與搖擺餌，強韌又具彎曲度的S調性。搭配大型餌、搖擺餌、CRANKS可呈現出具引誘性的動作。透過慢速擺動也能達到拋投效果並順暢地送達目標點。不僅是大型餌，也適合PLUG及軟蟲RubberJig，輕鬆一舉突破障礙區。 ■6104MB 近距離及遠投都能對應的泛用竿型。路亞的重量確實透過竿子拋至目標點，能同時達到精準及遠距拋投。性能優異，硬餌可對應1/4盎司～5/8盎司。強硬適中的中肚～本節配合鋼絲餌以及德州釣組、輕鐵板等障礙區皆能一舉突破，任誰皆能駕馭的必備用竿。 ■6104MHB 各種路亞都能夠愉快配合的強力泛用竿型。路亞的重量確實透過竿子拋至目標點，能達到遠距離拋投的泛用F調性。具有直達手心的感度以及迴避障礙的能力，配合德州釣組以及軟蟲RubberJig釣組能一擊突破障礙。透過慢捲搭配1/2盎司以上的旋轉亮片，及搖擺餌的效果，釣遊魅力無法擋。 ■644UL/LS 竿尾為強力的「UL」調性，本節採用「L」調設計的FITNESS SPIN。配備了柔軟的竿尾與強韌中肚的EXTRA F調，在急流場合使用NEKO釣組、軟蟲汲鉤頭、倒吊釣組等也都能展現細膩的操作，是所有輕釣組的基本竿款。 ■644L/MLS-ST 「L」調採用MEGA TOP實心竿尾，本節為「ML」空心竿體，是MEGA TOP高感度實心竿尾的輕量化版。使用較大抵抗的釣組也能輕鬆掌握就餌狀態，細膩度倍增，更具備了閃避障礙物的能力，以及操作性、遠投性優異等相反元素。即使是需要快速回捲的SHAD擬餌也能穩定配合。 ■664ML/LS 竿尾採用「ML」調性，本節採用「L」調設計的FINESSE泛用型。採用高硬度竿尾的F調設計更能對應障礙區的掙脫，除了適用於各式釣組外，也適合SHAD類的小型硬餌。 ■684ML＋SML的升級款ML+強力FINESSE型。 配合重型FLAT攻略障礙區周圍以及大型湖泊或較深潛的擬餌攻略魚礁區域，也可對應大尺寸軟蟲，竿尖對於抵抗釣組的作用力以及障礙區、礁岩區等具有毫不遜色的實力，可達成最佳的操控。一旦上鉤就能靠著強勁的竿身力量一口氣讓對手投降。 日本官網</v>
       </c>
       <c r="Q240" t="str">
-        <v>bass / 淡水泛用</v>
+        <v>bass / 淡水泛用 / 便攜</v>
       </c>
       <c r="R240" t="str">
-        <v>淡水路亞梯度完整 / 從技巧到泛用覆蓋清晰</v>
+        <v>淡水路亞便攜路線明確 / 出行與多技法兼顧</v>
       </c>
     </row>
     <row r="241" xml:space="preserve">
@@ -36030,7 +36030,7 @@
         <v>岸投</v>
       </c>
       <c r="I630" t="str">
-        <v>https://www.daiwaseiko.com.tw/upload/product_m/twL_product_24D26_3k6be9jtvs.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1034_EGING_X.jpg</v>
       </c>
       <c r="J630" t="str">
         <v/>
@@ -36054,10 +36054,10 @@
         <v>岸拋花軟釣的入門款式 1.作為初次嘗試岸拋花軟釣的初學者的首選款式，事注重易用性的入門款。 2.本作具有4種不同型號。 3.竿身部分使用Braiding X，以加固竿身的彈性感，讓使用上更加順暢並降低擺動。 4.捲座採用岸拋花軟釣中常見的FUJI VSS。 ■捲座 在岸拋花軟釣中廣泛使用的VSS捲線座。 ■塗裝部分 在「EGING X」字樣周圍採用綠色塗裝，令人聯想到花軟的眼睛顏色。 ■ 導環 使用不容易纏線的不鏽鋼框導環。 產品特徵 "Eging X" 是為了想要輕鬆開始岸拋花軟釣的人而推薦的初學者入門型號。儘管是入門款，竿身部分採用了用碳纖交叉編織的 "Braiding X"，確保了輕快的投擲和岸拋花軟釣的基本性能，包括靈活的投擲和操作。 ■Braiding X 通過使用碳纖將竿身的最外層呈X形纏緊，以抑制在操作釣竿時可能導致力量損失的強化結構。輕薄但確保高強度，重量減輕，提高了操作性。</v>
       </c>
       <c r="Q630" t="str">
-        <v/>
+        <v>木蝦 / 烏賊</v>
       </c>
       <c r="R630" t="str">
-        <v/>
+        <v>軟絲與岸拋木蝦路線明確 / 從入門到高階覆蓋清晰</v>
       </c>
     </row>
     <row r="631">
@@ -36086,7 +36086,7 @@
         <v>bass</v>
       </c>
       <c r="I631" t="str">
-        <v>https://www.daiwaseiko.com.tw/upload/product_m/twL_product_20H11_fzpj4fuci2.png</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1036_VERTICE.png</v>
       </c>
       <c r="J631" t="str">
         <v/>
@@ -36110,10 +36110,10 @@
         <v>VERTICE 平價路亞竿，竿身採用幻影變色設計，搭配DAIWA獨家技術與富士導珠!</v>
       </c>
       <c r="Q631" t="str">
-        <v/>
+        <v>淡海水泛用 / 入門</v>
       </c>
       <c r="R631" t="str">
-        <v/>
+        <v>入門泛用路線明確 / 多場景基礎作釣覆蓋較廣</v>
       </c>
     </row>
     <row r="632">
@@ -36142,7 +36142,7 @@
         <v>溪流,岸投</v>
       </c>
       <c r="I632" t="str">
-        <v>https://www.daiwaseiko.com.tw/upload/product_m/twL_product_21F21_ppsvnhprh5.png</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1037_CROSSFIRE.png</v>
       </c>
       <c r="J632" t="str">
         <v/>
@@ -36166,15 +36166,1695 @@
         <v>CROSSFIRE CROSSFIRE入門路亞竿，一竿多用設計，讓您一把釣竿釣遍湖泊、溪流、港口、沙灘。 竿子特色:EVA海綿握把、礦石珠、路亞掛勾</v>
       </c>
       <c r="Q632" t="str">
-        <v/>
+        <v>淡海水泛用 / 入門</v>
       </c>
       <c r="R632" t="str">
-        <v/>
+        <v>入門泛用路線明確 / 多場景基礎作釣覆蓋較廣</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="str">
+        <v>DR1045</v>
+      </c>
+      <c r="B633">
+        <v>2</v>
+      </c>
+      <c r="C633" t="str">
+        <v>MORETHAN WISEMEN</v>
+      </c>
+      <c r="D633" t="str">
+        <v>MORETHAN WISEMEN</v>
+      </c>
+      <c r="E633" t="str">
+        <v/>
+      </c>
+      <c r="F633" t="str">
+        <v>MORETHAN WISEMEN</v>
+      </c>
+      <c r="G633" t="str">
+        <v>海鱸</v>
+      </c>
+      <c r="H633" t="str">
+        <v>海鲈,岸投</v>
+      </c>
+      <c r="I633" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1045_MORETHAN_WISEMEN.jpg</v>
+      </c>
+      <c r="J633" t="str">
+        <v/>
+      </c>
+      <c r="K633" t="str">
+        <v/>
+      </c>
+      <c r="L633" t="str">
+        <v>海鱸</v>
+      </c>
+      <c r="M633" t="str">
+        <v>為了拋投得更遠、玩得更盡興、釣得更多。 海鱸魚。棲息於日本各地,從海水區域到海河口交接水域,足跡遍布各種釣場。時而兇猛、時而纖細、時而大膽,展現出多變的性格,令釣魚人既困惑又著迷。 「morethan」是為了與這充滿魅力的海鱸對峙,並將其魅力發揮到極致而誕生。 暢快地拋投、隨心所欲地操控路亞、清晰地捕捉海鱸的氣息與魚訊、引誘其上鉤。 作為一個綜合所有相關釣具裝備的魚種品牌,morethan專為海鱸釣而生,也正因為這份專用的堅持,才能看見那獨一無二的風景。 將堅持化為形體。打造能細細品味、長久相伴的夥伴。morethan「WISEMEN」 久候多時的morethan WISEMEN系列終於迎來全新魚餌釣竿。搭載凝聚DAIWA技術的纖細竿身,具備流暢的負重轉移特性,能毫不費力地將各類重量的路亞精準投射至目標點。富有黏性的竿身與收線力強勁的魚餌捲線器堪稱絕配。憑藉竿體扭力壓制大型平鱸與青魚的掙扎,再以魚餌捲線器的強勁收線力道將目標魚種一氣呵成拉近。 DAIWA 技術 感性領域設計系統 [ESS](專家感性模擬) 當釣竿彎曲時,會產生與彎曲方向相反的能量(復原力)。這是變形(扭曲)的竿身試圖恢復原狀的「扭曲能量」,是左右釣竿性能的極為重要要素。DAIWA獨自開發了分析和設計「扭曲能量」的系統,不僅能以數值明確掌握「優勢何在」、「不足之處」,還能將釣魚者的感性領域反映到設計中,使釣竿更貼近釣魚者的需求。 產品詳細(僅限109M、113M/MH型號) 細身坯體不易受各方向風勢影響,其設計手法更依據釣場特性與作釣方式大幅調整,展現精益求精的匠心。無論是能隨心所欲於中距離施展拋投與路亞操控的款式,抑或能劈開強勁逆風實現遠投的型號,皆蘊含豐富個性。</v>
+      </c>
+      <c r="N633" t="str">
+        <v>79,000~128,000円</v>
+      </c>
+      <c r="O633" t="str">
+        <v/>
+      </c>
+      <c r="P633" t="str">
+        <v>為了拋投得更遠、玩得更盡興、釣得更多。 海鱸魚。棲息於日本各地,從海水區域到海河口交接水域,足跡遍布各種釣場。時而兇猛、時而纖細、時而大膽,展現出多變的性格,令釣魚人既困惑又著迷。 「morethan」是為了與這充滿魅力的海鱸對峙,並將其魅力發揮到極致而誕生。 暢快地拋投、隨心所欲地操控路亞、清晰地捕捉海鱸的氣息與魚訊、引誘其上鉤。 作為一個綜合所有相關釣具裝備的魚種品牌,morethan專為海鱸釣而生,也正因為這份專用的堅持,才能看見那獨一無二的風景。 將堅持化為形體。打造能細細品味、長久相伴的夥伴。morethan「WISEMEN」 久候多時的morethan WISEMEN系列終於迎來全新魚餌釣竿。搭載凝聚DAIWA技術的纖細竿身,具備流暢的負重轉移特性,能毫不費力地將各類重量的路亞精準投射至目標點。富有黏性的竿身與收線力強勁的魚餌捲線器堪稱絕配。憑藉竿體扭力壓制大型平鱸與青魚的掙扎,再以魚餌捲線器的強勁收線力道將目標魚種一氣呵成拉近。 DAIWA 技術 感性領域設計系統 [ESS](專家感性模擬) 當釣竿彎曲時,會產生與彎曲方向相反的能量(復原力)。這是變形(扭曲)的竿身試圖恢復原狀的「扭曲能量」,是左右釣竿性能的極為重要要素。DAIWA獨自開發了分析和設計「扭曲能量」的系統,不僅能以數值明確掌握「優勢何在」、「不足之處」,還能將釣魚者的感性領域反映到設計中,使釣竿更貼近釣魚者的需求。 產品詳細(僅限109M、113M/MH型號) 細身坯體不易受各方向風勢影響,其設計手法更依據釣場特性與作釣方式大幅調整,展現精益求精的匠心。無論是能隨心所欲於中距離施展拋投與路亞操控的款式,抑或能劈開強勁逆風實現遠投的型號,皆蘊含豐富個性。</v>
+      </c>
+      <c r="Q633" t="str">
+        <v>海鲈 / 岸投 / 河口港湾到海滩</v>
+      </c>
+      <c r="R633" t="str">
+        <v>围绕米诺、沉水铅笔、震动和金属系路亚建立远投与控线能力，适合按场地宽度和目标鱼体型选长度。</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="str">
+        <v>DR1046</v>
+      </c>
+      <c r="B634">
+        <v>2</v>
+      </c>
+      <c r="C634" t="str">
+        <v>HEARTLAND AGS(紡車式款式)</v>
+      </c>
+      <c r="D634" t="str">
+        <v>HEARTLAND AGS(紡車式款式)</v>
+      </c>
+      <c r="E634" t="str">
+        <v/>
+      </c>
+      <c r="F634" t="str">
+        <v>HEARTLAND AGS(紡車式款式)</v>
+      </c>
+      <c r="G634" t="str">
+        <v>鱸魚</v>
+      </c>
+      <c r="H634" t="str">
+        <v>bass</v>
+      </c>
+      <c r="I634" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1046_HEARTLAND_AGS.jpg</v>
+      </c>
+      <c r="J634" t="str">
+        <v/>
+      </c>
+      <c r="K634" t="str">
+        <v/>
+      </c>
+      <c r="L634" t="str">
+        <v>鱸魚</v>
+      </c>
+      <c r="M634" t="str">
+        <v>至福的安寧。HEARTLAND的片刻。 DAIWA 技術 感性領域設計系統 [ESS](專家感性模擬) 當釣竿彎曲時,會產生與彎曲方向相反的能量(復原力)。這是變形(扭曲)的竿身試圖恢復原狀的「扭曲能量」,是左右釣竿性能的極為重要要素。DAIWA獨自開發了分析和設計「扭曲能量」的系統,不僅能以數值明確掌握「優勢何在」、「不足之處」,還能將釣魚者的感性領域反映到設計中,使釣竿更貼近釣魚者的需求。 ※6102LFS AGS13除外</v>
+      </c>
+      <c r="N634" t="str">
+        <v>67,000~103,000円</v>
+      </c>
+      <c r="O634" t="str">
+        <v/>
+      </c>
+      <c r="P634" t="str">
+        <v>至福的安寧。HEARTLAND的片刻。 DAIWA 技術 感性領域設計系統 [ESS](專家感性模擬) 當釣竿彎曲時,會產生與彎曲方向相反的能量(復原力)。這是變形(扭曲)的竿身試圖恢復原狀的「扭曲能量」,是左右釣竿性能的極為重要要素。DAIWA獨自開發了分析和設計「扭曲能量」的系統,不僅能以數值明確掌握「優勢何在」、「不足之處」,還能將釣魚者的感性領域反映到設計中,使釣竿更貼近釣魚者的需求。 ※6102LFS AGS13除外</v>
+      </c>
+      <c r="Q634" t="str">
+        <v>淡水 Bass / 技法分工 / 软硬饵覆盖</v>
+      </c>
+      <c r="R634" t="str">
+        <v>按子型号区分精细、卷阻、底操、cover 和大饵路线，适合依照钓组与作钓距离选型。</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="str">
+        <v>DR1047</v>
+      </c>
+      <c r="B635">
+        <v>2</v>
+      </c>
+      <c r="C635" t="str">
+        <v>HEARTLAND AGS(拋投兩軸款式)</v>
+      </c>
+      <c r="D635" t="str">
+        <v>HEARTLAND AGS(拋投兩軸款式)</v>
+      </c>
+      <c r="E635" t="str">
+        <v/>
+      </c>
+      <c r="F635" t="str">
+        <v>HEARTLAND AGS(拋投兩軸款式)</v>
+      </c>
+      <c r="G635" t="str">
+        <v>鱸魚</v>
+      </c>
+      <c r="H635" t="str">
+        <v>bass</v>
+      </c>
+      <c r="I635" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1047_HEARTLAND_AGS.jpg</v>
+      </c>
+      <c r="J635" t="str">
+        <v/>
+      </c>
+      <c r="K635" t="str">
+        <v/>
+      </c>
+      <c r="L635" t="str">
+        <v>鱸魚</v>
+      </c>
+      <c r="M635" t="str">
+        <v>水畔。那便是原點。HEARTLAND的軸心永不動搖。 DAIWA 技術 感性領域設計系統 [ESS](專家感性模擬) 當釣竿彎曲時,會產生與彎曲方向相反的能量(復原力)。這是變形(扭曲)的竿身試圖恢復原狀的「扭曲能量」,是左右釣竿性能的極為重要要素。DAIWA獨自開發了分析和設計「扭曲能量」的系統,不僅能以數值明確掌握「優勢何在」、「不足之處」,還能將釣魚者的感性領域反映到設計中,使釣竿更貼近釣魚者的需求。</v>
+      </c>
+      <c r="N635" t="str">
+        <v>91,000~100,000円</v>
+      </c>
+      <c r="O635" t="str">
+        <v/>
+      </c>
+      <c r="P635" t="str">
+        <v>水畔。那便是原點。HEARTLAND的軸心永不動搖。 DAIWA 技術 感性領域設計系統 [ESS](專家感性模擬) 當釣竿彎曲時,會產生與彎曲方向相反的能量(復原力)。這是變形(扭曲)的竿身試圖恢復原狀的「扭曲能量」,是左右釣竿性能的極為重要要素。DAIWA獨自開發了分析和設計「扭曲能量」的系統,不僅能以數值明確掌握「優勢何在」、「不足之處」,還能將釣魚者的感性領域反映到設計中,使釣竿更貼近釣魚者的需求。</v>
+      </c>
+      <c r="Q635" t="str">
+        <v>淡水 Bass / 技法分工 / 软硬饵覆盖</v>
+      </c>
+      <c r="R635" t="str">
+        <v>按子型号区分精细、卷阻、底操、cover 和大饵路线，适合依照钓组与作钓距离选型。</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="str">
+        <v>DR1048</v>
+      </c>
+      <c r="B636">
+        <v>2</v>
+      </c>
+      <c r="C636" t="str">
+        <v>MORETHAN</v>
+      </c>
+      <c r="D636" t="str">
+        <v>MORETHAN</v>
+      </c>
+      <c r="E636" t="str">
+        <v/>
+      </c>
+      <c r="F636" t="str">
+        <v>MORETHAN</v>
+      </c>
+      <c r="G636" t="str">
+        <v>海鱸</v>
+      </c>
+      <c r="H636" t="str">
+        <v>海鲈,岸投</v>
+      </c>
+      <c r="I636" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1048_MORETHAN.jpg</v>
+      </c>
+      <c r="J636" t="str">
+        <v/>
+      </c>
+      <c r="K636" t="str">
+        <v/>
+      </c>
+      <c r="L636" t="str">
+        <v>海鱸</v>
+      </c>
+      <c r="M636" t="str">
+        <v>為了拋投得更遠、玩得更盡興、釣得更多。 海鱸魚。棲息於日本各地,從海水區域到海河口交接水域,足跡遍布各種釣場。時而兇猛、時而纖細、時而大膽,展現出多變的性格,令釣魚人既困惑又著迷。 「morethan」是為了與這充滿魅力的海鱸對峙,並將其魅力發揮到極致而誕生。 暢快地拋投、隨心所欲地操控路亞、清晰地捕捉海鱸的氣息與魚訊、引誘其上鉤。 作為一個綜合所有相關釣具裝備的魚種品牌,morethan專為海鱸釣而生,也正因為這份專用的堅持,才能看見那獨一無二的風景。 「革新之道」——隨時隨地,無論誰使用都能展現高階性能的理想海鱸釣竿 DAIWA 技術 SVF COMPILE-X 奈米PLUS 由大幅減少的樹脂、以及相應地大量密集填入的石墨纖維所構成的超肌肉質竿身。因具有高硬度與彈性,帶來卓越的情報傳達能力,宛如親手觸摸水中的感度。此外,減少的樹脂量意味著輕量化與力量的升級,在相同力量下能製作更輕的釣竿,在相同力量與輕量下能製作更細的釣竿。這是對於要求咬餌瞬間立即反應的釣法不可或缺的竿身,能感受到敏銳的感度與強勁的竿尾力量。由於細身,更易恩於揮出,能進行不偏離目標點的精準拋投,其輕量化使持續拋投一整天成為可能。此高性能竿身因 NANO PLUS 技術而實現進化突破。 產品詳情 morethan的象徵——纖細而厚實的設計,採用超樹脂SVF Compile X Nano Plus製成的竿體。我們從根本重新審視這項設計理念。著重於順暢的負重傳遞,以及從握柄至竿尾的剛性結構,徹底排除力量損耗。除了具備卓越的遠投性能與精準拋投表現,更以強韌的黏性為特色。揮竿瞬間,便會沉醉於這份獨特手感。突破既有「morethan」框架的嶄新體驗。「以寬廣包容性,輕快有力地投擲各類路亞」。無高彈性尖銳感,無論遠投或精準定位皆能自如操控路亞。感度表現同樣卓越。憑藉morethan獨創的銳敏竿尖,不僅能精準感知輕量路亞觸底,連沉水鉛筆型的細微動作亦能清晰傳遞。採用印籠接法工藝的竿體,能流暢傳遞受力變化,精準呼應海鱸動態與釣友意圖。大幅降低脫鉤率,即使激烈搏魚亦能從容應對。 捲線器座升級為零縫隙無縫貼合設計。相較於氣感SLIM貼合座,其更為纖細的輪廓能提供更穩固的握持操作感。纖薄化設計使收線時無需施加多餘力道即可穩固握持,有效提升手部觸感靈敏度。 ※針對長軸型103ML/M、106M、106M/MH型號,考量搭配LT5000系列使用需求,採用與大型捲線器相容的氣壓感應器・SLIM捲線器座。</v>
+      </c>
+      <c r="N636" t="str">
+        <v>67,000~84,000円</v>
+      </c>
+      <c r="O636" t="str">
+        <v/>
+      </c>
+      <c r="P636" t="str">
+        <v>為了拋投得更遠、玩得更盡興、釣得更多。 海鱸魚。棲息於日本各地,從海水區域到海河口交接水域,足跡遍布各種釣場。時而兇猛、時而纖細、時而大膽,展現出多變的性格,令釣魚人既困惑又著迷。 「morethan」是為了與這充滿魅力的海鱸對峙,並將其魅力發揮到極致而誕生。 暢快地拋投、隨心所欲地操控路亞、清晰地捕捉海鱸的氣息與魚訊、引誘其上鉤。 作為一個綜合所有相關釣具裝備的魚種品牌,morethan專為海鱸釣而生,也正因為這份專用的堅持,才能看見那獨一無二的風景。 「革新之道」——隨時隨地,無論誰使用都能展現高階性能的理想海鱸釣竿 DAIWA 技術 SVF COMPILE-X 奈米PLUS 由大幅減少的樹脂、以及相應地大量密集填入的石墨纖維所構成的超肌肉質竿身。因具有高硬度與彈性,帶來卓越的情報傳達能力,宛如親手觸摸水中的感度。此外,減少的樹脂量意味著輕量化與力量的升級,在相同力量下能製作更輕的釣竿,在相同力量與輕量下能製作更細的釣竿。這是對於要求咬餌瞬間立即反應的釣法不可或缺的竿身,能感受到敏銳的感度與強勁的竿尾力量。由於細身,更易恩於揮出,能進行不偏離目標點的精準拋投,其輕量化使持續拋投一整天成為可能。此高性能竿身因 NANO PLUS 技術而實現進化突破。 產品詳情 morethan的象徵——纖細而厚實的設計,採用超樹脂SVF Compile X Nano Plus製成的竿體。我們從根本重新審視這項設計理念。著重於順暢的負重傳遞,以及從握柄至竿尾的剛性結構,徹底排除力量損耗。除了具備卓越的遠投性能與精準拋投表現,更以強韌的黏性為特色。揮竿瞬間,便會沉醉於這份獨特手感。突破既有「morethan」框架的嶄新體驗。「以寬廣包容性,輕快有力地投擲各類路亞」。無高彈性尖銳感,無論遠投或精準定位皆能自如操控路亞。感度表現同樣卓越。憑藉morethan獨創的銳敏竿尖,不僅能精準感知輕量路亞觸底,連沉水鉛筆型的細微動作亦能清晰傳遞。採用印籠接法工藝的竿體,能流暢傳遞受力變化,精準呼應海鱸動態與釣友意圖。大幅降低脫鉤率,即使激烈搏魚亦能從容應對。 捲線器座升級為零縫隙無縫貼合設計。相較於氣感SLIM貼合座,其更為纖細的輪廓能提供更穩固的握持操作感。纖薄化設計使收線時無需施加多餘力道即可穩固握持,有效提升手部觸感靈敏度。 ※針對長軸型103ML/M、106M、106M/MH型號,考量搭配LT5000系列使用需求,採用與大型捲線器相容的氣壓感應器・SLIM捲線器座。</v>
+      </c>
+      <c r="Q636" t="str">
+        <v>海鲈 / 岸投 / 河口港湾到海滩</v>
+      </c>
+      <c r="R636" t="str">
+        <v>围绕米诺、沉水铅笔、震动和金属系路亚建立远投与控线能力，适合按场地宽度和目标鱼体型选长度。</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="str">
+        <v>DR1049</v>
+      </c>
+      <c r="B637">
+        <v>2</v>
+      </c>
+      <c r="C637" t="str">
+        <v>DRAGGER BREAK THROUGH</v>
+      </c>
+      <c r="D637" t="str">
+        <v>DRAGGER BREAK THROUGH</v>
+      </c>
+      <c r="E637" t="str">
+        <v/>
+      </c>
+      <c r="F637" t="str">
+        <v>DRAGGER BREAK THROUGH</v>
+      </c>
+      <c r="G637" t="str">
+        <v>海水岸邊鐵板</v>
+      </c>
+      <c r="H637" t="str">
+        <v>岸投</v>
+      </c>
+      <c r="I637" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1049_DRAGGER_BREAK_THROUGH.jpg</v>
+      </c>
+      <c r="J637" t="str">
+        <v/>
+      </c>
+      <c r="K637" t="str">
+        <v/>
+      </c>
+      <c r="L637" t="str">
+        <v>海水岸邊鐵板</v>
+      </c>
+      <c r="M637" t="str">
+        <v>無壓力的路亞操控性,以及蘊藏壓倒性搏鬥性能的岩岸釣竿 ■DRAGGER-拖格 ■岸釣鐵板釣法竿的巔峰之作「BREAK THROUGH」 ■概念一 無壓力的路亞操作性 岸釣與插餌釣法中至關重要的是,為把握稀少的咬餌機會,必須持續操控路亞。岩岸海岸的主戰場在於潮水衝擊強勁的磯岩。操縱的是超過100公克的大型插餌或鐵板。透過時而俐落、時而溫和的施力,感受潮汐流動並誘引魚群。任何操作失誤都將瞬間被魚類識破。這項耗費體力與神經的操作絕非易事。我們在各類場域測試多種路亞,從多角度深入鑽研竿尖材質與錐度設計,最終實現流暢的受力傳導錐度與精準的反彈特性。此設計大幅提升路亞操控性,藉由最適反彈力使釣竿為路亞創造理想水流推力,使路亞游動時呈現「滑溜溜」的全新境界。此外,誤入水深的情況大幅減少。相較於傳統產品,釣竿受壓範圍縮小,使引導假餌更為輕鬆。至於鐵板專用釣竿,因重量能更深入竿身前段,使抽竿手感更為輕快。同時透過調整竿尖特性與假餌竿的差異,能適度抑制鐵板泳姿,協助創造讓青物自然咬餌的動作輸入。 概念二 壓倒性的戰鬥性能 在開發DRAGGER的過程中,我們對岸釣路亞竿的動力等級進行了大幅調整。然而,在專為頂尖釣手打造的岩岸專用竿「BREAKTHROUGH」上,與魚類的搏鬥堪稱生死對決。要在極限搏鬥中掌控大型魚類,必須具備作為最終防線的強韌竿尾動力。「BREAKTHROUGH」透過增粗竿身前段太徑,進一步強化釣竿力量。此設計能強行遏止暴戾的初始衝刺、在礁岩邊緣奪取主導權,並實現流暢的提竿動作。這支釣竿具專為鋼鐵之軀的岩岸釣手打造,即使面對大魚也絕不讓步,完美詮釋「不讓大魚主導戰局」的設計理念。 在持續進行實地測試的過程中所達到的三件式結構 白胚、握柄、導環配置......所有部件皆從零開始研發。耗費整整兩年光陰。為了打造一支釣竿,究竟試製了多少支原型,反覆進行了多少次實釣測試?為實現雙重開發理念,最終採用結合套筒接合與並接技術的複雜三節式結構。將第1節與第2節設計為套筒結構,使受力傳導更流暢,成就出能展現嫵媚俐落路亞動作的竿尖,以及能極其自然操控路亞與鐵板的竿腹。另一方面,第2節與第3節採用並接結構。透過加粗根節設計賦予強韌力量,從而實現遠投性能與強勁揚力。成功在高次元上兼顧操作性與力量這兩項矛盾要素。照片中展示的是單次釣行攜帶的樣品之一。我們反覆進行多次測試,與測試員共同追求細節處的理想境界。</v>
+      </c>
+      <c r="N637" t="str">
+        <v>69,000~79,500円</v>
+      </c>
+      <c r="O637" t="str">
+        <v/>
+      </c>
+      <c r="P637" t="str">
+        <v>無壓力的路亞操控性,以及蘊藏壓倒性搏鬥性能的岩岸釣竿 ■DRAGGER-拖格 ■岸釣鐵板釣法竿的巔峰之作「BREAK THROUGH」 ■概念一 無壓力的路亞操作性 岸釣與插餌釣法中至關重要的是,為把握稀少的咬餌機會,必須持續操控路亞。岩岸海岸的主戰場在於潮水衝擊強勁的磯岩。操縱的是超過100公克的大型插餌或鐵板。透過時而俐落、時而溫和的施力,感受潮汐流動並誘引魚群。任何操作失誤都將瞬間被魚類識破。這項耗費體力與神經的操作絕非易事。我們在各類場域測試多種路亞,從多角度深入鑽研竿尖材質與錐度設計,最終實現流暢的受力傳導錐度與精準的反彈特性。此設計大幅提升路亞操控性,藉由最適反彈力使釣竿為路亞創造理想水流推力,使路亞游動時呈現「滑溜溜」的全新境界。此外,誤入水深的情況大幅減少。相較於傳統產品,釣竿受壓範圍縮小,使引導假餌更為輕鬆。至於鐵板專用釣竿,因重量能更深入竿身前段,使抽竿手感更為輕快。同時透過調整竿尖特性與假餌竿的差異,能適度抑制鐵板泳姿,協助創造讓青物自然咬餌的動作輸入。 概念二 壓倒性的戰鬥性能 在開發DRAGGER的過程中,我們對岸釣路亞竿的動力等級進行了大幅調整。然而,在專為頂尖釣手打造的岩岸專用竿「BREAKTHROUGH」上,與魚類的搏鬥堪稱生死對決。要在極限搏鬥中掌控大型魚類,必須具備作為最終防線的強韌竿尾動力。「BREAKTHROUGH」透過增粗竿身前段太徑,進一步強化釣竿力量。此設計能強行遏止暴戾的初始衝刺、在礁岩邊緣奪取主導權,並實現流暢的提竿動作。這支釣竿具專為鋼鐵之軀的岩岸釣手打造,即使面對大魚也絕不讓步,完美詮釋「不讓大魚主導戰局」的設計理念。 在持續進行實地測試的過程中所達到的三件式結構 白胚、握柄、導環配置......所有部件皆從零開始研發。耗費整整兩年光陰。為了打造一支釣竿,究竟試製了多少支原型,反覆進行了多少次實釣測試?為實現雙重開發理念,最終採用結合套筒接合與並接技術的複雜三節式結構。將第1節與第2節設計為套筒結構,使受力傳導更流暢,成就出能展現嫵媚俐落路亞動作的竿尖,以及能極其自然操控路亞與鐵板的竿腹。另一方面,第2節與第3節採用並接結構。透過加粗根節設計賦予強韌力量,從而實現遠投性能與強勁揚力。成功在高次元上兼顧操作性與力量這兩項矛盾要素。照片中展示的是單次釣行攜帶的樣品之一。我們反覆進行多次測試,與測試員共同追求細節處的理想境界。</v>
+      </c>
+      <c r="Q637" t="str">
+        <v>岸投铁板 / 青物 / 远投强负荷</v>
+      </c>
+      <c r="R637" t="str">
+        <v>覆盖金属铁板、重型 plug 和高负荷控鱼场景，重点在远投、抽停节奏和持续搏鱼余量。</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="str">
+        <v>DR1050</v>
+      </c>
+      <c r="B638">
+        <v>2</v>
+      </c>
+      <c r="C638" t="str">
+        <v>銀狼 EX</v>
+      </c>
+      <c r="D638" t="str">
+        <v>銀狼 EX</v>
+      </c>
+      <c r="E638" t="str">
+        <v/>
+      </c>
+      <c r="F638" t="str">
+        <v>銀狼 EX</v>
+      </c>
+      <c r="G638" t="str">
+        <v>黑鯛路亞</v>
+      </c>
+      <c r="H638" t="str">
+        <v>岸投</v>
+      </c>
+      <c r="I638" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1050_EX.jpg</v>
+      </c>
+      <c r="J638" t="str">
+        <v/>
+      </c>
+      <c r="K638" t="str">
+        <v/>
+      </c>
+      <c r="L638" t="str">
+        <v>黑鯛路亞</v>
+      </c>
+      <c r="M638" t="str">
+        <v>將自身的直覺化為釣獲。可掌控一切的頂尖黑鯛竿降臨。 這是為了一心一意追尋黑鯛、對釣魚絕不妥協的釣手所打造的頂級旗艦竿。它具備讓釣手一用就愛上的強大性能,隨著出竿次數增加,會發現它越來越順手,這種人竿合一的感覺,正是旗艦機型才有的地位。Silver Wolf EX 追求的是一種直接感,像用雙手直接摸到水底、直接操控路亞一樣。這種清晰的感度和靈敏的反應,將黑鯛釣法帶入了新的境界。猶如極限賽車般具備高反應性與纖細性格的使用體驗,使用起來反應極快,能將水下的狀況直接傳達到釣手的直覺中。在黑鯛釣法最主流的自由釣組操作上,感覺像用手指刮過海底一樣靈敏;使用路亞時,則能透過細膩的動作讓路亞活靈活現。竿身採用了 SVF COMPILE-X NANOPLUS 素材與 X45X 技術,力量大到足以刺穿黑鯛堅硬的唇口;但同時透過 V-JOINTα 技術,讓竿子在強悍之餘還保有韌性,搏魚時非常輕鬆。導環則配備了又輕又靈敏的AGS,精確掌握路亞狀態。在這種需要快速判斷環境來決定勝負的釣法中,這把釣竿大幅提升了實戰表現。由專業釣手森浩平監修,徹底追求新世代的感度與操控性,這款擁有全新手感的釣竿正式完成。 DAIWA 技術 感性領域設計系統 [ESS](專家感性模擬) 當釣竿彎曲時,會產生與彎曲方向相反的能量(復原力)。這是變形(扭曲)的竿身試圖恢復原狀的「扭曲能量」,是左右釣竿性能的極為重要要素。DAIWA獨自開發了分析和設計「扭曲能量」的系統,不僅能以數值明確掌握「優勢何在」、「不足之處」,還能將釣魚者的感性領域反映到設計中,使釣竿更貼近釣魚者的需求。 產品詳情 奢侈地使用SVF COMPILE-X NANO PLUS 素材的高反應竿身,能瞬間判斷出水底的地形或是魚訊種類,實現精準中魚的高感度。 此外,透過 V-JOINTα 技術讓竿子保有柔軟韌性,外層再用 X45X 強化,防止力量流失,讓拋投距離更遠、操控更精準。 與拿在手上硬挺的感覺相比,中魚後卻擁有截然不同的黏魚韌性,即使使用較細的 PE 線或前導線,也能安全地將魚拉上岸,不用擔心斷線。</v>
+      </c>
+      <c r="N638" t="str">
+        <v>70,000~75,000円</v>
+      </c>
+      <c r="O638" t="str">
+        <v/>
+      </c>
+      <c r="P638" t="str">
+        <v>將自身的直覺化為釣獲。可掌控一切的頂尖黑鯛竿降臨。 這是為了一心一意追尋黑鯛、對釣魚絕不妥協的釣手所打造的頂級旗艦竿。它具備讓釣手一用就愛上的強大性能,隨著出竿次數增加,會發現它越來越順手,這種人竿合一的感覺,正是旗艦機型才有的地位。Silver Wolf EX 追求的是一種直接感,像用雙手直接摸到水底、直接操控路亞一樣。這種清晰的感度和靈敏的反應,將黑鯛釣法帶入了新的境界。猶如極限賽車般具備高反應性與纖細性格的使用體驗,使用起來反應極快,能將水下的狀況直接傳達到釣手的直覺中。在黑鯛釣法最主流的自由釣組操作上,感覺像用手指刮過海底一樣靈敏;使用路亞時,則能透過細膩的動作讓路亞活靈活現。竿身採用了 SVF COMPILE-X NANOPLUS 素材與 X45X 技術,力量大到足以刺穿黑鯛堅硬的唇口;但同時透過 V-JOINTα 技術,讓竿子在強悍之餘還保有韌性,搏魚時非常輕鬆。導環則配備了又輕又靈敏的AGS,精確掌握路亞狀態。在這種需要快速判斷環境來決定勝負的釣法中,這把釣竿大幅提升了實戰表現。由專業釣手森浩平監修,徹底追求新世代的感度與操控性,這款擁有全新手感的釣竿正式完成。 DAIWA 技術 感性領域設計系統 [ESS](專家感性模擬) 當釣竿彎曲時,會產生與彎曲方向相反的能量(復原力)。這是變形(扭曲)的竿身試圖恢復原狀的「扭曲能量」,是左右釣竿性能的極為重要要素。DAIWA獨自開發了分析和設計「扭曲能量」的系統,不僅能以數值明確掌握「優勢何在」、「不足之處」,還能將釣魚者的感性領域反映到設計中,使釣竿更貼近釣魚者的需求。 產品詳情 奢侈地使用SVF COMPILE-X NANO PLUS 素材的高反應竿身,能瞬間判斷出水底的地形或是魚訊種類,實現精準中魚的高感度。 此外,透過 V-JOINTα 技術讓竿子保有柔軟韌性,外層再用 X45X 強化,防止力量流失,讓拋投距離更遠、操控更精準。 與拿在手上硬挺的感覺相比,中魚後卻擁有截然不同的黏魚韌性,即使使用較細的 PE 線或前導線,也能安全地將魚拉上岸,不用擔心斷線。</v>
+      </c>
+      <c r="Q638" t="str">
+        <v>黑鲷路亚 / Free Rig / 岸边底层攻略</v>
+      </c>
+      <c r="R638" t="str">
+        <v>围绕 free rig、Texas 和小型硬饵建立贴底搜索能力，适合河口、港湾与浅滩障碍边。</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="str">
+        <v>DR1051</v>
+      </c>
+      <c r="B639">
+        <v>2</v>
+      </c>
+      <c r="C639" t="str">
+        <v>DRAGGER SX</v>
+      </c>
+      <c r="D639" t="str">
+        <v>DRAGGER SX</v>
+      </c>
+      <c r="E639" t="str">
+        <v/>
+      </c>
+      <c r="F639" t="str">
+        <v>DRAGGER SX</v>
+      </c>
+      <c r="G639" t="str">
+        <v>海水岸邊鐵板</v>
+      </c>
+      <c r="H639" t="str">
+        <v>岸投</v>
+      </c>
+      <c r="I639" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1051_DRAGGER_SX.jpg</v>
+      </c>
+      <c r="J639" t="str">
+        <v/>
+      </c>
+      <c r="K639" t="str">
+        <v/>
+      </c>
+      <c r="L639" t="str">
+        <v>海水岸邊鐵板</v>
+      </c>
+      <c r="M639" t="str">
+        <v>瞄準更大型目標。具備真實路亞操控性與黏性揚竿力的岸釣鐵板釣法釣竿 DRAGGER 拖格 DAIWA的岩岸・岸邊鐵板釣法釣竿「DRAGGER」。「DRAGGER」意為「強力拉扯」。岸釣竹筴魚的搏鬥風格,在於將捲線器阻力調至極限,藉由釣竿蓄力將青物拉浮。在這場極限對決中,釣竿必須是值得絕對信賴的夥伴。DRAGGER在釣場持續淬鍊,不斷進化。願您握持此竿,以渾身之力直面大魚。 正統系列「SX」 專為追求大魚的岸釣鐵板愛好者打造的高階岩岸鐵板釣法釣竿系列「SX」。其開發理念包含兩大核心:其一與高端「BREAKTHROUGH」系列相同——透過讓鐵板與流速完美結合,實現輕力操控的絕佳路亞操作性。另一項則是「SX」獨有的粘韌特性——當青物猛烈拉扯時,釣竿能緊密貼合魚體拉力彎曲,在大幅減輕釣友負擔的同時,以強韌的抗拉力徹底封鎖魚體逃逸動線,杜絕魚線被牽引的可能。 「SX」與「BREAKTHROUGH」擁有截然不同的性格。它早已超越次級產品的定位,更臻至「SX」獨有的境界。</v>
+      </c>
+      <c r="N639" t="str">
+        <v>51,000~70,000円</v>
+      </c>
+      <c r="O639" t="str">
+        <v/>
+      </c>
+      <c r="P639" t="str">
+        <v>瞄準更大型目標。具備真實路亞操控性與黏性揚竿力的岸釣鐵板釣法釣竿 DRAGGER 拖格 DAIWA的岩岸・岸邊鐵板釣法釣竿「DRAGGER」。「DRAGGER」意為「強力拉扯」。岸釣竹筴魚的搏鬥風格,在於將捲線器阻力調至極限,藉由釣竿蓄力將青物拉浮。在這場極限對決中,釣竿必須是值得絕對信賴的夥伴。DRAGGER在釣場持續淬鍊,不斷進化。願您握持此竿,以渾身之力直面大魚。 正統系列「SX」 專為追求大魚的岸釣鐵板愛好者打造的高階岩岸鐵板釣法釣竿系列「SX」。其開發理念包含兩大核心:其一與高端「BREAKTHROUGH」系列相同——透過讓鐵板與流速完美結合,實現輕力操控的絕佳路亞操作性。另一項則是「SX」獨有的粘韌特性——當青物猛烈拉扯時,釣竿能緊密貼合魚體拉力彎曲,在大幅減輕釣友負擔的同時,以強韌的抗拉力徹底封鎖魚體逃逸動線,杜絕魚線被牽引的可能。 「SX」與「BREAKTHROUGH」擁有截然不同的性格。它早已超越次級產品的定位,更臻至「SX」獨有的境界。</v>
+      </c>
+      <c r="Q639" t="str">
+        <v>岸投铁板 / 青物 / 远投强负荷</v>
+      </c>
+      <c r="R639" t="str">
+        <v>覆盖金属铁板、重型 plug 和高负荷控鱼场景，重点在远投、抽停节奏和持续搏鱼余量。</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="str">
+        <v>DR1052</v>
+      </c>
+      <c r="B640">
+        <v>2</v>
+      </c>
+      <c r="C640" t="str">
+        <v>HRF SX</v>
+      </c>
+      <c r="D640" t="str">
+        <v>HRF SX</v>
+      </c>
+      <c r="E640" t="str">
+        <v/>
+      </c>
+      <c r="F640" t="str">
+        <v>HRF SX</v>
+      </c>
+      <c r="G640" t="str">
+        <v>HRF(根魚路亞釣)</v>
+      </c>
+      <c r="H640" t="str">
+        <v>根钓,岸投</v>
+      </c>
+      <c r="I640" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1052_HRF_SX.jpg</v>
+      </c>
+      <c r="J640" t="str">
+        <v/>
+      </c>
+      <c r="K640" t="str">
+        <v/>
+      </c>
+      <c r="L640" t="str">
+        <v>HRF(根魚路亞釣)</v>
+      </c>
+      <c r="M640" t="str">
+        <v>憑藉壓倒性的射程與底部感知能力,徹底制壓目標。 DAIWA 技術 MEGA TOP R(MEGA TOP R) 在纖維與樹脂均勻分散的碳纖維實心材料「Mega Top」中,結合了東麗株式會社的TORAYCA T1100G碳纖維布與DAIWA獨家製造技術。透過研發更深入至樹脂領域,實現大幅提升的靈敏度與高反應的操作性,打造出高彈性碳纖維實心竿尾。 ※僅限實心竿尖 產品詳情 透過多層捲線SVF材質,在輕量纖細的同時實現前所未有的爆發力與操控性。能精準因應拋投重量負荷彎曲,榨取反彈力以擊出壓倒性飛距。從動作到刺魚的操作感雖強勁有力,但藉由厚實設計使竿身適度彎曲,中魚後仍能展現黏性,有效降低脫鉤率。 飛距離、感度、輕量化,所有性能皆實現驚人的進化 HRF系列頂尖旗艦機型誕生 對於熱愛岩魚釣的釣友而言,這無疑是眾所期盼的巔峰之作。承襲引領岩魚釣領域的「HRF」系列血統,傾注最新技術打造的頂尖型號「HRF SX」正式誕生。 融合強韌動力與驚人輕量的高彈性竿身、與手掌一體貼合大幅提升操控性的捲線器座等,採用多項新素材與設計新開發。無論是將擬餌送達未經垂釣之秘境的遠投性能、精準掌握海底狀況的靈敏度、維持長時間專注力的輕量化設計、迅速將巨物從岩根處拽出的爆發力,抑或誘使低活性魚類咬餌的高操控性,皆將現代岩魚釣所需的各項要素,以驚人的高次元境界完美體現。 更遠的距離。更高的靈敏度。更強的動力──。無論季節或晝夜,專注追尋魚蹤的嚴苛釣友所提出的嚴苛要求,「HRF SX」皆能完美回應。眼前展開的,是前所未見的全新岩魚釣世界。 兼具力量與輕量化的新開發坯料 更遠距離捕獲遠海魚類的壓倒性飛距。 鋒利度大幅提升的細身高彈性坯料 魚竿底部與釣組的狀態能直接傳遞至手掌的超高靈敏度。 連假路亞也能隨心所欲地操控 細身的空白握在手中,驚人的異次元輕盈感。 獻給那些能嚴謹堅持整日揮釣竿的釣友 兼具力量與柔韌的彎曲特性。 既不讓大型魚主導戰局,又能輕鬆應對並成功捕獲 新設計 搭載新零座設計,完美貼合每位釣友的手感. 手感靈敏度與路亞操控性大幅提升 新釣法亦能完全應對. 適用於各種場域與釣法的豐富產品陣容 在消除實心材質的沉悶感之餘,仍能保持出色的咬合力 高彈性碳素實心尖端,「Mega Top R」</v>
+      </c>
+      <c r="N640" t="str">
+        <v>51,500~57,500円</v>
+      </c>
+      <c r="O640" t="str">
+        <v/>
+      </c>
+      <c r="P640" t="str">
+        <v>憑藉壓倒性的射程與底部感知能力,徹底制壓目標。 DAIWA 技術 MEGA TOP R(MEGA TOP R) 在纖維與樹脂均勻分散的碳纖維實心材料「Mega Top」中,結合了東麗株式會社的TORAYCA T1100G碳纖維布與DAIWA獨家製造技術。透過研發更深入至樹脂領域,實現大幅提升的靈敏度與高反應的操作性,打造出高彈性碳纖維實心竿尾。 ※僅限實心竿尖 產品詳情 透過多層捲線SVF材質,在輕量纖細的同時實現前所未有的爆發力與操控性。能精準因應拋投重量負荷彎曲,榨取反彈力以擊出壓倒性飛距。從動作到刺魚的操作感雖強勁有力,但藉由厚實設計使竿身適度彎曲,中魚後仍能展現黏性,有效降低脫鉤率。 飛距離、感度、輕量化,所有性能皆實現驚人的進化 HRF系列頂尖旗艦機型誕生 對於熱愛岩魚釣的釣友而言,這無疑是眾所期盼的巔峰之作。承襲引領岩魚釣領域的「HRF」系列血統,傾注最新技術打造的頂尖型號「HRF SX」正式誕生。 融合強韌動力與驚人輕量的高彈性竿身、與手掌一體貼合大幅提升操控性的捲線器座等,採用多項新素材與設計新開發。無論是將擬餌送達未經垂釣之秘境的遠投性能、精準掌握海底狀況的靈敏度、維持長時間專注力的輕量化設計、迅速將巨物從岩根處拽出的爆發力,抑或誘使低活性魚類咬餌的高操控性,皆將現代岩魚釣所需的各項要素,以驚人的高次元境界完美體現。 更遠的距離。更高的靈敏度。更強的動力──。無論季節或晝夜,專注追尋魚蹤的嚴苛釣友所提出的嚴苛要求,「HRF SX」皆能完美回應。眼前展開的,是前所未見的全新岩魚釣世界。 兼具力量與輕量化的新開發坯料 更遠距離捕獲遠海魚類的壓倒性飛距。 鋒利度大幅提升的細身高彈性坯料 魚竿底部與釣組的狀態能直接傳遞至手掌的超高靈敏度。 連假路亞也能隨心所欲地操控 細身的空白握在手中,驚人的異次元輕盈感。 獻給那些能嚴謹堅持整日揮釣竿的釣友 兼具力量與柔韌的彎曲特性。 既不讓大型魚主導戰局,又能輕鬆應對並成功捕獲 新設計 搭載新零座設計,完美貼合每位釣友的手感. 手感靈敏度與路亞操控性大幅提升 新釣法亦能完全應對. 適用於各種場域與釣法的豐富產品陣容 在消除實心材質的沉悶感之餘,仍能保持出色的咬合力 高彈性碳素實心尖端,「Mega Top R」</v>
+      </c>
+      <c r="Q640" t="str">
+        <v>根鱼路亚 / Rockfish / 底层结构</v>
+      </c>
+      <c r="R640" t="str">
+        <v>适合用 free rig、Texas、jighead 和 shad 贴底找结构，兼顾远投、读底和障碍边控鱼。</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="str">
+        <v>DR1053</v>
+      </c>
+      <c r="B641">
+        <v>2</v>
+      </c>
+      <c r="C641" t="str">
+        <v>HRF SX GR</v>
+      </c>
+      <c r="D641" t="str">
+        <v>HRF SX GR</v>
+      </c>
+      <c r="E641" t="str">
+        <v/>
+      </c>
+      <c r="F641" t="str">
+        <v>HRF SX GR</v>
+      </c>
+      <c r="G641" t="str">
+        <v>HRF(根魚路亞釣)</v>
+      </c>
+      <c r="H641" t="str">
+        <v>根钓,岸投</v>
+      </c>
+      <c r="I641" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1053_HRF_SX_GR.jpg</v>
+      </c>
+      <c r="J641" t="str">
+        <v/>
+      </c>
+      <c r="K641" t="str">
+        <v/>
+      </c>
+      <c r="L641" t="str">
+        <v>HRF(根魚路亞釣)</v>
+      </c>
+      <c r="M641" t="str">
+        <v>復活的鯛魚專用釣竿!從壓倒性的竿尖輕快感與操控性所誕生的靈敏度與力量完美融合,這就是新鯛魚專用釣竿 DAIWA 技術 X4全覆蓋(=X45柯博護盾) 為了防止在拋投、操作、上鉤、搏魚等動作中所產生的扭曲,透過在竿身最容易發生扭曲的前端位置,以 45° 碳纖維斜紋布從最外層緊密纏繞而成的結構,即為X45全覆蓋。藉此,竿身的抗扭剛性大幅提升。因此能夠實現比以往更好的拋投精準度,並充分發揮竿子本身所具備的性能。 產品詳細 透過多層捲線SVF材質,在輕量纖細的同時實現前所未有的爆發力與操控性。能精準配合拋投重量的負荷彎曲,榨取反彈力以爆發壓倒性的飛距。從動作到刺魚的操作感雖強勁有力,但藉由厚實設計使竿身適度彎曲,中魚後仍能穩固咬鉤,有效降低脫鉤率。</v>
+      </c>
+      <c r="N641" t="str">
+        <v>52,000~54,000円</v>
+      </c>
+      <c r="O641" t="str">
+        <v>new</v>
+      </c>
+      <c r="P641" t="str">
+        <v>復活的鯛魚專用釣竿!從壓倒性的竿尖輕快感與操控性所誕生的靈敏度與力量完美融合,這就是新鯛魚專用釣竿 DAIWA 技術 X4全覆蓋(=X45柯博護盾) 為了防止在拋投、操作、上鉤、搏魚等動作中所產生的扭曲,透過在竿身最容易發生扭曲的前端位置,以 45° 碳纖維斜紋布從最外層緊密纏繞而成的結構,即為X45全覆蓋。藉此,竿身的抗扭剛性大幅提升。因此能夠實現比以往更好的拋投精準度,並充分發揮竿子本身所具備的性能。 產品詳細 透過多層捲線SVF材質,在輕量纖細的同時實現前所未有的爆發力與操控性。能精準配合拋投重量的負荷彎曲,榨取反彈力以爆發壓倒性的飛距。從動作到刺魚的操作感雖強勁有力,但藉由厚實設計使竿身適度彎曲,中魚後仍能穩固咬鉤,有效降低脫鉤率。</v>
+      </c>
+      <c r="Q641" t="str">
+        <v>根鱼路亚 / Rockfish / 底层结构</v>
+      </c>
+      <c r="R641" t="str">
+        <v>适合用 free rig、Texas、jighead 和 shad 贴底找结构，兼顾远投、读底和障碍边控鱼。</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="str">
+        <v>DR1054</v>
+      </c>
+      <c r="B642">
+        <v>2</v>
+      </c>
+      <c r="C642" t="str">
+        <v>SWAGGER</v>
+      </c>
+      <c r="D642" t="str">
+        <v>SWAGGER</v>
+      </c>
+      <c r="E642" t="str">
+        <v/>
+      </c>
+      <c r="F642" t="str">
+        <v>SWAGGER</v>
+      </c>
+      <c r="G642" t="str">
+        <v>鱸魚</v>
+      </c>
+      <c r="H642" t="str">
+        <v>bass</v>
+      </c>
+      <c r="I642" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1054_SWAGGER.jpg</v>
+      </c>
+      <c r="J642" t="str">
+        <v/>
+      </c>
+      <c r="K642" t="str">
+        <v/>
+      </c>
+      <c r="L642" t="str">
+        <v>鱸魚</v>
+      </c>
+      <c r="M642" t="str">
+        <v>尋找你的色彩。 不為外物所動,專注於自己的遊戲。 比起「釣了多少」,更重要的是「如何釣」。 競爭主義與另一條指引方向的標誌。 在路亞釣法中,鱸魚釣法可謂技巧繁多。 在那裡,酸甜苦辣都嘗盡了, 各自都有其獨特的風格。 擁有自我風格的釣友 憑藉著充滿主體性的帥氣釣法所釣獲的一尾, 無可取代。 尋找你的色彩。以自己的方式垂釣。 陳腔濫調的世界觀已經不需要了。 未曾見過的世界就在那裡。</v>
+      </c>
+      <c r="N642" t="str">
+        <v>47,000~54,000円</v>
+      </c>
+      <c r="O642" t="str">
+        <v/>
+      </c>
+      <c r="P642" t="str">
+        <v>尋找你的色彩。 不為外物所動,專注於自己的遊戲。 比起「釣了多少」,更重要的是「如何釣」。 競爭主義與另一條指引方向的標誌。 在路亞釣法中,鱸魚釣法可謂技巧繁多。 在那裡,酸甜苦辣都嘗盡了, 各自都有其獨特的風格。 擁有自我風格的釣友 憑藉著充滿主體性的帥氣釣法所釣獲的一尾, 無可取代。 尋找你的色彩。以自己的方式垂釣。 陳腔濫調的世界觀已經不需要了。 未曾見過的世界就在那裡。</v>
+      </c>
+      <c r="Q642" t="str">
+        <v>淡水 Bass / 技法分工 / 软硬饵覆盖</v>
+      </c>
+      <c r="R642" t="str">
+        <v>按子型号区分精细、卷阻、底操、cover 和大饵路线，适合依照钓组与作钓距离选型。</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="str">
+        <v>DR1055</v>
+      </c>
+      <c r="B643">
+        <v>2</v>
+      </c>
+      <c r="C643" t="str">
+        <v>OVERTHERE SX</v>
+      </c>
+      <c r="D643" t="str">
+        <v>OVERTHERE SX</v>
+      </c>
+      <c r="E643" t="str">
+        <v/>
+      </c>
+      <c r="F643" t="str">
+        <v>OVERTHERE SX</v>
+      </c>
+      <c r="G643" t="str">
+        <v>SURF(比目魚・牛尾魚・青物)</v>
+      </c>
+      <c r="H643" t="str">
+        <v>岸投</v>
+      </c>
+      <c r="I643" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1055_OVERTHERE_SX.jpg</v>
+      </c>
+      <c r="J643" t="str">
+        <v/>
+      </c>
+      <c r="K643" t="str">
+        <v/>
+      </c>
+      <c r="L643" t="str">
+        <v>SURF(比目魚・牛尾魚・青物)</v>
+      </c>
+      <c r="M643" t="str">
+        <v>如空氣般輕盈,兼具壓倒性操控性的超高感度海灘用多功能路亞釣竿 DAIWA 技術 X45 為了防止在拋投、操作、上鉤、搏魚等動作中產生的扭轉,長年研究結果顯示,除了傳統結構(相對於竿尖0°、90°)外,再捲繞「45°」偏置交叉布(±45°傾斜的碳纖維等)是防止扭轉的最佳選擇。搭載X45,實現防止扭轉,並使力量、操作性和感度得到飛躍性提升。 產品詳情 大和最輕量化竿體在岸釣領域所帶來的優勢難以估量。在需反覆進行數百次遠投的岸釣遊戲中,其輕量特性尤為突出。</v>
+      </c>
+      <c r="N643" t="str">
+        <v>50,500~52,500円</v>
+      </c>
+      <c r="O643" t="str">
+        <v>new</v>
+      </c>
+      <c r="P643" t="str">
+        <v>如空氣般輕盈,兼具壓倒性操控性的超高感度海灘用多功能路亞釣竿 DAIWA 技術 X45 為了防止在拋投、操作、上鉤、搏魚等動作中產生的扭轉,長年研究結果顯示,除了傳統結構(相對於竿尖0°、90°)外,再捲繞「45°」偏置交叉布(±45°傾斜的碳纖維等)是防止扭轉的最佳選擇。搭載X45,實現防止扭轉,並使力量、操作性和感度得到飛躍性提升。 產品詳情 大和最輕量化竿體在岸釣領域所帶來的優勢難以估量。在需反覆進行數百次遠投的岸釣遊戲中,其輕量特性尤為突出。</v>
+      </c>
+      <c r="Q643" t="str">
+        <v>海鲈 / 岸投 / 河口港湾到海滩</v>
+      </c>
+      <c r="R643" t="str">
+        <v>围绕米诺、沉水铅笔、震动和金属系路亚建立远投与控线能力，适合按场地宽度和目标鱼体型选长度。</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="str">
+        <v>DR1056</v>
+      </c>
+      <c r="B644">
+        <v>2</v>
+      </c>
+      <c r="C644" t="str">
+        <v>Silver Creek Trad</v>
+      </c>
+      <c r="D644" t="str">
+        <v>Silver Creek Trad</v>
+      </c>
+      <c r="E644" t="str">
+        <v/>
+      </c>
+      <c r="F644" t="str">
+        <v>Silver Creek Trad</v>
+      </c>
+      <c r="G644" t="str">
+        <v>鱒魚・飛蠅釣法</v>
+      </c>
+      <c r="H644" t="str">
+        <v>溪流</v>
+      </c>
+      <c r="I644" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1056_Silver_Creek_Trad.jpg</v>
+      </c>
+      <c r="J644" t="str">
+        <v/>
+      </c>
+      <c r="K644" t="str">
+        <v/>
+      </c>
+      <c r="L644" t="str">
+        <v>鱒魚・飛蠅釣法</v>
+      </c>
+      <c r="M644" t="str">
+        <v>與鱒魚同行,傳統與革新 將拋投、操控、博魚等鱒魚釣法的所有動作隨心所欲地完成。與美麗的溪魚並列時,更能彰顯釣竿本體的魅力,這就是 Silver Creek 的標準系列「Trad」。 本作重新審視了前代的調子,並為了能更舒適地執行鱒魚釣法的基本動作而煥然一新。從釣季初期的低活性期到盛產旺季,經過反覆的實地測試,追求能對應各種魚訊的動態表現。在拋投感方面,藉由採用斜紋結構碳纖維布、消除扭曲的 X45 技術,讓翻轉拋投或反手拋投等技術性動作能隨心所欲地達成;無論是精準射入標點的狙擊,還是開闊水域的遠投,皆能輕鬆駕馭。 外觀方面,採用了講究的綠色系塗裝,並搭配米色系的半透明絲線纏線。握把周邊承襲了 Silver Creek 系列的一貫風格,選用細徑木製捲線器座;槍柄型號則採用短扳機設計,確保了極致舒適的使用感。 這是一把兼具鱒魚釣法獨特世界觀與強大實戰性能的精美釣竿。</v>
+      </c>
+      <c r="N644" t="str">
+        <v>39,000~45,000円</v>
+      </c>
+      <c r="O644" t="str">
+        <v>additional</v>
+      </c>
+      <c r="P644" t="str">
+        <v>與鱒魚同行,傳統與革新 將拋投、操控、博魚等鱒魚釣法的所有動作隨心所欲地完成。與美麗的溪魚並列時,更能彰顯釣竿本體的魅力,這就是 Silver Creek 的標準系列「Trad」。 本作重新審視了前代的調子,並為了能更舒適地執行鱒魚釣法的基本動作而煥然一新。從釣季初期的低活性期到盛產旺季,經過反覆的實地測試,追求能對應各種魚訊的動態表現。在拋投感方面,藉由採用斜紋結構碳纖維布、消除扭曲的 X45 技術,讓翻轉拋投或反手拋投等技術性動作能隨心所欲地達成;無論是精準射入標點的狙擊,還是開闊水域的遠投,皆能輕鬆駕馭。 外觀方面,採用了講究的綠色系塗裝,並搭配米色系的半透明絲線纏線。握把周邊承襲了 Silver Creek 系列的一貫風格,選用細徑木製捲線器座;槍柄型號則採用短扳機設計,確保了極致舒適的使用感。 這是一把兼具鱒魚釣法獨特世界觀與強大實戰性能的精美釣竿。</v>
+      </c>
+      <c r="Q644" t="str">
+        <v>溪流鳟鱼 / Native trout / 轻量硬饵</v>
+      </c>
+      <c r="R644" t="str">
+        <v>按溪流宽度和携带方式选择长度，适合米诺、spoon 和 spinner 的短中距离精准抛投。</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="str">
+        <v>DR1057</v>
+      </c>
+      <c r="B645">
+        <v>2</v>
+      </c>
+      <c r="C645" t="str">
+        <v>月下美人 MX</v>
+      </c>
+      <c r="D645" t="str">
+        <v>月下美人 MX</v>
+      </c>
+      <c r="E645" t="str">
+        <v/>
+      </c>
+      <c r="F645" t="str">
+        <v>月下美人 MX</v>
+      </c>
+      <c r="G645" t="str">
+        <v>輕型SW路亞(岩魚・竹筴魚)</v>
+      </c>
+      <c r="H645" t="str">
+        <v>根钓,岸投</v>
+      </c>
+      <c r="I645" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1057_MX.jpg</v>
+      </c>
+      <c r="J645" t="str">
+        <v/>
+      </c>
+      <c r="K645" t="str">
+        <v/>
+      </c>
+      <c r="L645" t="str">
+        <v>輕型SW路亞(岩魚・竹筴魚)</v>
+      </c>
+      <c r="M645" t="str">
+        <v>夜裡綻放的花朵,持續綻放著更耀眼的光芒。 2005年,DAIWA產品陣容首度登場的輕量海水遊戲專用釣具『月下美人』。猶如絢爛盛放的花朵,月下美人翩然起舞,釣友亦隨之躍動。 月下美人釣具系列,專為應對近在咫尺卻需極致細膩手法的竹筴魚,以及藏身岩隙海藻縫隙、時刻戒備等待魚餌現身的老獪大型岩魚而進化。今後月下美人將持續與釣友共同進化,帶來前所未有的愉悅與樂趣。月下美人的絢麗光輝,將持續照亮輕海水釣場。 尖端調校技術與碳纖維單體式後握把,實現同級頂尖的操控靈敏度</v>
+      </c>
+      <c r="N645" t="str">
+        <v>39,500~43,500円</v>
+      </c>
+      <c r="O645" t="str">
+        <v/>
+      </c>
+      <c r="P645" t="str">
+        <v>夜裡綻放的花朵,持續綻放著更耀眼的光芒。 2005年,DAIWA產品陣容首度登場的輕量海水遊戲專用釣具『月下美人』。猶如絢爛盛放的花朵,月下美人翩然起舞,釣友亦隨之躍動。 月下美人釣具系列,專為應對近在咫尺卻需極致細膩手法的竹筴魚,以及藏身岩隙海藻縫隙、時刻戒備等待魚餌現身的老獪大型岩魚而進化。今後月下美人將持續與釣友共同進化,帶來前所未有的愉悅與樂趣。月下美人的絢麗光輝,將持續照亮輕海水釣場。 尖端調校技術與碳纖維單體式後握把,實現同級頂尖的操控靈敏度</v>
+      </c>
+      <c r="Q645" t="str">
+        <v>轻海水 / Ajing・Mebaring / 港湾精细</v>
+      </c>
+      <c r="R645" t="str">
+        <v>以轻量 jighead、小软饵和 micro plug 为核心，适合港湾、堤防和小型岩礁的细线控饵。</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="str">
+        <v>DR1058</v>
+      </c>
+      <c r="B646">
+        <v>2</v>
+      </c>
+      <c r="C646" t="str">
+        <v>銀狼 MX</v>
+      </c>
+      <c r="D646" t="str">
+        <v>銀狼 MX</v>
+      </c>
+      <c r="E646" t="str">
+        <v/>
+      </c>
+      <c r="F646" t="str">
+        <v>銀狼 MX</v>
+      </c>
+      <c r="G646" t="str">
+        <v>黑鯛路亞</v>
+      </c>
+      <c r="H646" t="str">
+        <v>岸投</v>
+      </c>
+      <c r="I646" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1058_MX.jpg</v>
+      </c>
+      <c r="J646" t="str">
+        <v/>
+      </c>
+      <c r="K646" t="str">
+        <v/>
+      </c>
+      <c r="L646" t="str">
+        <v>黑鯛路亞</v>
+      </c>
+      <c r="M646" t="str">
+        <v>全新黑鯛專用調性正式登場,以壓倒性的漁獲落差席捲戰場! 實現自由釣組(Free Rig)」精細微小動作的極致操控。 能在瞬間洞察黑鯛魚訊,並即刻做出持續誘魚或上鉤起魚的應對判斷。 在這種釣法中,不易產生釣線鬆弛的小烏龜捲線器具備絕對優勢。 為了更盡情享受使用細號 PE 線的黑鯛路亞遊戲, 釣竿所需的關鍵要素大致可分為三點。 DAIWA 技術 SVF碳纖維 SVF碳纖維是比HVF進一步減少樹脂含量,並緊密填入更多碳纖維,實現輕量化、力量和細身化。 產品詳情 無論捲線器性能如何進化,若釣竿無法完美承載路亞重量,便無法獲得拋投時所需的初始速度。本系列針對自由釣組(Free Rig)」最常使用的 1/4 ~ 3/4oz (7~21g) 鉛錘配置進行精準調校。憑藉著極致對標的後節竿力量以及能迅速抑制顫動的輕量化穗尖,不僅能有效防止細 PE 線斷裂或纏線問題,只需輕輕揮竿,即可感受路亞如流星般自然射出的爽快拋投感。此外,適度的後節動力設計,除了能防止因瞬間揚竿力道過猛導致的斷線外,更隱藏了一個迷人的調味劑——那就是透過釣竿的完美弧度,讓釣手能盡情享受黑鯛強勁衝刺的搏魚樂趣。 這款小烏龜路亞竿以絕妙平衡配置了柔韌感與彈性,讓釣手無需時刻擔心細號 PE 線的負擔,即可享受暢快淋漓的拋投手感。透過對動力與韌性的極致鑽研,徹底解決了拋投斷線與上鉤斷線的隱憂。穗尖搭載高彈性實心穗尖,能精確感知淤泥與砂地間的細微差異,同時兼顧了優異的就餌性能與感度。這是一款能細膩感受黑鯛魚訊並主動出擊作合,定義黑鯛路亞釣法新基準的高性能釣竿。</v>
+      </c>
+      <c r="N646" t="str">
+        <v>37,000~38,500円</v>
+      </c>
+      <c r="O646" t="str">
+        <v/>
+      </c>
+      <c r="P646" t="str">
+        <v>全新黑鯛專用調性正式登場,以壓倒性的漁獲落差席捲戰場! 實現自由釣組(Free Rig)」精細微小動作的極致操控。 能在瞬間洞察黑鯛魚訊,並即刻做出持續誘魚或上鉤起魚的應對判斷。 在這種釣法中,不易產生釣線鬆弛的小烏龜捲線器具備絕對優勢。 為了更盡情享受使用細號 PE 線的黑鯛路亞遊戲, 釣竿所需的關鍵要素大致可分為三點。 DAIWA 技術 SVF碳纖維 SVF碳纖維是比HVF進一步減少樹脂含量,並緊密填入更多碳纖維,實現輕量化、力量和細身化。 產品詳情 無論捲線器性能如何進化,若釣竿無法完美承載路亞重量,便無法獲得拋投時所需的初始速度。本系列針對自由釣組(Free Rig)」最常使用的 1/4 ~ 3/4oz (7~21g) 鉛錘配置進行精準調校。憑藉著極致對標的後節竿力量以及能迅速抑制顫動的輕量化穗尖,不僅能有效防止細 PE 線斷裂或纏線問題,只需輕輕揮竿,即可感受路亞如流星般自然射出的爽快拋投感。此外,適度的後節動力設計,除了能防止因瞬間揚竿力道過猛導致的斷線外,更隱藏了一個迷人的調味劑——那就是透過釣竿的完美弧度,讓釣手能盡情享受黑鯛強勁衝刺的搏魚樂趣。 這款小烏龜路亞竿以絕妙平衡配置了柔韌感與彈性,讓釣手無需時刻擔心細號 PE 線的負擔,即可享受暢快淋漓的拋投手感。透過對動力與韌性的極致鑽研,徹底解決了拋投斷線與上鉤斷線的隱憂。穗尖搭載高彈性實心穗尖,能精確感知淤泥與砂地間的細微差異,同時兼顧了優異的就餌性能與感度。這是一款能細膩感受黑鯛魚訊並主動出擊作合,定義黑鯛路亞釣法新基準的高性能釣竿。</v>
+      </c>
+      <c r="Q646" t="str">
+        <v>黑鲷路亚 / Free Rig / 岸边底层攻略</v>
+      </c>
+      <c r="R646" t="str">
+        <v>围绕 free rig、Texas 和小型硬饵建立贴底搜索能力，适合河口、港湾与浅滩障碍边。</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="str">
+        <v>DR1059</v>
+      </c>
+      <c r="B647">
+        <v>2</v>
+      </c>
+      <c r="C647" t="str">
+        <v>DRAGGER X</v>
+      </c>
+      <c r="D647" t="str">
+        <v>DRAGGER X</v>
+      </c>
+      <c r="E647" t="str">
+        <v/>
+      </c>
+      <c r="F647" t="str">
+        <v>DRAGGER X</v>
+      </c>
+      <c r="G647" t="str">
+        <v>海水岸邊鐵板</v>
+      </c>
+      <c r="H647" t="str">
+        <v>岸投</v>
+      </c>
+      <c r="I647" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1059_DRAGGER_X.jpg</v>
+      </c>
+      <c r="J647" t="str">
+        <v/>
+      </c>
+      <c r="K647" t="str">
+        <v/>
+      </c>
+      <c r="L647" t="str">
+        <v>海水岸邊鐵板</v>
+      </c>
+      <c r="M647" t="str">
+        <v>高功率卻不易疲勞,無故障的岸釣鐵板釣法入門釣竿 為超越鄰近釣友的拋投距離,捕獲更大型魚獲,我們打造出強化力量的岸釣鐵板釣法竿「DRAGGER」。採用編織X強化技術打造的堅韌竿身,能從容應對從輕量到重型路亞的操作需求。在提升強度的同時大幅調整竿性,即使持續整日拋投與抽竿動作亦不易疲勞,更能流暢執行快慢交錯的誘魚誘魚動作。搭載K導環系統大幅減少線材纏繞問題,樹立岸釣鐵板釣法入門級新標竿。 特徵 1適用於大魚的高功率・高強度 2長時間搖曳也不易疲勞的『新』調性 3不易發生線材糾結的K導環 ※ML~MH為空氣感應器座椅,H以上為DPS座椅規格 DAIWA 技術 BRAIDING X 用碳纖維帶將竿身尾節的最外層以X狀纏繞,釣竿操作時,抑制了會導致力量損耗的扭轉的強化結構。竿身本身保持纖細的同時,也確保了高強度,並降低手持時的重量感,從而提升操作性。 ※並接、逆並接的品項,於空白區域全面搭載編織X。 產品詳情 為配合現代釣場大魚化趨勢,特此設定相應的動力等級。大幅強化竿體骨架強度,全竿採用編織X技術,有效抑制扭轉造成的動力損耗。 ※振出模型僅限竿尾部分。</v>
+      </c>
+      <c r="N647" t="str">
+        <v>23,000~37,500円</v>
+      </c>
+      <c r="O647" t="str">
+        <v/>
+      </c>
+      <c r="P647" t="str">
+        <v>高功率卻不易疲勞,無故障的岸釣鐵板釣法入門釣竿 為超越鄰近釣友的拋投距離,捕獲更大型魚獲,我們打造出強化力量的岸釣鐵板釣法竿「DRAGGER」。採用編織X強化技術打造的堅韌竿身,能從容應對從輕量到重型路亞的操作需求。在提升強度的同時大幅調整竿性,即使持續整日拋投與抽竿動作亦不易疲勞,更能流暢執行快慢交錯的誘魚誘魚動作。搭載K導環系統大幅減少線材纏繞問題,樹立岸釣鐵板釣法入門級新標竿。 特徵 1適用於大魚的高功率・高強度 2長時間搖曳也不易疲勞的『新』調性 3不易發生線材糾結的K導環 ※ML~MH為空氣感應器座椅,H以上為DPS座椅規格 DAIWA 技術 BRAIDING X 用碳纖維帶將竿身尾節的最外層以X狀纏繞,釣竿操作時,抑制了會導致力量損耗的扭轉的強化結構。竿身本身保持纖細的同時,也確保了高強度,並降低手持時的重量感,從而提升操作性。 ※並接、逆並接的品項,於空白區域全面搭載編織X。 產品詳情 為配合現代釣場大魚化趨勢,特此設定相應的動力等級。大幅強化竿體骨架強度,全竿採用編織X技術,有效抑制扭轉造成的動力損耗。 ※振出模型僅限竿尾部分。</v>
+      </c>
+      <c r="Q647" t="str">
+        <v>岸投铁板 / 青物 / 远投强负荷</v>
+      </c>
+      <c r="R647" t="str">
+        <v>覆盖金属铁板、重型 plug 和高负荷控鱼场景，重点在远投、抽停节奏和持续搏鱼余量。</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="str">
+        <v>DR1060</v>
+      </c>
+      <c r="B648">
+        <v>2</v>
+      </c>
+      <c r="C648" t="str">
+        <v>DRAGGER MX</v>
+      </c>
+      <c r="D648" t="str">
+        <v>DRAGGER MX</v>
+      </c>
+      <c r="E648" t="str">
+        <v/>
+      </c>
+      <c r="F648" t="str">
+        <v>DRAGGER MX</v>
+      </c>
+      <c r="G648" t="str">
+        <v>海水岸邊鐵板</v>
+      </c>
+      <c r="H648" t="str">
+        <v>岸投</v>
+      </c>
+      <c r="I648" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1060_DRAGGER_MX.jpg</v>
+      </c>
+      <c r="J648" t="str">
+        <v/>
+      </c>
+      <c r="K648" t="str">
+        <v/>
+      </c>
+      <c r="L648" t="str">
+        <v>海水岸邊鐵板</v>
+      </c>
+      <c r="M648" t="str">
+        <v>追求「更遠的飛距與俐落的操作性」輕量設計的堅持灣岸岸釣鐵板釣法釣竿 DAIWA 技術 X45 為了防止在拋投、操作、上鉤、搏魚等動作中產生的扭轉,長年研究結果顯示,除了傳統結構(相對於竿尖0°、90°)外,再捲繞「45°」偏置交叉布(±45°傾斜的碳纖維等)是防止扭轉的最佳選擇。搭載X45,實現防止扭轉,並使力量、操作性和感度得到飛躍性提升。 產品詳情 為使竿尖更輕盈而進行的設計,即使長時間操作鐵板也能減少疲勞感。此外,因竿尖輕量化,對於近年使用頻率較高的米諾、刀片等誘餌所產生的水流阻力感知力亦有所提升。 專為障礙物較少的港灣區域設計的概念,使其在同價位岸釣竹筴魚釣竿中展現出無與倫比的輕快特性。同時具備強勁的竿尾力量,能有效防止魚類主導釣況。</v>
+      </c>
+      <c r="N648" t="str">
+        <v>28,500~35,000円</v>
+      </c>
+      <c r="O648" t="str">
+        <v/>
+      </c>
+      <c r="P648" t="str">
+        <v>追求「更遠的飛距與俐落的操作性」輕量設計的堅持灣岸岸釣鐵板釣法釣竿 DAIWA 技術 X45 為了防止在拋投、操作、上鉤、搏魚等動作中產生的扭轉,長年研究結果顯示,除了傳統結構(相對於竿尖0°、90°)外,再捲繞「45°」偏置交叉布(±45°傾斜的碳纖維等)是防止扭轉的最佳選擇。搭載X45,實現防止扭轉,並使力量、操作性和感度得到飛躍性提升。 產品詳情 為使竿尖更輕盈而進行的設計,即使長時間操作鐵板也能減少疲勞感。此外,因竿尖輕量化,對於近年使用頻率較高的米諾、刀片等誘餌所產生的水流阻力感知力亦有所提升。 專為障礙物較少的港灣區域設計的概念,使其在同價位岸釣竹筴魚釣竿中展現出無與倫比的輕快特性。同時具備強勁的竿尾力量,能有效防止魚類主導釣況。</v>
+      </c>
+      <c r="Q648" t="str">
+        <v>岸投铁板 / 青物 / 远投强负荷</v>
+      </c>
+      <c r="R648" t="str">
+        <v>覆盖金属铁板、重型 plug 和高负荷控鱼场景，重点在远投、抽停节奏和持续搏鱼余量。</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="str">
+        <v>DR1061</v>
+      </c>
+      <c r="B649">
+        <v>2</v>
+      </c>
+      <c r="C649" t="str">
+        <v>WiseStream</v>
+      </c>
+      <c r="D649" t="str">
+        <v>WiseStream</v>
+      </c>
+      <c r="E649" t="str">
+        <v/>
+      </c>
+      <c r="F649" t="str">
+        <v>WiseStream</v>
+      </c>
+      <c r="G649" t="str">
+        <v>鱒魚・飛蠅釣法</v>
+      </c>
+      <c r="H649" t="str">
+        <v>溪流</v>
+      </c>
+      <c r="I649" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1061_WiseStream.jpg</v>
+      </c>
+      <c r="J649" t="str">
+        <v/>
+      </c>
+      <c r="K649" t="str">
+        <v/>
+      </c>
+      <c r="L649" t="str">
+        <v>鱒魚・飛蠅釣法</v>
+      </c>
+      <c r="M649" t="str">
+        <v>基本性能充實。採用伸縮式多功能設計的鱒魚釣竿標準型號 追求的是在便攜性中蘊藏的快適使用感。 伸縮式、多功能品項具備優異的便攜性,無論搭乘大眾運輸工具時,或是前往目的地路途遙遠時,皆能發揮其便利性,適用情境相當廣泛。 然而,容易出現彎曲不自然、張力過強、沉重等缺點。 22WISE STREAM徹底排除這些負面因素。 描繪出令人誤以為是單節釣竿的彎曲曲線,從頭重新審視釣竿動作,徹底革新為能快適使用輕量路亞的調性。 握把周圍亦沿襲銀溪系列的細徑設計。 此外,全系列產品皆以多功能或伸縮式設計推出。 這支釣竿的完成度,讓人無論身在何處都想隨身攜帶。 DAIWA 技術 X45 為了防止在拋投、操作、上鉤、搏魚等動作中產生的扭轉,長年研究結果顯示,除了傳統結構(相對於竿尖0°、90°)外,再捲繞「45°」偏置交叉布(±45°傾斜的碳纖維等)是防止扭轉的最佳選擇。搭載X45,實現防止扭轉,並使力量、操作性和感度得到飛躍性提升。 產品詳情 握柄粗細適中,既不易太粗亦不過細,便於施加路亞動作,且在拋投時能輕鬆施力. 魚餌採用短扳機設計,實現靈活拋投。捲線器座選用每根紋理各異的天然木料。 ■其他規格詳情 木製捲線器座</v>
+      </c>
+      <c r="N649" t="str">
+        <v>25,000~33,500円</v>
+      </c>
+      <c r="O649" t="str">
+        <v/>
+      </c>
+      <c r="P649" t="str">
+        <v>基本性能充實。採用伸縮式多功能設計的鱒魚釣竿標準型號 追求的是在便攜性中蘊藏的快適使用感。 伸縮式、多功能品項具備優異的便攜性,無論搭乘大眾運輸工具時,或是前往目的地路途遙遠時,皆能發揮其便利性,適用情境相當廣泛。 然而,容易出現彎曲不自然、張力過強、沉重等缺點。 22WISE STREAM徹底排除這些負面因素。 描繪出令人誤以為是單節釣竿的彎曲曲線,從頭重新審視釣竿動作,徹底革新為能快適使用輕量路亞的調性。 握把周圍亦沿襲銀溪系列的細徑設計。 此外,全系列產品皆以多功能或伸縮式設計推出。 這支釣竿的完成度,讓人無論身在何處都想隨身攜帶。 DAIWA 技術 X45 為了防止在拋投、操作、上鉤、搏魚等動作中產生的扭轉,長年研究結果顯示,除了傳統結構(相對於竿尖0°、90°)外,再捲繞「45°」偏置交叉布(±45°傾斜的碳纖維等)是防止扭轉的最佳選擇。搭載X45,實現防止扭轉,並使力量、操作性和感度得到飛躍性提升。 產品詳情 握柄粗細適中,既不易太粗亦不過細,便於施加路亞動作,且在拋投時能輕鬆施力. 魚餌採用短扳機設計,實現靈活拋投。捲線器座選用每根紋理各異的天然木料。 ■其他規格詳情 木製捲線器座</v>
+      </c>
+      <c r="Q649" t="str">
+        <v>溪流鳟鱼 / Native trout / 轻量硬饵</v>
+      </c>
+      <c r="R649" t="str">
+        <v>按溪流宽度和携带方式选择长度，适合米诺、spoon 和 spinner 的短中距离精准抛投。</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="str">
+        <v>DR1062</v>
+      </c>
+      <c r="B650">
+        <v>2</v>
+      </c>
+      <c r="C650" t="str">
+        <v>HRF</v>
+      </c>
+      <c r="D650" t="str">
+        <v>HRF</v>
+      </c>
+      <c r="E650" t="str">
+        <v/>
+      </c>
+      <c r="F650" t="str">
+        <v>HRF</v>
+      </c>
+      <c r="G650" t="str">
+        <v>HRF(根魚路亞釣)</v>
+      </c>
+      <c r="H650" t="str">
+        <v>根钓,岸投</v>
+      </c>
+      <c r="I650" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1062_HRF.jpg</v>
+      </c>
+      <c r="J650" t="str">
+        <v/>
+      </c>
+      <c r="K650" t="str">
+        <v/>
+      </c>
+      <c r="L650" t="str">
+        <v>HRF(根魚路亞釣)</v>
+      </c>
+      <c r="M650" t="str">
+        <v>HRF釣竿具備令中階至高階釣手都深感滿意的高度靈敏度與操作性。 輕量與強勁性能兼備,作為岩魚釣竿入門款廣受好評的HRF系列,此次搭載空氣感應器座全面升級,大幅提升靈敏度與操控性。從漁港到岩岸皆能應對的無死角產品陣容,將包圍全國岩魚棲息地。 DAIWA 技術 X45 為了防止在拋投、操作、上鉤、搏魚等動作中產生的扭轉,長年研究結果顯示,除了傳統結構(相對於竿尖0°、90°)外,再捲繞「45°」偏置交叉布(±45°傾斜的碳纖維等)是防止扭轉的最佳選擇。搭載X45,實現防止扭轉,並使力量、操作性和感度得到飛躍性提升。</v>
+      </c>
+      <c r="N650" t="str">
+        <v>26,500~28,500円</v>
+      </c>
+      <c r="O650" t="str">
+        <v/>
+      </c>
+      <c r="P650" t="str">
+        <v>HRF釣竿具備令中階至高階釣手都深感滿意的高度靈敏度與操作性。 輕量與強勁性能兼備,作為岩魚釣竿入門款廣受好評的HRF系列,此次搭載空氣感應器座全面升級,大幅提升靈敏度與操控性。從漁港到岩岸皆能應對的無死角產品陣容,將包圍全國岩魚棲息地。 DAIWA 技術 X45 為了防止在拋投、操作、上鉤、搏魚等動作中產生的扭轉,長年研究結果顯示,除了傳統結構(相對於竿尖0°、90°)外,再捲繞「45°」偏置交叉布(±45°傾斜的碳纖維等)是防止扭轉的最佳選擇。搭載X45,實現防止扭轉,並使力量、操作性和感度得到飛躍性提升。</v>
+      </c>
+      <c r="Q650" t="str">
+        <v>根鱼路亚 / Rockfish / 底层结构</v>
+      </c>
+      <c r="R650" t="str">
+        <v>适合用 free rig、Texas、jighead 和 shad 贴底找结构，兼顾远投、读底和障碍边控鱼。</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="str">
+        <v>DR1063</v>
+      </c>
+      <c r="B651">
+        <v>2</v>
+      </c>
+      <c r="C651" t="str">
+        <v>B.B.B (Triple B)</v>
+      </c>
+      <c r="D651" t="str">
+        <v>B.B.B (Triple B)</v>
+      </c>
+      <c r="E651" t="str">
+        <v/>
+      </c>
+      <c r="F651" t="str">
+        <v>B.B.B (Triple B)</v>
+      </c>
+      <c r="G651" t="str">
+        <v>鱸魚</v>
+      </c>
+      <c r="H651" t="str">
+        <v>bass</v>
+      </c>
+      <c r="I651" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1063_B_B_B_Triple_B.jpg</v>
+      </c>
+      <c r="J651" t="str">
+        <v/>
+      </c>
+      <c r="K651" t="str">
+        <v/>
+      </c>
+      <c r="L651" t="str">
+        <v>鱸魚</v>
+      </c>
+      <c r="M651" t="str">
+        <v>讓釣魚變得更貼近生活的便於攜帶釣具 比 2 節竿更加輕巧緊湊的振出式釣竿。只要收納在專用包中隨身攜帶,無論何時何地都能享受黑鱸釣的樂趣。當然,在裝備性能上也不想有任何妥協。 真正實現釣友這項夢想的,正是 DAIWA 的「B.B.B. (Triple B)」。能將所需的裝備以 All-in-one 的方式隨身攜帶,開啟全新的行動化裝備岸釣風格。 不僅限於黑鱸,舉凡管理釣場、溪流鱒魚,或是海邊的輕量路亞遊戲等,是一款不分場景、能隨心所欲享受釣魚樂趣的實用行動化裝備。 產品詳情 所有款式均附贈內含緩衝墊的釣竿收納包,即使裝著捲線器也能直接收納。除了專用包外,也能輕鬆放入隨身包袋,讓您隨處輕鬆攜帶。</v>
+      </c>
+      <c r="N651" t="str">
+        <v>23,400~24,400円</v>
+      </c>
+      <c r="O651" t="str">
+        <v/>
+      </c>
+      <c r="P651" t="str">
+        <v>讓釣魚變得更貼近生活的便於攜帶釣具 比 2 節竿更加輕巧緊湊的振出式釣竿。只要收納在專用包中隨身攜帶,無論何時何地都能享受黑鱸釣的樂趣。當然,在裝備性能上也不想有任何妥協。 真正實現釣友這項夢想的,正是 DAIWA 的「B.B.B. (Triple B)」。能將所需的裝備以 All-in-one 的方式隨身攜帶,開啟全新的行動化裝備岸釣風格。 不僅限於黑鱸,舉凡管理釣場、溪流鱒魚,或是海邊的輕量路亞遊戲等,是一款不分場景、能隨心所欲享受釣魚樂趣的實用行動化裝備。 產品詳情 所有款式均附贈內含緩衝墊的釣竿收納包,即使裝著捲線器也能直接收納。除了專用包外,也能輕鬆放入隨身包袋,讓您隨處輕鬆攜帶。</v>
+      </c>
+      <c r="Q651" t="str">
+        <v>淡水 Bass / 技法分工 / 软硬饵覆盖</v>
+      </c>
+      <c r="R651" t="str">
+        <v>按子型号区分精细、卷阻、底操、cover 和大饵路线，适合依照钓组与作钓距离选型。</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="str">
+        <v>DR1064</v>
+      </c>
+      <c r="B652">
+        <v>2</v>
+      </c>
+      <c r="C652" t="str">
+        <v>PURELIST</v>
+      </c>
+      <c r="D652" t="str">
+        <v>PURELIST</v>
+      </c>
+      <c r="E652" t="str">
+        <v/>
+      </c>
+      <c r="F652" t="str">
+        <v>PURELIST</v>
+      </c>
+      <c r="G652" t="str">
+        <v>鱒魚・飛蠅釣法</v>
+      </c>
+      <c r="H652" t="str">
+        <v>溪流</v>
+      </c>
+      <c r="I652" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1064_PURELIST.jpg</v>
+      </c>
+      <c r="J652" t="str">
+        <v/>
+      </c>
+      <c r="K652" t="str">
+        <v/>
+      </c>
+      <c r="L652" t="str">
+        <v>鱒魚・飛蠅釣法</v>
+      </c>
+      <c r="M652" t="str">
+        <v>適用於各種情境的專用調性原生鱒魚釣竿 兼具嶄新外觀與嶄新使用感的原生鱒魚釣竿標準型號。原生鱒魚釣竿的標準之作「PURELIST」。 大幅調整前作的調性,推出涵蓋湯匙、旋轉鉤乃至沉水型米諾釣法的廣泛產品陣容。 採用X45碳纖維編織結構,透過捲線排除扭轉現象,使翻竿拋投與反手拋投等技術性拋投動作皆能隨心所欲地施展。 外觀採用講究的米色系配色,搭配同色系導引線。 握柄部分同樣沿用銀溪系列的細徑木製捲線器座,釣竿則採用短扳機設計,不僅具備媲美高階機型的使用手感,更打造出人人皆能輕鬆駕馭的釣竿。 本次新增的「48XUL」與「46XULB」兩款,無論為旋轉式或魚餌式釣組類型,皆能輕鬆操控約40mm、3g左右的路亞,共計兩款型號。 這款品項能讓任何人都輕鬆彎曲,實現精準拋投(Accuracy Cast),助您拉近與溪魚的距離。 DAIWA 技術 X45 為了防止在拋投、操作、上鉤、搏魚等動作中產生的扭轉,長年研究結果顯示,除了傳統結構(相對於竿尖0°、90°)外,再捲繞「45°」偏置交叉布(±45°傾斜的碳纖維等)是防止扭轉的最佳選擇。搭載X45,實現防止扭轉,並使力量、操作性和感度得到飛躍性提升。 產品詳情 採用天然木捲線器座,提供媲美高階機型的使用體驗。軟木握柄亦採用纖細設計,帶來快適握感。</v>
+      </c>
+      <c r="N652" t="str">
+        <v>19,900~24,300円</v>
+      </c>
+      <c r="O652" t="str">
+        <v>additional</v>
+      </c>
+      <c r="P652" t="str">
+        <v>適用於各種情境的專用調性原生鱒魚釣竿 兼具嶄新外觀與嶄新使用感的原生鱒魚釣竿標準型號。原生鱒魚釣竿的標準之作「PURELIST」。 大幅調整前作的調性,推出涵蓋湯匙、旋轉鉤乃至沉水型米諾釣法的廣泛產品陣容。 採用X45碳纖維編織結構,透過捲線排除扭轉現象,使翻竿拋投與反手拋投等技術性拋投動作皆能隨心所欲地施展。 外觀採用講究的米色系配色,搭配同色系導引線。 握柄部分同樣沿用銀溪系列的細徑木製捲線器座,釣竿則採用短扳機設計,不僅具備媲美高階機型的使用手感,更打造出人人皆能輕鬆駕馭的釣竿。 本次新增的「48XUL」與「46XULB」兩款,無論為旋轉式或魚餌式釣組類型,皆能輕鬆操控約40mm、3g左右的路亞,共計兩款型號。 這款品項能讓任何人都輕鬆彎曲,實現精準拋投(Accuracy Cast),助您拉近與溪魚的距離。 DAIWA 技術 X45 為了防止在拋投、操作、上鉤、搏魚等動作中產生的扭轉,長年研究結果顯示,除了傳統結構(相對於竿尖0°、90°)外,再捲繞「45°」偏置交叉布(±45°傾斜的碳纖維等)是防止扭轉的最佳選擇。搭載X45,實現防止扭轉,並使力量、操作性和感度得到飛躍性提升。 產品詳情 採用天然木捲線器座,提供媲美高階機型的使用體驗。軟木握柄亦採用纖細設計,帶來快適握感。</v>
+      </c>
+      <c r="Q652" t="str">
+        <v>溪流鳟鱼 / Native trout / 轻量硬饵</v>
+      </c>
+      <c r="R652" t="str">
+        <v>按溪流宽度和携带方式选择长度，适合米诺、spoon 和 spinner 的短中距离精准抛投。</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="str">
+        <v>DR1065</v>
+      </c>
+      <c r="B653">
+        <v>2</v>
+      </c>
+      <c r="C653" t="str">
+        <v>銀狼</v>
+      </c>
+      <c r="D653" t="str">
+        <v>銀狼</v>
+      </c>
+      <c r="E653" t="str">
+        <v/>
+      </c>
+      <c r="F653" t="str">
+        <v>銀狼</v>
+      </c>
+      <c r="G653" t="str">
+        <v>黑鯛路亞</v>
+      </c>
+      <c r="H653" t="str">
+        <v>岸投</v>
+      </c>
+      <c r="I653" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1065_main.jpg</v>
+      </c>
+      <c r="J653" t="str">
+        <v/>
+      </c>
+      <c r="K653" t="str">
+        <v/>
+      </c>
+      <c r="L653" t="str">
+        <v>黑鯛路亞</v>
+      </c>
+      <c r="M653" t="str">
+        <v>支援自由鉤組!鱸魚入門釣竿的終極之作 鱸魚釣竿入門款「銀狼」以全新概念「都市鱸釣」為主題進行改款升級。 採用與高階機型共享設計理念的硬質實心尖端、輕量化且易於拋投的竿體,以及多點配置的小徑導環,大幅提升操作性能。 以自由釣組等底層釣組為核心,廣泛適用於頂水插鉤、沉水鉛筆型路亞、黑鯛魂等釣組的系列產品。具備流暢無滯曳的拋投性能、優異的路亞操控性,以及能即時轉為刺魚動作、絕不延遲黑鯛咬餌反應的靈敏度。 品項組合包含兩款魚餌品項與兩款旋轉式釣具。此配置亦顧及對魚餌釣法存有抗拒的初學者需求。 DAIWA 技術 MEGA TOP MEGA TOP是一種纖維與樹脂均勻分佈的碳纖維實心材料,無論從哪個方向彎曲都展現相同的彎曲度。其強度比一般碳纖維實心材料飛躍性提升。這使得製造出細徑、柔軟、高錐形形狀的竿尖成為可能,不僅增強了傳遞魚訊至手掌的感度,更傳遞視覺感知,打造出精準捕捉魚訊的彎曲竿尖。 產品詳情 採用比以往更具張力的實心尖端,並將實心部分縮短, (1)實現精細的路亞操控性 (2)實現路亞如在水底爬行般的自然動作 (3)誘發黑鯛咬餌時減少不適感 (4)實現提升鉤魚反應 更能品味垂釣的醍醐味與深奧之處。 品項別特徵 ScrollLeft</v>
+      </c>
+      <c r="N653" t="str">
+        <v>22,500~23,500円</v>
+      </c>
+      <c r="O653" t="str">
+        <v/>
+      </c>
+      <c r="P653" t="str">
+        <v>支援自由鉤組!鱸魚入門釣竿的終極之作 鱸魚釣竿入門款「銀狼」以全新概念「都市鱸釣」為主題進行改款升級。 採用與高階機型共享設計理念的硬質實心尖端、輕量化且易於拋投的竿體,以及多點配置的小徑導環,大幅提升操作性能。 以自由釣組等底層釣組為核心,廣泛適用於頂水插鉤、沉水鉛筆型路亞、黑鯛魂等釣組的系列產品。具備流暢無滯曳的拋投性能、優異的路亞操控性,以及能即時轉為刺魚動作、絕不延遲黑鯛咬餌反應的靈敏度。 品項組合包含兩款魚餌品項與兩款旋轉式釣具。此配置亦顧及對魚餌釣法存有抗拒的初學者需求。 DAIWA 技術 MEGA TOP MEGA TOP是一種纖維與樹脂均勻分佈的碳纖維實心材料,無論從哪個方向彎曲都展現相同的彎曲度。其強度比一般碳纖維實心材料飛躍性提升。這使得製造出細徑、柔軟、高錐形形狀的竿尖成為可能,不僅增強了傳遞魚訊至手掌的感度,更傳遞視覺感知,打造出精準捕捉魚訊的彎曲竿尖。 產品詳情 採用比以往更具張力的實心尖端,並將實心部分縮短, (1)實現精細的路亞操控性 (2)實現路亞如在水底爬行般的自然動作 (3)誘發黑鯛咬餌時減少不適感 (4)實現提升鉤魚反應 更能品味垂釣的醍醐味與深奧之處。 品項別特徵 ScrollLeft</v>
+      </c>
+      <c r="Q653" t="str">
+        <v>黑鲷路亚 / Free Rig / 岸边底层攻略</v>
+      </c>
+      <c r="R653" t="str">
+        <v>围绕 free rig、Texas 和小型硬饵建立贴底搜索能力，适合河口、港湾与浅滩障碍边。</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="str">
+        <v>DR1066</v>
+      </c>
+      <c r="B654">
+        <v>2</v>
+      </c>
+      <c r="C654" t="str">
+        <v>BLAZON</v>
+      </c>
+      <c r="D654" t="str">
+        <v>BLAZON</v>
+      </c>
+      <c r="E654" t="str">
+        <v/>
+      </c>
+      <c r="F654" t="str">
+        <v>BLAZON</v>
+      </c>
+      <c r="G654" t="str">
+        <v>鱸魚</v>
+      </c>
+      <c r="H654" t="str">
+        <v>bass</v>
+      </c>
+      <c r="I654" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1066_BLAZON.jpg</v>
+      </c>
+      <c r="J654" t="str">
+        <v/>
+      </c>
+      <c r="K654" t="str">
+        <v/>
+      </c>
+      <c r="L654" t="str">
+        <v>鱸魚</v>
+      </c>
+      <c r="M654" t="str">
+        <v>blaze on ー炎、立起ー 那份能觸及魚嘴邊緣的拋投距離、感知水中細微變化的靈敏度、瞬間完成刺魚的爆發力,以及在與大魚搏鬥時憑藉竿體黏性掌控主導權的實力。21布雷松所追求的,正是於日本黑鱸釣魚最前線淬鍊而成的、毫無虛飾的黑鱸釣竿本質。 DAIWA 技術 AIR SENSOR SEAT 透過加入碳纖維的AIR SENSOR SEAT,實現輕量化、高強度和高感度。根據釣竿的用途進行專門設計,帶來一般通用捲線器座無法體驗的操作性。 ※魚餌拋投型號:空心觸發式 / 旋轉型號:纖薄貼合式 產品詳情 魚餌モデルは「空白觸發」片,旋轉型則採用「SLIM貼合」片。 更改魚餌式與旋轉式標示法。採用「魚餌式:C、旋轉式:S」標示,2節式釣竿則於長度後方標註「-2」。</v>
+      </c>
+      <c r="N654" t="str">
+        <v>19,300~23,300円</v>
+      </c>
+      <c r="O654" t="str">
+        <v/>
+      </c>
+      <c r="P654" t="str">
+        <v>blaze on ー炎、立起ー 那份能觸及魚嘴邊緣的拋投距離、感知水中細微變化的靈敏度、瞬間完成刺魚的爆發力,以及在與大魚搏鬥時憑藉竿體黏性掌控主導權的實力。21布雷松所追求的,正是於日本黑鱸釣魚最前線淬鍊而成的、毫無虛飾的黑鱸釣竿本質。 DAIWA 技術 AIR SENSOR SEAT 透過加入碳纖維的AIR SENSOR SEAT,實現輕量化、高強度和高感度。根據釣竿的用途進行專門設計,帶來一般通用捲線器座無法體驗的操作性。 ※魚餌拋投型號:空心觸發式 / 旋轉型號:纖薄貼合式 產品詳情 魚餌モデルは「空白觸發」片,旋轉型則採用「SLIM貼合」片。 更改魚餌式與旋轉式標示法。採用「魚餌式:C、旋轉式:S」標示,2節式釣竿則於長度後方標註「-2」。</v>
+      </c>
+      <c r="Q654" t="str">
+        <v>淡水 Bass / 技法分工 / 软硬饵覆盖</v>
+      </c>
+      <c r="R654" t="str">
+        <v>按子型号区分精细、卷阻、底操、cover 和大饵路线，适合依照钓组与作钓距离选型。</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="str">
+        <v>DR1067</v>
+      </c>
+      <c r="B655">
+        <v>2</v>
+      </c>
+      <c r="C655" t="str">
+        <v>MOBILE PACK</v>
+      </c>
+      <c r="D655" t="str">
+        <v>MOBILE PACK</v>
+      </c>
+      <c r="E655" t="str">
+        <v/>
+      </c>
+      <c r="F655" t="str">
+        <v>MOBILE PACK</v>
+      </c>
+      <c r="G655" t="str">
+        <v>鱸魚</v>
+      </c>
+      <c r="H655" t="str">
+        <v>bass</v>
+      </c>
+      <c r="I655" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1067_MOBILE_PACK.jpg</v>
+      </c>
+      <c r="J655" t="str">
+        <v/>
+      </c>
+      <c r="K655" t="str">
+        <v/>
+      </c>
+      <c r="L655" t="str">
+        <v>鱸魚</v>
+      </c>
+      <c r="M655" t="str">
+        <v>搭載高感度俐落竿身,性能更卓越的振出式行動路亞竿。 「振出伸縮式路亞釣竿雖能緊湊收納相當便利,但相較於並繼式釣竿性能較差」。抱持此想法的釣友不在少數。為顛覆此認知,我們傾注心力設計出這款「Mobile Pack」伸縮式路亞釣竿。大量採用輕量高強度的HVF碳纖維打造出富有張力的竿身,實現更卓越的拋投性能,帶來更遠的飛距與更精準的拋投。不僅輕量化釣竿身,更在捲線器座搭載碳纖維製空氣感應器,將觸感靈敏度推向極致。多數移動式釣竿多以收納尺寸為設計優先,但本款Mobile Pack著眼於操作流暢性,透過優化捲線器座與握把造型,使釣竿性能更臻完美。從淡水到海水,九款適用於各類路亞釣法的竿款,將持續拓展路亞釣法的無限可能。 「振出式路亞竿雖然收納方便,但性能就是比並繼竿差」這是許多釣手的刻板印象。為了徹底翻轉這個想法,傾盡全力研發出這款Mobile Pack。大量採用輕量、高強度的 HVF 碳纖維,打造出強韌的竿身,實現了更佳的拋投性能,帶來更遠的飛行距離與精準度。除了輕量化竿身,捲線器座也搭載了碳纖維製的 AIR SENSOR,讓感度更為細膩銳利。一般的旅行竿往往優先考慮收納長度,但這款 Mobile Pack 則優先考慮操竿手感,針對捲線器座與握把形狀進行優化配置,進一步提升了整體的作釣性能。全系列共 9 個型號,能對應淡水到海水的各種路亞釣法,讓釣友擁有更多無限的可能。 DAIWA 技術 AIR SENSOR SEAT 透過加入碳纖維的AIR SENSOR SEAT,實現輕量化、高強度和高感度。根據釣竿的用途進行專門設計,帶來一般通用捲線器座無法體驗的操作性。 產品詳情 具備優異彈性與彎曲弧度完美的竿身,實現了俐落的拋投感。無論是精準的標的狙擊還是長距離遠投,都能展現游刃有餘的強悍竿身性能。 奢侈地搭載了通常僅用於高階竿款的碳纖維製 AIR SENSOR 捲線器座。由於材質升級為極輕量的碳纖維,不僅感度大幅提升,整體操竿的靈活性與平衡感也更進化。 無論河川、池塘、湖泊、港灣,或是沙灘與防波堤——在任何場域都能盡情發揮,帶給你百分之百的釣魚樂趣。 專欄:有何不同?CROSSBEAT SW 與 MOBILE PACK</v>
+      </c>
+      <c r="N655" t="str">
+        <v>17,000~21,900円</v>
+      </c>
+      <c r="O655" t="str">
+        <v/>
+      </c>
+      <c r="P655" t="str">
+        <v>搭載高感度俐落竿身,性能更卓越的振出式行動路亞竿。 「振出伸縮式路亞釣竿雖能緊湊收納相當便利,但相較於並繼式釣竿性能較差」。抱持此想法的釣友不在少數。為顛覆此認知,我們傾注心力設計出這款「Mobile Pack」伸縮式路亞釣竿。大量採用輕量高強度的HVF碳纖維打造出富有張力的竿身,實現更卓越的拋投性能,帶來更遠的飛距與更精準的拋投。不僅輕量化釣竿身,更在捲線器座搭載碳纖維製空氣感應器,將觸感靈敏度推向極致。多數移動式釣竿多以收納尺寸為設計優先,但本款Mobile Pack著眼於操作流暢性,透過優化捲線器座與握把造型,使釣竿性能更臻完美。從淡水到海水,九款適用於各類路亞釣法的竿款,將持續拓展路亞釣法的無限可能。 「振出式路亞竿雖然收納方便,但性能就是比並繼竿差」這是許多釣手的刻板印象。為了徹底翻轉這個想法,傾盡全力研發出這款Mobile Pack。大量採用輕量、高強度的 HVF 碳纖維,打造出強韌的竿身,實現了更佳的拋投性能,帶來更遠的飛行距離與精準度。除了輕量化竿身,捲線器座也搭載了碳纖維製的 AIR SENSOR,讓感度更為細膩銳利。一般的旅行竿往往優先考慮收納長度,但這款 Mobile Pack 則優先考慮操竿手感,針對捲線器座與握把形狀進行優化配置,進一步提升了整體的作釣性能。全系列共 9 個型號,能對應淡水到海水的各種路亞釣法,讓釣友擁有更多無限的可能。 DAIWA 技術 AIR SENSOR SEAT 透過加入碳纖維的AIR SENSOR SEAT,實現輕量化、高強度和高感度。根據釣竿的用途進行專門設計,帶來一般通用捲線器座無法體驗的操作性。 產品詳情 具備優異彈性與彎曲弧度完美的竿身,實現了俐落的拋投感。無論是精準的標的狙擊還是長距離遠投,都能展現游刃有餘的強悍竿身性能。 奢侈地搭載了通常僅用於高階竿款的碳纖維製 AIR SENSOR 捲線器座。由於材質升級為極輕量的碳纖維,不僅感度大幅提升,整體操竿的靈活性與平衡感也更進化。 無論河川、池塘、湖泊、港灣,或是沙灘與防波堤——在任何場域都能盡情發揮,帶給你百分之百的釣魚樂趣。 專欄:有何不同?CROSSBEAT SW 與 MOBILE PACK</v>
+      </c>
+      <c r="Q655" t="str">
+        <v>轻海水 / Ajing・Mebaring / 港湾精细</v>
+      </c>
+      <c r="R655" t="str">
+        <v>以轻量 jighead、小软饵和 micro plug 为核心，适合港湾、堤防和小型岩礁的细线控饵。</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="str">
+        <v>DR1068</v>
+      </c>
+      <c r="B656">
+        <v>2</v>
+      </c>
+      <c r="C656" t="str">
+        <v>月下美人 AJING</v>
+      </c>
+      <c r="D656" t="str">
+        <v>月下美人 AJING</v>
+      </c>
+      <c r="E656" t="str">
+        <v/>
+      </c>
+      <c r="F656" t="str">
+        <v>月下美人 AJING</v>
+      </c>
+      <c r="G656" t="str">
+        <v>輕型SW路亞(岩魚・竹筴魚)</v>
+      </c>
+      <c r="H656" t="str">
+        <v>根钓,岸投</v>
+      </c>
+      <c r="I656" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1068_AJING.jpg</v>
+      </c>
+      <c r="J656" t="str">
+        <v/>
+      </c>
+      <c r="K656" t="str">
+        <v/>
+      </c>
+      <c r="L656" t="str">
+        <v>輕型SW路亞(岩魚・竹筴魚)</v>
+      </c>
+      <c r="M656" t="str">
+        <v>夜裡綻放的花朵,持續綻放著更耀眼的光芒。 2005年,DAIWA產品陣容首度登場的輕量海水遊戲專用釣具『月下美人』。猶如絢爛盛放的花朵,月下美人翩然起舞,釣友亦隨之躍動。 月下美人釣具系列,專為應對近在咫尺卻需極致細膩手法的竹筴魚,以及藏身岩隙海藻縫隙、時刻戒備等待魚餌現身的老獪大型岩魚而進化。今後月下美人將持續與釣友共同進化,帶來前所未有的愉悅與樂趣。月下美人的絢麗光輝,將持續照亮輕海水釣場。 兼具更高層次輕量化與操作性的高性價比竹筴魚入門釣竿 採用高品質釣竿,能充分體驗以竿技誘魚、在下落停留時咬鉤的竹筴魚釣精髓,並配備易握緊湊握把以加速釣友反應的竹筴魚釣竿。雖屬入門級別,卻具備50克級超輕量與高感度設計。更透過DAIWA獨家導環配置實現優異放線性,使輕量路亞具備卓越遠投性能,夜間作釣時亦能順暢穿線。 DAIWA 技術 HVF碳纖維 DAIWA著眼於對釣竿性能影響最大的碳纖維布中,不僅追求碳纖維本身的高彈性化,也聚焦作為黏合劑的樹脂量。減少被稱為贅肉的樹脂量,相對增加碳纖維密度的「高密度HVF碳纖維」更具肌肉感和力量。它是最適合重視彈性和強度的釣竿材料。 產品詳情 搭載輕量化坯料,實現超越入門款的輕量化與靈敏度。</v>
+      </c>
+      <c r="N656" t="str">
+        <v>16,500~19,000円</v>
+      </c>
+      <c r="O656" t="str">
+        <v/>
+      </c>
+      <c r="P656" t="str">
+        <v>夜裡綻放的花朵,持續綻放著更耀眼的光芒。 2005年,DAIWA產品陣容首度登場的輕量海水遊戲專用釣具『月下美人』。猶如絢爛盛放的花朵,月下美人翩然起舞,釣友亦隨之躍動。 月下美人釣具系列,專為應對近在咫尺卻需極致細膩手法的竹筴魚,以及藏身岩隙海藻縫隙、時刻戒備等待魚餌現身的老獪大型岩魚而進化。今後月下美人將持續與釣友共同進化,帶來前所未有的愉悅與樂趣。月下美人的絢麗光輝,將持續照亮輕海水釣場。 兼具更高層次輕量化與操作性的高性價比竹筴魚入門釣竿 採用高品質釣竿,能充分體驗以竿技誘魚、在下落停留時咬鉤的竹筴魚釣精髓,並配備易握緊湊握把以加速釣友反應的竹筴魚釣竿。雖屬入門級別,卻具備50克級超輕量與高感度設計。更透過DAIWA獨家導環配置實現優異放線性,使輕量路亞具備卓越遠投性能,夜間作釣時亦能順暢穿線。 DAIWA 技術 HVF碳纖維 DAIWA著眼於對釣竿性能影響最大的碳纖維布中,不僅追求碳纖維本身的高彈性化,也聚焦作為黏合劑的樹脂量。減少被稱為贅肉的樹脂量,相對增加碳纖維密度的「高密度HVF碳纖維」更具肌肉感和力量。它是最適合重視彈性和強度的釣竿材料。 產品詳情 搭載輕量化坯料,實現超越入門款的輕量化與靈敏度。</v>
+      </c>
+      <c r="Q656" t="str">
+        <v>轻海水 / Ajing・Mebaring / 港湾精细</v>
+      </c>
+      <c r="R656" t="str">
+        <v>以轻量 jighead、小软饵和 micro plug 为核心，适合港湾、堤防和小型岩礁的细线控饵。</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="str">
+        <v>DR1069</v>
+      </c>
+      <c r="B657">
+        <v>2</v>
+      </c>
+      <c r="C657" t="str">
+        <v>BLAZON 行動版</v>
+      </c>
+      <c r="D657" t="str">
+        <v>BLAZON 行動版</v>
+      </c>
+      <c r="E657" t="str">
+        <v/>
+      </c>
+      <c r="F657" t="str">
+        <v>BLAZON 行動版</v>
+      </c>
+      <c r="G657" t="str">
+        <v>鱸魚</v>
+      </c>
+      <c r="H657" t="str">
+        <v>bass</v>
+      </c>
+      <c r="I657" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1069_BLAZON.jpg</v>
+      </c>
+      <c r="J657" t="str">
+        <v/>
+      </c>
+      <c r="K657" t="str">
+        <v/>
+      </c>
+      <c r="L657" t="str">
+        <v>鱸魚</v>
+      </c>
+      <c r="M657" t="str">
+        <v>追求鱸魚釣竿本質的移動式鱸魚釣竿。 666TMB: 從中大型硬式魚餌如潛泳路亞(Crank)、震動魚餌、旋轉魚餌,到無鉛釣組、重型下沉釣組、輕型德州釣組等各類釣法皆能駕馭。竿體採用兼具輕量與強度的HVF碳纖維,並搭載X型纏繞結構BRAIDING X技術,有效抑制扭轉力。 6106TMB: 從中大型硬式魚餌如潛泳路亞(Crank)、震動魚餌、旋轉魚餌,到無鉛釣組、重型下沉釣組、輕型德州釣組等各類釣法皆能駕馭。竿體採用兼具輕量與強度的HVF碳纖維,並搭載X型纏繞結構BRAIDING X技術,有效抑制扭轉力。 6106TMHB: 這款全能型強力釣竿,從重型硬餌如振動魚餌、旋轉魚餌,到高比重無鉛餌的倒滑釣法,乃至用於障礙物區域的鉛頭鉤、鐵板等皆能駕馭。竿體採用兼具輕量與強度的HVF碳纖維,並搭載X型纏繞結構BRAIDING X技術,有效抑制竿體扭轉。 646TLS: 在高壓化釣場中備受青睞的小型硬魚餌至輕量釣組,這款輕量型多功能釣竿能應對各種釣況。竿體採用兼具輕量與強度的HVF碳纖維,並搭載X型壓縮結構BRAIDING X技術,有效抑制扭轉現象。 666TLS: 在高壓化場域中備受青睞的小型硬魚餌至輕量釣組,皆能應對各種狀況的輕量多功能型號。竿體採用兼具輕量與強度的HVF碳纖維,並搭載X型壓縮結構BRAIDING X以抑制扭轉。 DAIWA 技術 HVF碳纖維 DAIWA著眼於對釣竿性能影響最大的碳纖維布中,不僅追求碳纖維本身的高彈性化,也聚焦作為黏合劑的樹脂量。減少被稱為贅肉的樹脂量,相對增加碳纖維密度的「高密度HVF碳纖維」更具肌肉感和力量。它是最適合重視彈性和強度的釣竿材料。 VIDEO</v>
+      </c>
+      <c r="N657" t="str">
+        <v>17,500~18,500円</v>
+      </c>
+      <c r="O657" t="str">
+        <v/>
+      </c>
+      <c r="P657" t="str">
+        <v>追求鱸魚釣竿本質的移動式鱸魚釣竿。 666TMB: 從中大型硬式魚餌如潛泳路亞(Crank)、震動魚餌、旋轉魚餌,到無鉛釣組、重型下沉釣組、輕型德州釣組等各類釣法皆能駕馭。竿體採用兼具輕量與強度的HVF碳纖維,並搭載X型纏繞結構BRAIDING X技術,有效抑制扭轉力。 6106TMB: 從中大型硬式魚餌如潛泳路亞(Crank)、震動魚餌、旋轉魚餌,到無鉛釣組、重型下沉釣組、輕型德州釣組等各類釣法皆能駕馭。竿體採用兼具輕量與強度的HVF碳纖維,並搭載X型纏繞結構BRAIDING X技術,有效抑制扭轉力。 6106TMHB: 這款全能型強力釣竿,從重型硬餌如振動魚餌、旋轉魚餌,到高比重無鉛餌的倒滑釣法,乃至用於障礙物區域的鉛頭鉤、鐵板等皆能駕馭。竿體採用兼具輕量與強度的HVF碳纖維,並搭載X型纏繞結構BRAIDING X技術,有效抑制竿體扭轉。 646TLS: 在高壓化釣場中備受青睞的小型硬魚餌至輕量釣組,這款輕量型多功能釣竿能應對各種釣況。竿體採用兼具輕量與強度的HVF碳纖維,並搭載X型壓縮結構BRAIDING X技術,有效抑制扭轉現象。 666TLS: 在高壓化場域中備受青睞的小型硬魚餌至輕量釣組,皆能應對各種狀況的輕量多功能型號。竿體採用兼具輕量與強度的HVF碳纖維,並搭載X型壓縮結構BRAIDING X以抑制扭轉。 DAIWA 技術 HVF碳纖維 DAIWA著眼於對釣竿性能影響最大的碳纖維布中,不僅追求碳纖維本身的高彈性化,也聚焦作為黏合劑的樹脂量。減少被稱為贅肉的樹脂量,相對增加碳纖維密度的「高密度HVF碳纖維」更具肌肉感和力量。它是最適合重視彈性和強度的釣竿材料。 VIDEO</v>
+      </c>
+      <c r="Q657" t="str">
+        <v>淡水 Bass / 技法分工 / 软硬饵覆盖</v>
+      </c>
+      <c r="R657" t="str">
+        <v>按子型号区分精细、卷阻、底操、cover 和大饵路线，适合依照钓组与作钓距离选型。</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="str">
+        <v>DR1070</v>
+      </c>
+      <c r="B658">
+        <v>2</v>
+      </c>
+      <c r="C658" t="str">
+        <v>SHOREJIGGING X</v>
+      </c>
+      <c r="D658" t="str">
+        <v>SHOREJIGGING X</v>
+      </c>
+      <c r="E658" t="str">
+        <v/>
+      </c>
+      <c r="F658" t="str">
+        <v>SHOREJIGGING X</v>
+      </c>
+      <c r="G658" t="str">
+        <v>海水岸邊鐵板</v>
+      </c>
+      <c r="H658" t="str">
+        <v>岸投</v>
+      </c>
+      <c r="I658" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1070_SHOREJIGGING_X.jpg</v>
+      </c>
+      <c r="J658" t="str">
+        <v/>
+      </c>
+      <c r="K658" t="str">
+        <v/>
+      </c>
+      <c r="L658" t="str">
+        <v>海水岸邊鐵板</v>
+      </c>
+      <c r="M658" t="str">
+        <v>高品質岸拋鐵板竿的入門款式。 在享受釣魚樂趣與品嚐美味的海水路亞釣中,特別容易瞄準大魚、感受強大拉力的便是岸拋鐵板。這款 SHORE JIGGING X 採用了易於投擲的調性,因此能輕易地從防波堤等地遠投金屬鐵板或水面系路亞,讓人輕鬆享受岸拋鐵板的樂趣。搭載了 BRAIDING X,採用不輸給魚拉力的強韌竿身。全面支援岸拋鐵板的入門階段。 DAIWA 技術 BRAIDING X 用碳纖維帶將竿身尾節的最外層以X狀纏繞,釣竿操作時,抑制了會導致力量損耗的扭轉的強化結構。竿身本身保持纖細的同時,也確保了高強度,並降低手持時的重量感,從而提升操作性。 產品詳情 藉由以 X 狀碳纖維帶補強,強化強勁的竿尾部分,成功打造出堅固且損耗力極少的竿體。 能將路亞投射至更遠的近海,並確實承受青物的拉力。即便在擁擠的防波堤釣到大魚,也能強勢地將魚拉近。 目標的基準 ScrollLeft 路亞適用表 MOVIE 測試者印象 在岸邊鐵板釣法入門階段,這款釣竿的規格已相當完善。首先因其輕量化設計,即使長時間作釣也不易疲勞。此外,容易掌握拋投時機亦是此釣竿特色。即使不習慣使用長而強韌的岸邊鐵板釣法竿者,也能流暢地遠投。無特殊慣性的竿身,無論鐵板或假餌皆能廣泛應對。</v>
+      </c>
+      <c r="N658" t="str">
+        <v>16,500~17,700円</v>
+      </c>
+      <c r="O658" t="str">
+        <v/>
+      </c>
+      <c r="P658" t="str">
+        <v>高品質岸拋鐵板竿的入門款式。 在享受釣魚樂趣與品嚐美味的海水路亞釣中,特別容易瞄準大魚、感受強大拉力的便是岸拋鐵板。這款 SHORE JIGGING X 採用了易於投擲的調性,因此能輕易地從防波堤等地遠投金屬鐵板或水面系路亞,讓人輕鬆享受岸拋鐵板的樂趣。搭載了 BRAIDING X,採用不輸給魚拉力的強韌竿身。全面支援岸拋鐵板的入門階段。 DAIWA 技術 BRAIDING X 用碳纖維帶將竿身尾節的最外層以X狀纏繞,釣竿操作時,抑制了會導致力量損耗的扭轉的強化結構。竿身本身保持纖細的同時,也確保了高強度,並降低手持時的重量感,從而提升操作性。 產品詳情 藉由以 X 狀碳纖維帶補強,強化強勁的竿尾部分,成功打造出堅固且損耗力極少的竿體。 能將路亞投射至更遠的近海,並確實承受青物的拉力。即便在擁擠的防波堤釣到大魚,也能強勢地將魚拉近。 目標的基準 ScrollLeft 路亞適用表 MOVIE 測試者印象 在岸邊鐵板釣法入門階段,這款釣竿的規格已相當完善。首先因其輕量化設計,即使長時間作釣也不易疲勞。此外,容易掌握拋投時機亦是此釣竿特色。即使不習慣使用長而強韌的岸邊鐵板釣法竿者,也能流暢地遠投。無特殊慣性的竿身,無論鐵板或假餌皆能廣泛應對。</v>
+      </c>
+      <c r="Q658" t="str">
+        <v>岸投铁板 / 青物 / 远投强负荷</v>
+      </c>
+      <c r="R658" t="str">
+        <v>覆盖金属铁板、重型 plug 和高负荷控鱼场景，重点在远投、抽停节奏和持续搏鱼余量。</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="str">
+        <v>DR1071</v>
+      </c>
+      <c r="B659">
+        <v>2</v>
+      </c>
+      <c r="C659" t="str">
+        <v>SEABASS FLAT X</v>
+      </c>
+      <c r="D659" t="str">
+        <v>SEABASS FLAT X</v>
+      </c>
+      <c r="E659" t="str">
+        <v/>
+      </c>
+      <c r="F659" t="str">
+        <v>SEABASS FLAT X</v>
+      </c>
+      <c r="G659" t="str">
+        <v>海鱸</v>
+      </c>
+      <c r="H659" t="str">
+        <v>海鲈,岸投</v>
+      </c>
+      <c r="I659" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1071_SEABASS_FLAT_X.jpg</v>
+      </c>
+      <c r="J659" t="str">
+        <v/>
+      </c>
+      <c r="K659" t="str">
+        <v/>
+      </c>
+      <c r="L659" t="str">
+        <v>海鱸</v>
+      </c>
+      <c r="M659" t="str">
+        <v>安心品質的入門級海鱸魚・扁魚專用釣竿 棲息於港灣、河川、運河等近岸水域,以「鰓洗」稱之的豪邁搏鬥著稱的海鱸魚。以及棲息於爽快海灘區、能享受海灘釣樂趣的平坦魚(比目魚・牛尾魚)。專為這兩大目標魚種設計的「海鱸扁魚X」,兼具易拋投性與抗魚拉力強韌的安心品質。助您開啟海水路亞釣的入門之旅。 DAIWA 技術 BRAIDING X 用碳纖維帶將竿身尾節的最外層以X狀纏繞,釣竿操作時,抑制了會導致力量損耗的扭轉的強化結構。竿身本身保持纖細的同時,也確保了高強度,並降低手持時的重量感,從而提升操作性。 產品詳情 在承受巨大負荷的竿尾部位,搭載抗扭力優異的編織X結構。有效降低動力損耗,提升遠投性能與操控性。</v>
+      </c>
+      <c r="N659" t="str">
+        <v>13,800~16,300円</v>
+      </c>
+      <c r="O659" t="str">
+        <v/>
+      </c>
+      <c r="P659" t="str">
+        <v>安心品質的入門級海鱸魚・扁魚專用釣竿 棲息於港灣、河川、運河等近岸水域,以「鰓洗」稱之的豪邁搏鬥著稱的海鱸魚。以及棲息於爽快海灘區、能享受海灘釣樂趣的平坦魚(比目魚・牛尾魚)。專為這兩大目標魚種設計的「海鱸扁魚X」,兼具易拋投性與抗魚拉力強韌的安心品質。助您開啟海水路亞釣的入門之旅。 DAIWA 技術 BRAIDING X 用碳纖維帶將竿身尾節的最外層以X狀纏繞,釣竿操作時,抑制了會導致力量損耗的扭轉的強化結構。竿身本身保持纖細的同時,也確保了高強度,並降低手持時的重量感,從而提升操作性。 產品詳情 在承受巨大負荷的竿尾部位,搭載抗扭力優異的編織X結構。有效降低動力損耗,提升遠投性能與操控性。</v>
+      </c>
+      <c r="Q659" t="str">
+        <v>海鲈 / 岸投 / 河口港湾到海滩</v>
+      </c>
+      <c r="R659" t="str">
+        <v>围绕米诺、沉水铅笔、震动和金属系路亚建立远投与控线能力，适合按场地宽度和目标鱼体型选长度。</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="str">
+        <v>DR1072</v>
+      </c>
+      <c r="B660">
+        <v>2</v>
+      </c>
+      <c r="C660" t="str">
+        <v>CHINING X</v>
+      </c>
+      <c r="D660" t="str">
+        <v>CHINING X</v>
+      </c>
+      <c r="E660" t="str">
+        <v/>
+      </c>
+      <c r="F660" t="str">
+        <v>CHINING X</v>
+      </c>
+      <c r="G660" t="str">
+        <v>黑鯛路亞</v>
+      </c>
+      <c r="H660" t="str">
+        <v>岸投</v>
+      </c>
+      <c r="I660" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1072_CHINING_X.jpg</v>
+      </c>
+      <c r="J660" t="str">
+        <v/>
+      </c>
+      <c r="K660" t="str">
+        <v/>
+      </c>
+      <c r="L660" t="str">
+        <v>黑鯛路亞</v>
+      </c>
+      <c r="M660" t="str">
+        <v>具備高操作性與最適柔韌度,能盡情享受黑鯛拉扯力的鱸魚釣竿 黑鯛專用調性的釣竿 搭載布雷丁X的強打竿尾 捲線器座採用下鎖式設計,具備優異的固定性能 產品詳情 在遠投與搏鬥時至關重要的竿尾部位,採用了防扭轉結構的編織X技術。 雖為高感度管狀竿身,卻採用柔韌竿尖設計。不易彈開黑鯛的咬餌動作。</v>
+      </c>
+      <c r="N660" t="str">
+        <v>13,500~15,100円</v>
+      </c>
+      <c r="O660" t="str">
+        <v/>
+      </c>
+      <c r="P660" t="str">
+        <v>具備高操作性與最適柔韌度,能盡情享受黑鯛拉扯力的鱸魚釣竿 黑鯛專用調性的釣竿 搭載布雷丁X的強打竿尾 捲線器座採用下鎖式設計,具備優異的固定性能 產品詳情 在遠投與搏鬥時至關重要的竿尾部位,採用了防扭轉結構的編織X技術。 雖為高感度管狀竿身,卻採用柔韌竿尖設計。不易彈開黑鯛的咬餌動作。</v>
+      </c>
+      <c r="Q660" t="str">
+        <v>黑鲷路亚 / Free Rig / 岸边底层攻略</v>
+      </c>
+      <c r="R660" t="str">
+        <v>围绕 free rig、Texas 和小型硬饵建立贴底搜索能力，适合河口、港湾与浅滩障碍边。</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="str">
+        <v>DR1073</v>
+      </c>
+      <c r="B661">
+        <v>2</v>
+      </c>
+      <c r="C661" t="str">
+        <v>竹筴魚 X</v>
+      </c>
+      <c r="D661" t="str">
+        <v>竹筴魚 X</v>
+      </c>
+      <c r="E661" t="str">
+        <v/>
+      </c>
+      <c r="F661" t="str">
+        <v>竹筴魚 X</v>
+      </c>
+      <c r="G661" t="str">
+        <v>輕型SW路亞(岩魚・竹筴魚)</v>
+      </c>
+      <c r="H661" t="str">
+        <v>根钓,岸投</v>
+      </c>
+      <c r="I661" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1073_X.png</v>
+      </c>
+      <c r="J661" t="str">
+        <v/>
+      </c>
+      <c r="K661" t="str">
+        <v/>
+      </c>
+      <c r="L661" t="str">
+        <v>輕型SW路亞(岩魚・竹筴魚)</v>
+      </c>
+      <c r="M661" t="str">
+        <v>無雜質且易於操作,輕量遊戲入門釣竿的終極之作 無特殊癖好且易於操作,專為輕量遊戲入門者設計的釣竿。 專為初次嘗試輕型海水釣法(如輕型竹筴魚釣、輕型鱈魚釣)的入門者設計的輕量化海水釣竿。 憑藉著無瑕疵且柔韌的坯料,即使是初學者也能輕鬆駕馭輕量路亞的拋投動作,使其在熟練前也能流暢操作。 另一方面,在承受負荷的球桿頭部至竿尾部位,搭載了具備抗扭轉結構的編織X技術。 由於功率損失減少,因此更容易控制拋投,即使遇到大魚獲時也能安心應對。 導環採用不易纏釣線的K型導環,並以最佳平衡配置。 即使在視野受限的夜間賽事或風勢強勁的環境下,也能安心使用。 DAIWA 技術 BRAIDING X 用碳纖維帶將竿身尾節的最外層以X狀纏繞,釣竿操作時,抑制了會導致力量損耗的扭轉的強化結構。竿身本身保持纖細的同時,也確保了高強度,並降低手持時的重量感,從而提升操作性。 產品詳情 輕量且銳利的竿身,調性設定為人人皆易掌控。拋投時能清晰感知路亞負荷,操作時則能感受路亞重量,精準操控路亞動作。竿尾部搭載編織X技術,有效抑制扭轉現象,減少動力損耗。</v>
+      </c>
+      <c r="N661" t="str">
+        <v>12,800~14,300円</v>
+      </c>
+      <c r="O661" t="str">
+        <v/>
+      </c>
+      <c r="P661" t="str">
+        <v>無雜質且易於操作,輕量遊戲入門釣竿的終極之作 無特殊癖好且易於操作,專為輕量遊戲入門者設計的釣竿。 專為初次嘗試輕型海水釣法(如輕型竹筴魚釣、輕型鱈魚釣)的入門者設計的輕量化海水釣竿。 憑藉著無瑕疵且柔韌的坯料,即使是初學者也能輕鬆駕馭輕量路亞的拋投動作,使其在熟練前也能流暢操作。 另一方面,在承受負荷的球桿頭部至竿尾部位,搭載了具備抗扭轉結構的編織X技術。 由於功率損失減少,因此更容易控制拋投,即使遇到大魚獲時也能安心應對。 導環採用不易纏釣線的K型導環,並以最佳平衡配置。 即使在視野受限的夜間賽事或風勢強勁的環境下,也能安心使用。 DAIWA 技術 BRAIDING X 用碳纖維帶將竿身尾節的最外層以X狀纏繞,釣竿操作時,抑制了會導致力量損耗的扭轉的強化結構。竿身本身保持纖細的同時,也確保了高強度,並降低手持時的重量感,從而提升操作性。 產品詳情 輕量且銳利的竿身,調性設定為人人皆易掌控。拋投時能清晰感知路亞負荷,操作時則能感受路亞重量,精準操控路亞動作。竿尾部搭載編織X技術,有效抑制扭轉現象,減少動力損耗。</v>
+      </c>
+      <c r="Q661" t="str">
+        <v>轻海水 / Ajing・Mebaring / 港湾精细</v>
+      </c>
+      <c r="R661" t="str">
+        <v>以轻量 jighead、小软饵和 micro plug 为核心，适合港湾、堤防和小型岩礁的细线控饵。</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="str">
+        <v>DR1074</v>
+      </c>
+      <c r="B662">
+        <v>2</v>
+      </c>
+      <c r="C662" t="str">
+        <v>TATULA XT</v>
+      </c>
+      <c r="D662" t="str">
+        <v>TATULA XT</v>
+      </c>
+      <c r="E662" t="str">
+        <v/>
+      </c>
+      <c r="F662" t="str">
+        <v>TATULA XT</v>
+      </c>
+      <c r="G662" t="str">
+        <v>鱸魚</v>
+      </c>
+      <c r="H662" t="str">
+        <v>bass</v>
+      </c>
+      <c r="I662" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/+mages/daiwa_rods/DR1074_TATULA_XT.jpg</v>
+      </c>
+      <c r="J662" t="str">
+        <v/>
+      </c>
+      <c r="K662" t="str">
+        <v/>
+      </c>
+      <c r="L662" t="str">
+        <v>鱸魚</v>
+      </c>
+      <c r="M662" t="str">
+        <v>世界標準「TATULA」 世界標準的路亞代名詞「TATULA」 釣竿全新系列「TATULA XT」正式登場!! 追求基本性能的極致,高性價比款式。 日本規格版針對日本釣場開發,從岸釣到船釣皆能對應,擁有豐富的款式陣容。 以 2 節竿(並繼)為主打,並針對經典規格推出單節竿版本。 在堅持專業細節的同時,具備極高的泛用性,外型吸睛且做工精悍。 DAIWA 技術 X45 為了防止在拋投、操作、上鉤、搏魚等動作中產生的扭轉,長年研究結果顯示,除了傳統結構(相對於竿尖0°、90°)外,再捲繞「45°」偏置交叉布(±45°傾斜的碳纖維等)是防止扭轉的最佳選擇。搭載X45,實現防止扭轉,並使力量、操作性和感度得到飛躍性提升。 產品詳細 以 TATULA 品牌代表色的黑色為基底,搭配銀色標誌與零件,呈現精悍的外觀。 型號介紹(單節竿) ScrollLeft 型號介紹(2節竿(並繼)) 路亞適用表 路亞適用表 PdfString MOVIE</v>
+      </c>
+      <c r="N662" t="str">
+        <v>12,100~13,800円</v>
+      </c>
+      <c r="O662" t="str">
+        <v/>
+      </c>
+      <c r="P662" t="str">
+        <v>世界標準「TATULA」 世界標準的路亞代名詞「TATULA」 釣竿全新系列「TATULA XT」正式登場!! 追求基本性能的極致,高性價比款式。 日本規格版針對日本釣場開發,從岸釣到船釣皆能對應,擁有豐富的款式陣容。 以 2 節竿(並繼)為主打,並針對經典規格推出單節竿版本。 在堅持專業細節的同時,具備極高的泛用性,外型吸睛且做工精悍。 DAIWA 技術 X45 為了防止在拋投、操作、上鉤、搏魚等動作中產生的扭轉,長年研究結果顯示,除了傳統結構(相對於竿尖0°、90°)外,再捲繞「45°」偏置交叉布(±45°傾斜的碳纖維等)是防止扭轉的最佳選擇。搭載X45,實現防止扭轉,並使力量、操作性和感度得到飛躍性提升。 產品詳細 以 TATULA 品牌代表色的黑色為基底,搭配銀色標誌與零件,呈現精悍的外觀。 型號介紹(單節竿) ScrollLeft 型號介紹(2節竿(並繼)) 路亞適用表 路亞適用表 PdfString MOVIE</v>
+      </c>
+      <c r="Q662" t="str">
+        <v>淡水 Bass / 技法分工 / 软硬饵覆盖</v>
+      </c>
+      <c r="R662" t="str">
+        <v>按子型号区分精细、卷阻、底操、cover 和大饵路线，适合依照钓组与作钓距离选型。</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R632"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R662"/>
   </ignoredErrors>
 </worksheet>
 </file>